--- a/中药材数据/中药材分类标签列表/中药材分类多维标签表.xlsx
+++ b/中药材数据/中药材分类标签列表/中药材分类多维标签表.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3807" uniqueCount="1185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3807" uniqueCount="841">
   <si>
     <t>药材名称</t>
   </si>
@@ -2455,1120 +2455,88 @@
     <t>脾、肾、肺、膀胱</t>
   </si>
   <si>
-    <t>健脾养胃、增强免疫、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气养血、滋阴润燥、润肺止咳、增强免疫、泻下通便</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、补气固表</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、补气固表、散寒止痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>清热降火、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、增强免疫、活血化瘀</t>
-  </si>
-  <si>
-    <t>收敛止血</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、疏肝理气、祛风湿痛</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、疏肝理气</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、滋阴养颜、补气固表、健脾升阳、增强免疫、疏肝理气、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、散寒止痛</t>
-  </si>
-  <si>
-    <t>润肺止咳、利水渗湿、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、养心安神、润肺止咳、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、增强免疫、利水渗湿</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>利水渗湿</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、健脾升阳、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养肝明目、清热降火、润肺止咳、疏肝理气、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、增强免疫、散寒止痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、润肺止咳、活血化瘀</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养心安神、补气固表、活血化瘀</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>润肺止咳、健脾升阳</t>
-  </si>
-  <si>
-    <t>增强免疫、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、补气固表、增强免疫、散寒止痛、疏肝理气</t>
-  </si>
-  <si>
-    <t>散寒止痛、祛风湿痛</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、散寒止痛、利水渗湿</t>
-  </si>
-  <si>
-    <t>滋阴润燥、散寒止痛</t>
-  </si>
-  <si>
-    <t>清热降火、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表</t>
+    <t>消食化积、驱虫止痒</t>
+  </si>
+  <si>
+    <t>滋阴养血、收敛固涩</t>
+  </si>
+  <si>
+    <t>开窍醒神、活血化瘀</t>
+  </si>
+  <si>
+    <t>温经止血、温里散寒</t>
+  </si>
+  <si>
+    <t>清热解毒、利水通淋</t>
+  </si>
+  <si>
+    <t>清热解毒</t>
   </si>
   <si>
     <t>活血化瘀</t>
   </si>
   <si>
-    <t>清热降火、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、疏肝理气、活血化瘀、泻下通便</t>
-  </si>
-  <si>
-    <t>健脾养胃</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养肝明目、润肺止咳、补气固表</t>
-  </si>
-  <si>
-    <t>补气固表、散寒止痛、活血化瘀</t>
-  </si>
-  <si>
-    <t>清热降火、养心安神、润肺止咳、补气固表、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、散寒止痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、补气固表、健脾升阳、增强免疫、疏肝理气、泻下通便、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、补气固表、增强免疫、宁心安神、祛风湿痛</t>
-  </si>
-  <si>
-    <t>补气固表、健脾升阳、散寒止痛、利水渗湿、疏肝理气、泻下通便、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、泻下通便、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、润肺止咳、补气固表、健脾升阳、利水渗湿、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>清热降火、增强免疫、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、增强免疫</t>
-  </si>
-  <si>
-    <t>清热降火、利水渗湿、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、增强免疫、疏肝理气</t>
-  </si>
-  <si>
-    <t>散寒止痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>散寒止痛</t>
-  </si>
-  <si>
-    <t>养肝明目、补气固表、健脾升阳、增强免疫、散寒止痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、养肝明目、清热降火、润肺止咳、散寒止痛、补虚暖身、利水渗湿、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>补气固表、健脾升阳、散寒止痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、润肺止咳、疏肝理气</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养肝明目、养心安神、健脾升阳、散寒止痛</t>
-  </si>
-  <si>
-    <t>润肺止咳</t>
-  </si>
-  <si>
-    <t>祛风湿痛</t>
-  </si>
-  <si>
-    <t>补气养血、活血化瘀</t>
-  </si>
-  <si>
-    <t>散寒止痛、疏肝理气、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火</t>
-  </si>
-  <si>
-    <t>润肺止咳、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养肝明目、清热降火、润肺止咳、补气固表、增强免疫、疏肝理气、泻下通便</t>
-  </si>
-  <si>
-    <t>增强免疫、散寒止痛、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、补气固表、增强免疫、疏肝理气、泻下通便</t>
-  </si>
-  <si>
-    <t>润肺止咳、散寒止痛、活血化瘀、祛风湿痛</t>
+    <t>凉血止血</t>
+  </si>
+  <si>
+    <t>滋阴养血</t>
+  </si>
+  <si>
+    <t>化痰止咳平喘</t>
+  </si>
+  <si>
+    <t>温补肾阳</t>
+  </si>
+  <si>
+    <t>清热泻火</t>
+  </si>
+  <si>
+    <t>理气解郁</t>
+  </si>
+  <si>
+    <t>益气固表</t>
+  </si>
+  <si>
+    <t>利水通淋</t>
+  </si>
+  <si>
+    <t>宁心安神</t>
+  </si>
+  <si>
+    <t>芳香化湿</t>
+  </si>
+  <si>
+    <t>开窍醒神</t>
+  </si>
+  <si>
+    <t>祛风除湿</t>
+  </si>
+  <si>
+    <t>泻下通便</t>
+  </si>
+  <si>
+    <t>解表散风</t>
+  </si>
+  <si>
+    <t>驱虫止痒</t>
+  </si>
+  <si>
+    <t>平肝息风</t>
+  </si>
+  <si>
+    <t>温里散寒</t>
   </si>
   <si>
     <t>收敛固涩</t>
   </si>
   <si>
-    <t>补气固表、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、润肺止咳、补气固表、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、补气固表、利水渗湿、疏肝理气、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、补气固表、健脾升阳、利水渗湿、疏肝理气</t>
-  </si>
-  <si>
-    <t>养肝明目、补气固表、健脾升阳</t>
-  </si>
-  <si>
-    <t>润肺止咳、利水渗湿</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气固表、健脾升阳、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>增强免疫、散寒止痛</t>
-  </si>
-  <si>
-    <t>疏肝理气</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、增强免疫、散寒止痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、散寒止痛、活血化瘀</t>
-  </si>
-  <si>
-    <t>补虚暖身、利水渗湿</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、增强免疫</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、利水渗湿、活血化瘀、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥</t>
-  </si>
-  <si>
-    <t>润肺止咳、温经养血、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、养心安神、补气固表、利水渗湿</t>
-  </si>
-  <si>
-    <t>活血化瘀、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、补气固表、散寒止痛</t>
-  </si>
-  <si>
-    <t>补气养血、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、利水渗湿</t>
-  </si>
-  <si>
-    <t>养肝明目、补气固表</t>
-  </si>
-  <si>
-    <t>补气固表、泻下通便、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>补气固表、温经养血、散寒止痛、活血化瘀</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、祛风湿痛</t>
-  </si>
-  <si>
-    <t>补气养血、滋阴润燥、清热降火、补气固表、健脾升阳</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气固表、健脾升阳、利水渗湿</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、补气固表、增强免疫、散寒止痛、疏肝理气、活血化瘀、泻下通便</t>
-  </si>
-  <si>
-    <t>增强免疫、补虚暖身</t>
-  </si>
-  <si>
-    <t>补气养血、补气固表、增强免疫、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、润肺止咳、活血化瘀、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、泻下通便、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>利水渗湿、疏肝理气</t>
-  </si>
-  <si>
-    <t>补气固表</t>
-  </si>
-  <si>
-    <t>健脾养胃、增强免疫、泻下通便</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、补气固表、泻下通便、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、补气固表、增强免疫、温经养血、散寒止痛、利水渗湿、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、补气固表、利水渗湿、疏肝理气</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、泻下通便、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养心安神、补气固表、健脾升阳、利水渗湿</t>
-  </si>
-  <si>
-    <t>健脾养胃、润肺止咳、散寒止痛、疏肝理气</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养肝明目、清热降火、润肺止咳、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气固表、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、散寒止痛、宁心安神、活血化瘀、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、润肺止咳、补气固表、增强免疫、散寒止痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、温经养血、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、增强免疫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、散寒止痛、疏肝理气</t>
-  </si>
-  <si>
-    <t>清热降火、养心安神、补气固表、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、润肺止咳</t>
-  </si>
-  <si>
-    <t>增强免疫、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、养心安神、润肺止咳、增强免疫、补虚暖身、祛风湿痛</t>
-  </si>
-  <si>
-    <t>养肝明目</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、利水渗湿</t>
-  </si>
-  <si>
-    <t>健脾养胃、润肺止咳、增强免疫</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气养血、滋阴润燥、养心安神、滋阴养颜、增强免疫、补虚暖身、祛风湿痛</t>
-  </si>
-  <si>
-    <t>补气养血、滋阴润燥、清热降火、养心安神、润肺止咳、补气固表、增强免疫</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气固表、增强免疫</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、补气固表、健脾升阳</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、增强免疫、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、润肺止咳、散寒止痛、补虚暖身、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养肝明目、清热降火、养心安神、散寒止痛、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、利水渗湿、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、利水渗湿、活血化瘀、泻下通便</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、散寒止痛、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、补气固表、疏肝理气、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、泻下通便</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养肝明目、清热降火、补气固表、增强免疫、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、补气固表、疏肝理气</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、散寒止痛、疏肝理气、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、养肝明目、增强免疫、疏肝理气、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、散寒止痛、利水渗湿、疏肝理气、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾升阳</t>
-  </si>
-  <si>
-    <t>养心安神</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养心安神、疏肝理气、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、补气固表、利水渗湿、活血化瘀</t>
-  </si>
-  <si>
-    <t>滋阴润燥、补气固表、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、散寒止痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气养血、滋阴润燥、清热降火、润肺止咳、补气固表、健脾升阳、增强免疫、散寒止痛、补虚暖身、疏肝理气、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、补气固表、散寒止痛、活血化瘀、泻下通便</t>
-  </si>
-  <si>
-    <t>养心安神、润肺止咳、散寒止痛、疏肝理气、活血化瘀、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、养心安神、补气固表、散寒止痛、泻下通便、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、补气固表、疏肝理气、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、健脾升阳、利水渗湿、疏肝理气、泻下通便</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、健脾升阳、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、养心安神、润肺止咳、补气固表、增强免疫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、散寒止痛、利水渗湿、活血化瘀、泻下通便、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气养血、清热降火、养心安神、润肺止咳、补气固表、健脾升阳、增强免疫、散寒止痛、活血化瘀、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>散寒止痛、疏肝理气</t>
-  </si>
-  <si>
-    <t>滋阴润燥、散寒止痛、补虚暖身、疏肝理气</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、散寒止痛、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、润肺止咳、利水渗湿、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>补气养血、滋阴润燥、清热降火、健脾升阳、泻下通便</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养心安神、润肺止咳、补气固表、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、补气固表、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、补气固表、健脾升阳、活血化瘀</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、增强免疫、散寒止痛、利水渗湿、活血化瘀、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、泻下通便</t>
-  </si>
-  <si>
-    <t>补气养血、滋阴润燥、清热降火、祛风湿痛</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、补气固表</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、活血化瘀</t>
-  </si>
-  <si>
-    <t>驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、健脾升阳、散寒止痛、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、散寒止痛、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、补气固表、泻下通便</t>
-  </si>
-  <si>
-    <t>补气固表、散寒止痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、散寒止痛、祛风湿痛</t>
-  </si>
-  <si>
-    <t>增强免疫、利水渗湿</t>
-  </si>
-  <si>
-    <t>补气固表、增强免疫</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、增强免疫、疏肝理气、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、增强免疫、宁心安神、泻下通便</t>
-  </si>
-  <si>
-    <t>利水渗湿、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、养心安神、补气固表、增强免疫、温经养血、补虚暖身、利水渗湿</t>
-  </si>
-  <si>
-    <t>滋阴润燥、补气固表</t>
-  </si>
-  <si>
-    <t>健脾养胃、养心安神</t>
-  </si>
-  <si>
-    <t>健脾养胃、润肺止咳、补气固表、活血化瘀</t>
-  </si>
-  <si>
-    <t>清热降火、养心安神、补气固表、健脾升阳</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、健脾升阳、利水渗湿、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、润肺止咳、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气养血、养心安神、润肺止咳、散寒止痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、补气固表、增强免疫、散寒止痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、散寒止痛、宁心安神、泻下通便</t>
-  </si>
-  <si>
-    <t>温经养血、补虚暖身、活血化瘀</t>
-  </si>
-  <si>
-    <t>养肝明目、养心安神、补气固表</t>
-  </si>
-  <si>
-    <t>散寒止痛、补虚暖身、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、增强免疫、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、散寒止痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、润肺止咳、补气固表、健脾升阳</t>
-  </si>
-  <si>
-    <t>清热降火、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾升阳、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>拔毒生肌</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、润肺止咳、温经养血、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、润肺止咳、增强免疫、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、润肺止咳、补气固表</t>
-  </si>
-  <si>
-    <t>健脾养胃、健脾升阳、增强免疫</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、补气固表、增强免疫、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>养心安神、活血化瘀</t>
-  </si>
-  <si>
-    <t>补气固表、增强免疫、活血化瘀</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、补气固表、增强免疫、利水渗湿、疏肝理气</t>
-  </si>
-  <si>
-    <t>清热降火、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>补气固表、利水渗湿、泻下通便</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、补气固表、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、宁心安神</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、润肺止咳、补气固表、增强免疫、利水渗湿、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、健脾升阳、增强免疫、利水渗湿、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>增强免疫、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、散寒止痛</t>
-  </si>
-  <si>
-    <t>清热降火、补气固表</t>
-  </si>
-  <si>
-    <t>滋阴润燥、健脾升阳、散寒止痛、疏肝理气、活血化瘀</t>
-  </si>
-  <si>
-    <t>增强免疫</t>
-  </si>
-  <si>
-    <t>健脾养胃、增强免疫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、补气固表</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、增强免疫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、利水渗湿</t>
-  </si>
-  <si>
-    <t>健脾养胃、养肝明目、补气固表、利水渗湿</t>
-  </si>
-  <si>
-    <t>补气固表、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气固表、散寒止痛、利水渗湿、疏肝理气、泻下通便、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>润肺止咳、散寒止痛、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、养心安神、滋阴养颜、补气固表、活血化瘀</t>
-  </si>
-  <si>
-    <t>润肺止咳、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、利水渗湿</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、润肺止咳</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、补气固表、疏肝理气、祛风湿痛</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、润肺止咳、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>平肝息风</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、增强免疫、泻下通便、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、散寒止痛、活血化瘀</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、补气固表、散寒止痛、补虚暖身、利水渗湿、疏肝理气、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、养心安神、润肺止咳、补气固表、增强免疫、疏肝理气、泻下通便</t>
-  </si>
-  <si>
-    <t>泻下通便、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>清热降火、泻下通便、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、养心安神、补气固表、散寒止痛</t>
-  </si>
-  <si>
-    <t>祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养肝明目、清热降火、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、健脾升阳、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>补虚暖身</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、利水渗湿、疏肝理气、活血化瘀、泻下通便、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、泻下通便</t>
-  </si>
-  <si>
-    <t>润肺止咳、增强免疫、散寒止痛、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、宁心安神、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>润肺止咳、利水渗湿、疏肝理气、祛风湿痛</t>
-  </si>
-  <si>
-    <t>开窍醒神</t>
-  </si>
-  <si>
-    <t>健脾升阳、补虚暖身、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>补气固表、活血化瘀</t>
-  </si>
-  <si>
-    <t>利水渗湿、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、润肺止咳、补气固表、健脾升阳、散寒止痛、疏肝理气</t>
-  </si>
-  <si>
-    <t>增强免疫、散寒止痛、利水渗湿、活血化瘀</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、活血化瘀、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>养肝明目、润肺止咳、健脾升阳、散寒止痛、祛风湿痛</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、润肺止咳、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、散寒止痛、疏肝理气、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>养心安神、补气固表</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火</t>
-  </si>
-  <si>
-    <t>泻下通便</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、活血化瘀</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养肝明目、清热降火、养心安神、润肺止咳、补气固表、健脾升阳、散寒止痛</t>
-  </si>
-  <si>
-    <t>补气养血、滋阴润燥、清热降火、润肺止咳、补气固表、健脾升阳、增强免疫、补虚暖身、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、利水渗湿、疏肝理气、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>增强免疫、散寒止痛、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、润肺止咳、散寒止痛、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、增强免疫、散寒止痛</t>
-  </si>
-  <si>
-    <t>养肝明目、养心安神、补气固表、增强免疫、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、增强免疫、疏肝理气、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、润肺止咳、补气固表、疏肝理气、祛风湿痛</t>
-  </si>
-  <si>
-    <t>散寒止痛、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气固表、增强免疫、散寒止痛</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、宁心安神</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、泻下通便</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、润肺止咳、增强免疫、利水渗湿</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、散寒止痛、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、润肺止咳、健脾升阳、散寒止痛、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、利水渗湿、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、散寒止痛、利水渗湿、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>补气养血、滋阴润燥、养肝明目、清热降火、养心安神、增强免疫、散寒止痛、补虚暖身</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、补气固表、祛风湿痛</t>
-  </si>
-  <si>
-    <t>增强免疫、活血化瘀</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、补气固表、活血化瘀</t>
-  </si>
-  <si>
-    <t>增强免疫、散寒止痛、活血化瘀</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、润肺止咳、利水渗湿、活血化瘀</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、润肺止咳、健脾升阳、疏肝理气、泻下通便</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、补气固表、增强免疫、散寒止痛、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气固表、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>补气养血、养肝明目、清热降火、利水渗湿、泻下通便</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、润肺止咳、利水渗湿、泻下通便、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、润肺止咳、补气固表</t>
-  </si>
-  <si>
-    <t>养肝明目、散寒止痛、活血化瘀</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、补气固表、健脾升阳、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、润肺止咳、补气固表、散寒止痛、利水渗湿、疏肝理气、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、活血化瘀、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>清热降火、疏肝理气、活血化瘀、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、补气固表、疏肝理气、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、补气固表、活血化瘀</t>
-  </si>
-  <si>
-    <t>润肺止咳、增强免疫、散寒止痛、活血化瘀</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、补气固表、散寒止痛、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、润肺止咳、补气固表、散寒止痛、疏肝理气</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、利水渗湿、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、散寒止痛、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、补气固表、利水渗湿</t>
-  </si>
-  <si>
-    <t>滋阴润燥、补气固表、散寒止痛、疏肝理气</t>
-  </si>
-  <si>
-    <t>养心安神、补气固表、利水渗湿、活血化瘀</t>
-  </si>
-  <si>
-    <t>散寒止痛、补虚暖身、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>增强免疫、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>散寒止痛、疏肝理气、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养肝明目、清热降火、润肺止咳、补虚暖身</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、补气固表、利水渗湿</t>
-  </si>
-  <si>
-    <t>滋阴润燥、补气固表、疏肝理气、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、润肺止咳、增强免疫、利水渗湿、疏肝理气、泻下通便</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、补气固表、散寒止痛、活血化瘀</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、补气固表、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、润肺止咳</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、养心安神、润肺止咳、补气固表、疏肝理气</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、利水渗湿</t>
-  </si>
-  <si>
-    <t>散寒止痛、利水渗湿、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养心安神、散寒止痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、补气固表、疏肝理气</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、增强免疫、温经养血、散寒止痛、补虚暖身、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、健脾升阳、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、利水渗湿</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、增强免疫、散寒止痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、利水渗湿、活血化瘀</t>
-  </si>
-  <si>
-    <t>润肺止咳、活血化瘀</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、养心安神、增强免疫</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、补气固表、健脾升阳、增强免疫、散寒止痛、宁心安神、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气养血、滋阴润燥、清热降火、润肺止咳、补气固表、增强免疫、补虚暖身</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、疏肝理气、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、润肺止咳、利水渗湿、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、润肺止咳、补气固表、祛风湿痛</t>
-  </si>
-  <si>
-    <t>利水渗湿、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气固表、增强免疫、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、补气固表、增强免疫</t>
-  </si>
-  <si>
-    <t>补气养血、养心安神</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、润肺止咳、散寒止痛、疏肝理气、祛风湿痛</t>
-  </si>
-  <si>
-    <t>补气固表、散寒止痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>润肺止咳、散寒止痛、利水渗湿、疏肝理气</t>
-  </si>
-  <si>
-    <t>滋阴润燥、利水渗湿、疏肝理气、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、增强免疫</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、散寒止痛、利水渗湿、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气固表、健脾升阳、增强免疫、祛风湿痛</t>
-  </si>
-  <si>
-    <t>养肝明目、养心安神</t>
+    <t>泻下通便、清热泻火</t>
+  </si>
+  <si>
+    <t>温经止血</t>
+  </si>
+  <si>
+    <t>消食化积</t>
   </si>
 </sst>
 </file>
@@ -4248,7 +3216,7 @@
         <v>645</v>
       </c>
       <c r="G14" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -4271,7 +3239,7 @@
         <v>646</v>
       </c>
       <c r="G15" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -4294,7 +3262,7 @@
         <v>647</v>
       </c>
       <c r="G16" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -4317,7 +3285,7 @@
         <v>648</v>
       </c>
       <c r="G17" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -4340,7 +3308,7 @@
         <v>649</v>
       </c>
       <c r="G18" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -4363,7 +3331,7 @@
         <v>650</v>
       </c>
       <c r="G19" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -4386,7 +3354,7 @@
         <v>641</v>
       </c>
       <c r="G20" t="s">
-        <v>831</v>
+        <v>822</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -4409,7 +3377,7 @@
         <v>651</v>
       </c>
       <c r="G21" t="s">
-        <v>832</v>
+        <v>818</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -4432,7 +3400,7 @@
         <v>652</v>
       </c>
       <c r="G22" t="s">
-        <v>833</v>
+        <v>821</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -4455,7 +3423,7 @@
         <v>636</v>
       </c>
       <c r="G23" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -4478,7 +3446,7 @@
         <v>653</v>
       </c>
       <c r="G24" t="s">
-        <v>835</v>
+        <v>823</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -4501,7 +3469,7 @@
         <v>654</v>
       </c>
       <c r="G25" t="s">
-        <v>836</v>
+        <v>822</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -4524,7 +3492,7 @@
         <v>655</v>
       </c>
       <c r="G26" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -4547,7 +3515,7 @@
         <v>642</v>
       </c>
       <c r="G27" t="s">
-        <v>838</v>
+        <v>829</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -4570,7 +3538,7 @@
         <v>656</v>
       </c>
       <c r="G28" t="s">
-        <v>839</v>
+        <v>825</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -4593,7 +3561,7 @@
         <v>657</v>
       </c>
       <c r="G29" t="s">
-        <v>840</v>
+        <v>827</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -4616,7 +3584,7 @@
         <v>658</v>
       </c>
       <c r="G30" t="s">
-        <v>841</v>
+        <v>830</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -4639,7 +3607,7 @@
         <v>647</v>
       </c>
       <c r="G31" t="s">
-        <v>842</v>
+        <v>824</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -4662,7 +3630,7 @@
         <v>659</v>
       </c>
       <c r="G32" t="s">
-        <v>843</v>
+        <v>822</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -4682,7 +3650,7 @@
         <v>627</v>
       </c>
       <c r="G33" t="s">
-        <v>844</v>
+        <v>819</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -4705,7 +3673,7 @@
         <v>649</v>
       </c>
       <c r="G34" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -4728,7 +3696,7 @@
         <v>660</v>
       </c>
       <c r="G35" t="s">
-        <v>846</v>
+        <v>825</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -4751,7 +3719,7 @@
         <v>661</v>
       </c>
       <c r="G36" t="s">
-        <v>847</v>
+        <v>824</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -4774,7 +3742,7 @@
         <v>662</v>
       </c>
       <c r="G37" t="s">
-        <v>848</v>
+        <v>832</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -4797,7 +3765,7 @@
         <v>663</v>
       </c>
       <c r="G38" t="s">
-        <v>829</v>
+        <v>820</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -4820,7 +3788,7 @@
         <v>636</v>
       </c>
       <c r="G39" t="s">
-        <v>849</v>
+        <v>820</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -4843,7 +3811,7 @@
         <v>640</v>
       </c>
       <c r="G40" t="s">
-        <v>850</v>
+        <v>833</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -4866,7 +3834,7 @@
         <v>652</v>
       </c>
       <c r="G41" t="s">
-        <v>851</v>
+        <v>821</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -4889,7 +3857,7 @@
         <v>658</v>
       </c>
       <c r="G42" t="s">
-        <v>852</v>
+        <v>821</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -4912,7 +3880,7 @@
         <v>657</v>
       </c>
       <c r="G43" t="s">
-        <v>853</v>
+        <v>833</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -4935,7 +3903,7 @@
         <v>664</v>
       </c>
       <c r="G44" t="s">
-        <v>844</v>
+        <v>834</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -4958,7 +3926,7 @@
         <v>647</v>
       </c>
       <c r="G45" t="s">
-        <v>854</v>
+        <v>826</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -4981,7 +3949,7 @@
         <v>647</v>
       </c>
       <c r="G46" t="s">
-        <v>855</v>
+        <v>822</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -5004,7 +3972,7 @@
         <v>660</v>
       </c>
       <c r="G47" t="s">
-        <v>856</v>
+        <v>834</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -5027,7 +3995,7 @@
         <v>657</v>
       </c>
       <c r="G48" t="s">
-        <v>857</v>
+        <v>822</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -5050,7 +4018,7 @@
         <v>665</v>
       </c>
       <c r="G49" t="s">
-        <v>858</v>
+        <v>818</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -5073,7 +4041,7 @@
         <v>635</v>
       </c>
       <c r="G50" t="s">
-        <v>859</v>
+        <v>824</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -5096,7 +4064,7 @@
         <v>666</v>
       </c>
       <c r="G51" t="s">
-        <v>829</v>
+        <v>818</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -5119,7 +4087,7 @@
         <v>667</v>
       </c>
       <c r="G52" t="s">
-        <v>860</v>
+        <v>834</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -5142,7 +4110,7 @@
         <v>668</v>
       </c>
       <c r="G53" t="s">
-        <v>861</v>
+        <v>824</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -5165,7 +4133,7 @@
         <v>669</v>
       </c>
       <c r="G54" t="s">
-        <v>862</v>
+        <v>834</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -5188,7 +4156,7 @@
         <v>670</v>
       </c>
       <c r="G55" t="s">
-        <v>863</v>
+        <v>826</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -5211,7 +4179,7 @@
         <v>671</v>
       </c>
       <c r="G56" t="s">
-        <v>864</v>
+        <v>827</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -5234,7 +4202,7 @@
         <v>672</v>
       </c>
       <c r="G57" t="s">
-        <v>829</v>
+        <v>818</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -5257,7 +4225,7 @@
         <v>647</v>
       </c>
       <c r="G58" t="s">
-        <v>865</v>
+        <v>829</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -5280,7 +4248,7 @@
         <v>657</v>
       </c>
       <c r="G59" t="s">
-        <v>866</v>
+        <v>833</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -5303,7 +4271,7 @@
         <v>673</v>
       </c>
       <c r="G60" t="s">
-        <v>867</v>
+        <v>820</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -5326,7 +4294,7 @@
         <v>674</v>
       </c>
       <c r="G61" t="s">
-        <v>868</v>
+        <v>827</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -5349,7 +4317,7 @@
         <v>646</v>
       </c>
       <c r="G62" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -5372,7 +4340,7 @@
         <v>675</v>
       </c>
       <c r="G63" t="s">
-        <v>869</v>
+        <v>836</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -5395,7 +4363,7 @@
         <v>676</v>
       </c>
       <c r="G64" t="s">
-        <v>870</v>
+        <v>826</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -5418,7 +4386,7 @@
         <v>677</v>
       </c>
       <c r="G65" t="s">
-        <v>871</v>
+        <v>822</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -5441,7 +4409,7 @@
         <v>678</v>
       </c>
       <c r="G66" t="s">
-        <v>847</v>
+        <v>818</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -5464,7 +4432,7 @@
         <v>679</v>
       </c>
       <c r="G67" t="s">
-        <v>872</v>
+        <v>828</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -5487,7 +4455,7 @@
         <v>640</v>
       </c>
       <c r="G68" t="s">
-        <v>873</v>
+        <v>833</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -5510,7 +4478,7 @@
         <v>680</v>
       </c>
       <c r="G69" t="s">
-        <v>874</v>
+        <v>825</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -5533,7 +4501,7 @@
         <v>640</v>
       </c>
       <c r="G70" t="s">
-        <v>874</v>
+        <v>833</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -5556,7 +4524,7 @@
         <v>665</v>
       </c>
       <c r="G71" t="s">
-        <v>875</v>
+        <v>819</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -5579,7 +4547,7 @@
         <v>681</v>
       </c>
       <c r="G72" t="s">
-        <v>876</v>
+        <v>825</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -5602,7 +4570,7 @@
         <v>682</v>
       </c>
       <c r="G73" t="s">
-        <v>877</v>
+        <v>826</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -5625,7 +4593,7 @@
         <v>649</v>
       </c>
       <c r="G74" t="s">
-        <v>878</v>
+        <v>836</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -5648,7 +4616,7 @@
         <v>683</v>
       </c>
       <c r="G75" t="s">
-        <v>879</v>
+        <v>829</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -5671,7 +4639,7 @@
         <v>649</v>
       </c>
       <c r="G76" t="s">
-        <v>880</v>
+        <v>819</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -5694,7 +4662,7 @@
         <v>642</v>
       </c>
       <c r="G77" t="s">
-        <v>881</v>
+        <v>825</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -5717,7 +4685,7 @@
         <v>646</v>
       </c>
       <c r="G78" t="s">
-        <v>882</v>
+        <v>819</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -5740,7 +4708,7 @@
         <v>684</v>
       </c>
       <c r="G79" t="s">
-        <v>883</v>
+        <v>837</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -5763,7 +4731,7 @@
         <v>647</v>
       </c>
       <c r="G80" t="s">
-        <v>884</v>
+        <v>829</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -5786,7 +4754,7 @@
         <v>685</v>
       </c>
       <c r="G81" t="s">
-        <v>885</v>
+        <v>819</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -5809,7 +4777,7 @@
         <v>686</v>
       </c>
       <c r="G82" t="s">
-        <v>886</v>
+        <v>824</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -5832,7 +4800,7 @@
         <v>685</v>
       </c>
       <c r="G83" t="s">
-        <v>887</v>
+        <v>833</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -5855,7 +4823,7 @@
         <v>687</v>
       </c>
       <c r="G84" t="s">
-        <v>888</v>
+        <v>825</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -5878,7 +4846,7 @@
         <v>688</v>
       </c>
       <c r="G85" t="s">
-        <v>889</v>
+        <v>827</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -5901,7 +4869,7 @@
         <v>634</v>
       </c>
       <c r="G86" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -5924,7 +4892,7 @@
         <v>689</v>
       </c>
       <c r="G87" t="s">
-        <v>890</v>
+        <v>827</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -5947,7 +4915,7 @@
         <v>690</v>
       </c>
       <c r="G88" t="s">
-        <v>891</v>
+        <v>820</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -5970,7 +4938,7 @@
         <v>635</v>
       </c>
       <c r="G89" t="s">
-        <v>892</v>
+        <v>818</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -5993,7 +4961,7 @@
         <v>691</v>
       </c>
       <c r="G90" t="s">
-        <v>849</v>
+        <v>818</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -6016,7 +4984,7 @@
         <v>692</v>
       </c>
       <c r="G91" t="s">
-        <v>893</v>
+        <v>825</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -6039,7 +5007,7 @@
         <v>635</v>
       </c>
       <c r="G92" t="s">
-        <v>894</v>
+        <v>824</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -6062,7 +5030,7 @@
         <v>693</v>
       </c>
       <c r="G93" t="s">
-        <v>847</v>
+        <v>835</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -6085,7 +5053,7 @@
         <v>652</v>
       </c>
       <c r="G94" t="s">
-        <v>895</v>
+        <v>820</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -6108,7 +5076,7 @@
         <v>652</v>
       </c>
       <c r="G95" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -6131,7 +5099,7 @@
         <v>694</v>
       </c>
       <c r="G96" t="s">
-        <v>896</v>
+        <v>827</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -6154,7 +5122,7 @@
         <v>685</v>
       </c>
       <c r="G97" t="s">
-        <v>897</v>
+        <v>822</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -6177,7 +5145,7 @@
         <v>695</v>
       </c>
       <c r="G98" t="s">
-        <v>898</v>
+        <v>818</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -6200,7 +5168,7 @@
         <v>696</v>
       </c>
       <c r="G99" t="s">
-        <v>899</v>
+        <v>825</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -6223,7 +5191,7 @@
         <v>697</v>
       </c>
       <c r="G100" t="s">
-        <v>900</v>
+        <v>836</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -6246,7 +5214,7 @@
         <v>698</v>
       </c>
       <c r="G101" t="s">
-        <v>901</v>
+        <v>827</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -6269,7 +5237,7 @@
         <v>690</v>
       </c>
       <c r="G102" t="s">
-        <v>902</v>
+        <v>834</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -6292,7 +5260,7 @@
         <v>699</v>
       </c>
       <c r="G103" t="s">
-        <v>903</v>
+        <v>834</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -6315,7 +5283,7 @@
         <v>647</v>
       </c>
       <c r="G104" t="s">
-        <v>904</v>
+        <v>826</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -6338,7 +5306,7 @@
         <v>674</v>
       </c>
       <c r="G105" t="s">
-        <v>905</v>
+        <v>827</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -6361,7 +5329,7 @@
         <v>700</v>
       </c>
       <c r="G106" t="s">
-        <v>906</v>
+        <v>827</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -6384,7 +5352,7 @@
         <v>701</v>
       </c>
       <c r="G107" t="s">
-        <v>907</v>
+        <v>825</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -6407,7 +5375,7 @@
         <v>674</v>
       </c>
       <c r="G108" t="s">
-        <v>908</v>
+        <v>831</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -6430,7 +5398,7 @@
         <v>702</v>
       </c>
       <c r="G109" t="s">
-        <v>909</v>
+        <v>819</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -6453,7 +5421,7 @@
         <v>703</v>
       </c>
       <c r="G110" t="s">
-        <v>910</v>
+        <v>824</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -6476,7 +5444,7 @@
         <v>704</v>
       </c>
       <c r="G111" t="s">
-        <v>911</v>
+        <v>835</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -6499,7 +5467,7 @@
         <v>653</v>
       </c>
       <c r="G112" t="s">
-        <v>912</v>
+        <v>823</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -6522,7 +5490,7 @@
         <v>705</v>
       </c>
       <c r="G113" t="s">
-        <v>913</v>
+        <v>826</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -6545,7 +5513,7 @@
         <v>706</v>
       </c>
       <c r="G114" t="s">
-        <v>914</v>
+        <v>827</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -6568,7 +5536,7 @@
         <v>651</v>
       </c>
       <c r="G115" t="s">
-        <v>915</v>
+        <v>838</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -6591,7 +5559,7 @@
         <v>659</v>
       </c>
       <c r="G116" t="s">
-        <v>916</v>
+        <v>823</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -6614,7 +5582,7 @@
         <v>707</v>
       </c>
       <c r="G117" t="s">
-        <v>899</v>
+        <v>836</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -6637,7 +5605,7 @@
         <v>636</v>
       </c>
       <c r="G118" t="s">
-        <v>917</v>
+        <v>821</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -6660,7 +5628,7 @@
         <v>708</v>
       </c>
       <c r="G119" t="s">
-        <v>918</v>
+        <v>822</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -6683,7 +5651,7 @@
         <v>640</v>
       </c>
       <c r="G120" t="s">
-        <v>919</v>
+        <v>836</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -6706,7 +5674,7 @@
         <v>709</v>
       </c>
       <c r="G121" t="s">
-        <v>899</v>
+        <v>836</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -6729,7 +5697,7 @@
         <v>710</v>
       </c>
       <c r="G122" t="s">
-        <v>920</v>
+        <v>834</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -6752,7 +5720,7 @@
         <v>674</v>
       </c>
       <c r="G123" t="s">
-        <v>921</v>
+        <v>825</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -6775,7 +5743,7 @@
         <v>674</v>
       </c>
       <c r="G124" t="s">
-        <v>905</v>
+        <v>837</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -6798,7 +5766,7 @@
         <v>711</v>
       </c>
       <c r="G125" t="s">
-        <v>922</v>
+        <v>837</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -6821,7 +5789,7 @@
         <v>712</v>
       </c>
       <c r="G126" t="s">
-        <v>923</v>
+        <v>832</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -6844,7 +5812,7 @@
         <v>713</v>
       </c>
       <c r="G127" t="s">
-        <v>873</v>
+        <v>824</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -6867,7 +5835,7 @@
         <v>714</v>
       </c>
       <c r="G128" t="s">
-        <v>924</v>
+        <v>833</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -6890,7 +5858,7 @@
         <v>715</v>
       </c>
       <c r="G129" t="s">
-        <v>925</v>
+        <v>836</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6913,7 +5881,7 @@
         <v>716</v>
       </c>
       <c r="G130" t="s">
-        <v>926</v>
+        <v>831</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -6936,7 +5904,7 @@
         <v>638</v>
       </c>
       <c r="G131" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -6959,7 +5927,7 @@
         <v>700</v>
       </c>
       <c r="G132" t="s">
-        <v>927</v>
+        <v>826</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -6982,7 +5950,7 @@
         <v>647</v>
       </c>
       <c r="G133" t="s">
-        <v>899</v>
+        <v>839</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -7005,7 +5973,7 @@
         <v>717</v>
       </c>
       <c r="G134" t="s">
-        <v>928</v>
+        <v>827</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -7028,7 +5996,7 @@
         <v>670</v>
       </c>
       <c r="G135" t="s">
-        <v>929</v>
+        <v>825</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -7051,7 +6019,7 @@
         <v>653</v>
       </c>
       <c r="G136" t="s">
-        <v>930</v>
+        <v>818</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -7074,7 +6042,7 @@
         <v>718</v>
       </c>
       <c r="G137" t="s">
-        <v>829</v>
+        <v>818</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -7097,7 +6065,7 @@
         <v>719</v>
       </c>
       <c r="G138" t="s">
-        <v>931</v>
+        <v>838</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -7120,7 +6088,7 @@
         <v>653</v>
       </c>
       <c r="G139" t="s">
-        <v>844</v>
+        <v>823</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -7143,7 +6111,7 @@
         <v>649</v>
       </c>
       <c r="G140" t="s">
-        <v>932</v>
+        <v>818</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -7166,7 +6134,7 @@
         <v>699</v>
       </c>
       <c r="G141" t="s">
-        <v>933</v>
+        <v>836</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -7189,7 +6157,7 @@
         <v>657</v>
       </c>
       <c r="G142" t="s">
-        <v>934</v>
+        <v>822</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -7212,7 +6180,7 @@
         <v>653</v>
       </c>
       <c r="G143" t="s">
-        <v>935</v>
+        <v>831</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -7232,7 +6200,7 @@
         <v>720</v>
       </c>
       <c r="G144" t="s">
-        <v>936</v>
+        <v>833</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -7255,7 +6223,7 @@
         <v>647</v>
       </c>
       <c r="G145" t="s">
-        <v>922</v>
+        <v>818</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -7278,7 +6246,7 @@
         <v>659</v>
       </c>
       <c r="G146" t="s">
-        <v>829</v>
+        <v>818</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -7301,7 +6269,7 @@
         <v>647</v>
       </c>
       <c r="G147" t="s">
-        <v>937</v>
+        <v>840</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -7324,7 +6292,7 @@
         <v>647</v>
       </c>
       <c r="G148" t="s">
-        <v>938</v>
+        <v>836</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -7347,7 +6315,7 @@
         <v>699</v>
       </c>
       <c r="G149" t="s">
-        <v>939</v>
+        <v>826</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -7370,7 +6338,7 @@
         <v>710</v>
       </c>
       <c r="G150" t="s">
-        <v>940</v>
+        <v>822</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -7393,7 +6361,7 @@
         <v>652</v>
       </c>
       <c r="G151" t="s">
-        <v>941</v>
+        <v>834</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -7416,7 +6384,7 @@
         <v>659</v>
       </c>
       <c r="G152" t="s">
-        <v>942</v>
+        <v>823</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -7439,7 +6407,7 @@
         <v>699</v>
       </c>
       <c r="G153" t="s">
-        <v>877</v>
+        <v>836</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -7462,7 +6430,7 @@
         <v>647</v>
       </c>
       <c r="G154" t="s">
-        <v>911</v>
+        <v>833</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -7485,7 +6453,7 @@
         <v>649</v>
       </c>
       <c r="G155" t="s">
-        <v>943</v>
+        <v>833</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -7505,7 +6473,7 @@
         <v>630</v>
       </c>
       <c r="G156" t="s">
-        <v>864</v>
+        <v>818</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -7528,7 +6496,7 @@
         <v>721</v>
       </c>
       <c r="G157" t="s">
-        <v>944</v>
+        <v>824</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -7551,7 +6519,7 @@
         <v>647</v>
       </c>
       <c r="G158" t="s">
-        <v>945</v>
+        <v>822</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -7574,7 +6542,7 @@
         <v>665</v>
       </c>
       <c r="G159" t="s">
-        <v>874</v>
+        <v>818</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -7597,7 +6565,7 @@
         <v>722</v>
       </c>
       <c r="G160" t="s">
-        <v>874</v>
+        <v>835</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -7620,7 +6588,7 @@
         <v>653</v>
       </c>
       <c r="G161" t="s">
-        <v>946</v>
+        <v>821</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -7643,7 +6611,7 @@
         <v>723</v>
       </c>
       <c r="G162" t="s">
-        <v>947</v>
+        <v>821</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -7666,7 +6634,7 @@
         <v>724</v>
       </c>
       <c r="G163" t="s">
-        <v>912</v>
+        <v>833</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -7689,7 +6657,7 @@
         <v>725</v>
       </c>
       <c r="G164" t="s">
-        <v>948</v>
+        <v>824</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -7712,7 +6680,7 @@
         <v>726</v>
       </c>
       <c r="G165" t="s">
-        <v>911</v>
+        <v>825</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -7735,7 +6703,7 @@
         <v>710</v>
       </c>
       <c r="G166" t="s">
-        <v>949</v>
+        <v>837</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -7758,7 +6726,7 @@
         <v>727</v>
       </c>
       <c r="G167" t="s">
-        <v>950</v>
+        <v>822</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -7781,7 +6749,7 @@
         <v>728</v>
       </c>
       <c r="G168" t="s">
-        <v>916</v>
+        <v>826</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -7804,7 +6772,7 @@
         <v>648</v>
       </c>
       <c r="G169" t="s">
-        <v>951</v>
+        <v>836</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -7827,7 +6795,7 @@
         <v>640</v>
       </c>
       <c r="G170" t="s">
-        <v>847</v>
+        <v>825</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -7850,7 +6818,7 @@
         <v>729</v>
       </c>
       <c r="G171" t="s">
-        <v>952</v>
+        <v>828</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -7873,7 +6841,7 @@
         <v>730</v>
       </c>
       <c r="G172" t="s">
-        <v>953</v>
+        <v>822</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -7896,7 +6864,7 @@
         <v>731</v>
       </c>
       <c r="G173" t="s">
-        <v>899</v>
+        <v>821</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -7919,7 +6887,7 @@
         <v>660</v>
       </c>
       <c r="G174" t="s">
-        <v>954</v>
+        <v>832</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -7942,7 +6910,7 @@
         <v>653</v>
       </c>
       <c r="G175" t="s">
-        <v>955</v>
+        <v>825</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -7965,7 +6933,7 @@
         <v>634</v>
       </c>
       <c r="G176" t="s">
-        <v>956</v>
+        <v>822</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -7988,7 +6956,7 @@
         <v>653</v>
       </c>
       <c r="G177" t="s">
-        <v>957</v>
+        <v>837</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -8011,7 +6979,7 @@
         <v>732</v>
       </c>
       <c r="G178" t="s">
-        <v>958</v>
+        <v>823</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -8034,7 +7002,7 @@
         <v>733</v>
       </c>
       <c r="G179" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -8057,7 +7025,7 @@
         <v>705</v>
       </c>
       <c r="G180" t="s">
-        <v>873</v>
+        <v>825</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -8080,7 +7048,7 @@
         <v>642</v>
       </c>
       <c r="G181" t="s">
-        <v>959</v>
+        <v>825</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -8103,7 +7071,7 @@
         <v>662</v>
       </c>
       <c r="G182" t="s">
-        <v>960</v>
+        <v>836</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -8126,7 +7094,7 @@
         <v>648</v>
       </c>
       <c r="G183" t="s">
-        <v>961</v>
+        <v>821</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -8149,7 +7117,7 @@
         <v>730</v>
       </c>
       <c r="G184" t="s">
-        <v>962</v>
+        <v>831</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -8172,7 +7140,7 @@
         <v>734</v>
       </c>
       <c r="G185" t="s">
-        <v>849</v>
+        <v>826</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -8195,7 +7163,7 @@
         <v>735</v>
       </c>
       <c r="G186" t="s">
-        <v>963</v>
+        <v>825</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -8218,7 +7186,7 @@
         <v>636</v>
       </c>
       <c r="G187" t="s">
-        <v>964</v>
+        <v>820</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -8241,7 +7209,7 @@
         <v>653</v>
       </c>
       <c r="G188" t="s">
-        <v>877</v>
+        <v>823</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -8264,7 +7232,7 @@
         <v>736</v>
       </c>
       <c r="G189" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -8287,7 +7255,7 @@
         <v>737</v>
       </c>
       <c r="G190" t="s">
-        <v>965</v>
+        <v>828</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -8310,7 +7278,7 @@
         <v>638</v>
       </c>
       <c r="G191" t="s">
-        <v>966</v>
+        <v>819</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -8333,7 +7301,7 @@
         <v>702</v>
       </c>
       <c r="G192" t="s">
-        <v>875</v>
+        <v>819</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -8356,7 +7324,7 @@
         <v>738</v>
       </c>
       <c r="G193" t="s">
-        <v>967</v>
+        <v>824</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -8379,7 +7347,7 @@
         <v>653</v>
       </c>
       <c r="G194" t="s">
-        <v>968</v>
+        <v>821</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -8402,7 +7370,7 @@
         <v>739</v>
       </c>
       <c r="G195" t="s">
-        <v>969</v>
+        <v>829</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -8448,7 +7416,7 @@
         <v>702</v>
       </c>
       <c r="G197" t="s">
-        <v>829</v>
+        <v>818</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -8471,7 +7439,7 @@
         <v>642</v>
       </c>
       <c r="G198" t="s">
-        <v>970</v>
+        <v>826</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -8494,7 +7462,7 @@
         <v>674</v>
       </c>
       <c r="G199" t="s">
-        <v>971</v>
+        <v>824</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -8517,7 +7485,7 @@
         <v>702</v>
       </c>
       <c r="G200" t="s">
-        <v>972</v>
+        <v>828</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -8540,7 +7508,7 @@
         <v>741</v>
       </c>
       <c r="G201" t="s">
-        <v>973</v>
+        <v>824</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -8563,7 +7531,7 @@
         <v>706</v>
       </c>
       <c r="G202" t="s">
-        <v>921</v>
+        <v>827</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -8586,7 +7554,7 @@
         <v>742</v>
       </c>
       <c r="G203" t="s">
-        <v>918</v>
+        <v>820</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -8609,7 +7577,7 @@
         <v>660</v>
       </c>
       <c r="G204" t="s">
-        <v>974</v>
+        <v>829</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -8632,7 +7600,7 @@
         <v>743</v>
       </c>
       <c r="G205" t="s">
-        <v>975</v>
+        <v>824</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -8655,7 +7623,7 @@
         <v>641</v>
       </c>
       <c r="G206" t="s">
-        <v>976</v>
+        <v>818</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -8678,7 +7646,7 @@
         <v>722</v>
       </c>
       <c r="G207" t="s">
-        <v>844</v>
+        <v>820</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -8701,7 +7669,7 @@
         <v>744</v>
       </c>
       <c r="G208" t="s">
-        <v>977</v>
+        <v>826</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -8724,7 +7692,7 @@
         <v>653</v>
       </c>
       <c r="G209" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -8747,7 +7715,7 @@
         <v>691</v>
       </c>
       <c r="G210" t="s">
-        <v>893</v>
+        <v>840</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -8767,7 +7735,7 @@
         <v>628</v>
       </c>
       <c r="G211" t="s">
-        <v>978</v>
+        <v>827</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -8790,7 +7758,7 @@
         <v>669</v>
       </c>
       <c r="G212" t="s">
-        <v>979</v>
+        <v>840</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -8813,7 +7781,7 @@
         <v>655</v>
       </c>
       <c r="G213" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -8836,7 +7804,7 @@
         <v>709</v>
       </c>
       <c r="G214" t="s">
-        <v>980</v>
+        <v>819</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -8859,7 +7827,7 @@
         <v>653</v>
       </c>
       <c r="G215" t="s">
-        <v>981</v>
+        <v>825</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -8882,7 +7850,7 @@
         <v>697</v>
       </c>
       <c r="G216" t="s">
-        <v>982</v>
+        <v>820</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -8905,7 +7873,7 @@
         <v>745</v>
       </c>
       <c r="G217" t="s">
-        <v>829</v>
+        <v>818</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -8928,7 +7896,7 @@
         <v>746</v>
       </c>
       <c r="G218" t="s">
-        <v>983</v>
+        <v>827</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -8951,7 +7919,7 @@
         <v>747</v>
       </c>
       <c r="G219" t="s">
-        <v>984</v>
+        <v>837</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -8974,7 +7942,7 @@
         <v>647</v>
       </c>
       <c r="G220" t="s">
-        <v>911</v>
+        <v>840</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -8997,7 +7965,7 @@
         <v>642</v>
       </c>
       <c r="G221" t="s">
-        <v>985</v>
+        <v>825</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -9020,7 +7988,7 @@
         <v>700</v>
       </c>
       <c r="G222" t="s">
-        <v>873</v>
+        <v>818</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -9040,7 +8008,7 @@
         <v>640</v>
       </c>
       <c r="G223" t="s">
-        <v>986</v>
+        <v>833</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -9063,7 +8031,7 @@
         <v>748</v>
       </c>
       <c r="G224" t="s">
-        <v>987</v>
+        <v>836</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -9086,7 +8054,7 @@
         <v>646</v>
       </c>
       <c r="G225" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -9109,7 +8077,7 @@
         <v>657</v>
       </c>
       <c r="G226" t="s">
-        <v>899</v>
+        <v>822</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -9132,7 +8100,7 @@
         <v>653</v>
       </c>
       <c r="G227" t="s">
-        <v>964</v>
+        <v>820</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -9155,7 +8123,7 @@
         <v>653</v>
       </c>
       <c r="G228" t="s">
-        <v>943</v>
+        <v>818</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -9178,7 +8146,7 @@
         <v>665</v>
       </c>
       <c r="G229" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -9201,7 +8169,7 @@
         <v>749</v>
       </c>
       <c r="G230" t="s">
-        <v>988</v>
+        <v>839</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -9224,7 +8192,7 @@
         <v>688</v>
       </c>
       <c r="G231" t="s">
-        <v>989</v>
+        <v>818</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -9247,7 +8215,7 @@
         <v>657</v>
       </c>
       <c r="G232" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -9270,7 +8238,7 @@
         <v>750</v>
       </c>
       <c r="G233" t="s">
-        <v>990</v>
+        <v>839</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -9293,7 +8261,7 @@
         <v>653</v>
       </c>
       <c r="G234" t="s">
-        <v>991</v>
+        <v>819</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -9316,7 +8284,7 @@
         <v>640</v>
       </c>
       <c r="G235" t="s">
-        <v>992</v>
+        <v>833</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -9339,7 +8307,7 @@
         <v>657</v>
       </c>
       <c r="G236" t="s">
-        <v>922</v>
+        <v>824</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -9362,7 +8330,7 @@
         <v>717</v>
       </c>
       <c r="G237" t="s">
-        <v>911</v>
+        <v>824</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -9385,7 +8353,7 @@
         <v>638</v>
       </c>
       <c r="G238" t="s">
-        <v>993</v>
+        <v>824</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -9408,7 +8376,7 @@
         <v>683</v>
       </c>
       <c r="G239" t="s">
-        <v>994</v>
+        <v>834</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -9431,7 +8399,7 @@
         <v>641</v>
       </c>
       <c r="G240" t="s">
-        <v>934</v>
+        <v>822</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -9454,7 +8422,7 @@
         <v>751</v>
       </c>
       <c r="G241" t="s">
-        <v>995</v>
+        <v>824</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -9477,7 +8445,7 @@
         <v>700</v>
       </c>
       <c r="G242" t="s">
-        <v>944</v>
+        <v>824</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -9500,7 +8468,7 @@
         <v>749</v>
       </c>
       <c r="G243" t="s">
-        <v>873</v>
+        <v>822</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -9523,7 +8491,7 @@
         <v>665</v>
       </c>
       <c r="G244" t="s">
-        <v>996</v>
+        <v>833</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -9546,7 +8514,7 @@
         <v>700</v>
       </c>
       <c r="G245" t="s">
-        <v>997</v>
+        <v>822</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -9569,7 +8537,7 @@
         <v>651</v>
       </c>
       <c r="G246" t="s">
-        <v>998</v>
+        <v>824</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -9592,7 +8560,7 @@
         <v>653</v>
       </c>
       <c r="G247" t="s">
-        <v>999</v>
+        <v>839</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -9615,7 +8583,7 @@
         <v>752</v>
       </c>
       <c r="G248" t="s">
-        <v>1000</v>
+        <v>818</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -9638,7 +8606,7 @@
         <v>722</v>
       </c>
       <c r="G249" t="s">
-        <v>1001</v>
+        <v>825</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -9661,7 +8629,7 @@
         <v>715</v>
       </c>
       <c r="G250" t="s">
-        <v>923</v>
+        <v>837</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -9684,7 +8652,7 @@
         <v>638</v>
       </c>
       <c r="G251" t="s">
-        <v>1002</v>
+        <v>819</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -9707,7 +8675,7 @@
         <v>657</v>
       </c>
       <c r="G252" t="s">
-        <v>980</v>
+        <v>824</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -9730,7 +8698,7 @@
         <v>722</v>
       </c>
       <c r="G253" t="s">
-        <v>1003</v>
+        <v>835</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -9753,7 +8721,7 @@
         <v>641</v>
       </c>
       <c r="G254" t="s">
-        <v>1004</v>
+        <v>840</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -9776,7 +8744,7 @@
         <v>647</v>
       </c>
       <c r="G255" t="s">
-        <v>895</v>
+        <v>840</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -9799,7 +8767,7 @@
         <v>653</v>
       </c>
       <c r="G256" t="s">
-        <v>1005</v>
+        <v>823</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -9822,7 +8790,7 @@
         <v>641</v>
       </c>
       <c r="G257" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -9845,7 +8813,7 @@
         <v>702</v>
       </c>
       <c r="G258" t="s">
-        <v>874</v>
+        <v>818</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -9868,7 +8836,7 @@
         <v>653</v>
       </c>
       <c r="G259" t="s">
-        <v>1006</v>
+        <v>836</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -9891,7 +8859,7 @@
         <v>647</v>
       </c>
       <c r="G260" t="s">
-        <v>918</v>
+        <v>836</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -9914,7 +8882,7 @@
         <v>665</v>
       </c>
       <c r="G261" t="s">
-        <v>1007</v>
+        <v>835</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -9937,7 +8905,7 @@
         <v>657</v>
       </c>
       <c r="G262" t="s">
-        <v>1008</v>
+        <v>840</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -9960,7 +8928,7 @@
         <v>753</v>
       </c>
       <c r="G263" t="s">
-        <v>1009</v>
+        <v>828</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -9983,7 +8951,7 @@
         <v>657</v>
       </c>
       <c r="G264" t="s">
-        <v>1010</v>
+        <v>820</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -10006,7 +8974,7 @@
         <v>730</v>
       </c>
       <c r="G265" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -10029,7 +8997,7 @@
         <v>754</v>
       </c>
       <c r="G266" t="s">
-        <v>1011</v>
+        <v>831</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -10052,7 +9020,7 @@
         <v>755</v>
       </c>
       <c r="G267" t="s">
-        <v>1012</v>
+        <v>821</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -10075,7 +9043,7 @@
         <v>709</v>
       </c>
       <c r="G268" t="s">
-        <v>1013</v>
+        <v>826</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -10098,7 +9066,7 @@
         <v>642</v>
       </c>
       <c r="G269" t="s">
-        <v>829</v>
+        <v>818</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -10121,7 +9089,7 @@
         <v>653</v>
       </c>
       <c r="G270" t="s">
-        <v>1014</v>
+        <v>825</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -10144,7 +9112,7 @@
         <v>727</v>
       </c>
       <c r="G271" t="s">
-        <v>941</v>
+        <v>822</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -10167,7 +9135,7 @@
         <v>756</v>
       </c>
       <c r="G272" t="s">
-        <v>948</v>
+        <v>818</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -10190,7 +9158,7 @@
         <v>653</v>
       </c>
       <c r="G273" t="s">
-        <v>893</v>
+        <v>825</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -10213,7 +9181,7 @@
         <v>757</v>
       </c>
       <c r="G274" t="s">
-        <v>1015</v>
+        <v>824</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -10236,7 +9204,7 @@
         <v>657</v>
       </c>
       <c r="G275" t="s">
-        <v>873</v>
+        <v>818</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -10259,7 +9227,7 @@
         <v>688</v>
       </c>
       <c r="G276" t="s">
-        <v>1016</v>
+        <v>826</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -10282,7 +9250,7 @@
         <v>730</v>
       </c>
       <c r="G277" t="s">
-        <v>1017</v>
+        <v>833</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -10305,7 +9273,7 @@
         <v>653</v>
       </c>
       <c r="G278" t="s">
-        <v>1018</v>
+        <v>831</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -10328,7 +9296,7 @@
         <v>685</v>
       </c>
       <c r="G279" t="s">
-        <v>1019</v>
+        <v>824</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -10351,7 +9319,7 @@
         <v>668</v>
       </c>
       <c r="G280" t="s">
-        <v>847</v>
+        <v>824</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -10374,7 +9342,7 @@
         <v>653</v>
       </c>
       <c r="G281" t="s">
-        <v>1020</v>
+        <v>836</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -10397,7 +9365,7 @@
         <v>758</v>
       </c>
       <c r="G282" t="s">
-        <v>1021</v>
+        <v>834</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -10420,7 +9388,7 @@
         <v>759</v>
       </c>
       <c r="G283" t="s">
-        <v>1022</v>
+        <v>821</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -10443,7 +9411,7 @@
         <v>652</v>
       </c>
       <c r="G284" t="s">
-        <v>874</v>
+        <v>831</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -10466,7 +9434,7 @@
         <v>702</v>
       </c>
       <c r="G285" t="s">
-        <v>1023</v>
+        <v>818</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -10489,7 +9457,7 @@
         <v>652</v>
       </c>
       <c r="G286" t="s">
-        <v>880</v>
+        <v>819</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -10512,7 +9480,7 @@
         <v>673</v>
       </c>
       <c r="G287" t="s">
-        <v>847</v>
+        <v>818</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -10535,7 +9503,7 @@
         <v>652</v>
       </c>
       <c r="G288" t="s">
-        <v>847</v>
+        <v>818</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -10558,7 +9526,7 @@
         <v>760</v>
       </c>
       <c r="G289" t="s">
-        <v>1024</v>
+        <v>833</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -10581,7 +9549,7 @@
         <v>680</v>
       </c>
       <c r="G290" t="s">
-        <v>1025</v>
+        <v>818</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -10604,7 +9572,7 @@
         <v>652</v>
       </c>
       <c r="G291" t="s">
-        <v>1026</v>
+        <v>825</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -10627,7 +9595,7 @@
         <v>647</v>
       </c>
       <c r="G292" t="s">
-        <v>849</v>
+        <v>840</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -10650,7 +9618,7 @@
         <v>640</v>
       </c>
       <c r="G293" t="s">
-        <v>1027</v>
+        <v>822</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -10673,7 +9641,7 @@
         <v>646</v>
       </c>
       <c r="G294" t="s">
-        <v>910</v>
+        <v>822</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -10696,7 +9664,7 @@
         <v>653</v>
       </c>
       <c r="G295" t="s">
-        <v>1028</v>
+        <v>821</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -10719,7 +9687,7 @@
         <v>662</v>
       </c>
       <c r="G296" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="297" spans="1:7">
@@ -10742,7 +9710,7 @@
         <v>761</v>
       </c>
       <c r="G297" t="s">
-        <v>1029</v>
+        <v>834</v>
       </c>
     </row>
     <row r="298" spans="1:7">
@@ -10765,7 +9733,7 @@
         <v>650</v>
       </c>
       <c r="G298" t="s">
-        <v>874</v>
+        <v>833</v>
       </c>
     </row>
     <row r="299" spans="1:7">
@@ -10788,7 +9756,7 @@
         <v>762</v>
       </c>
       <c r="G299" t="s">
-        <v>1030</v>
+        <v>820</v>
       </c>
     </row>
     <row r="300" spans="1:7">
@@ -10811,7 +9779,7 @@
         <v>763</v>
       </c>
       <c r="G300" t="s">
-        <v>1031</v>
+        <v>833</v>
       </c>
     </row>
     <row r="301" spans="1:7">
@@ -10834,7 +9802,7 @@
         <v>665</v>
       </c>
       <c r="G301" t="s">
-        <v>1032</v>
+        <v>819</v>
       </c>
     </row>
     <row r="302" spans="1:7">
@@ -10857,7 +9825,7 @@
         <v>764</v>
       </c>
       <c r="G302" t="s">
-        <v>1033</v>
+        <v>827</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -10880,7 +9848,7 @@
         <v>744</v>
       </c>
       <c r="G303" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
     </row>
     <row r="304" spans="1:7">
@@ -10903,7 +9871,7 @@
         <v>641</v>
       </c>
       <c r="G304" t="s">
-        <v>874</v>
+        <v>820</v>
       </c>
     </row>
     <row r="305" spans="1:7">
@@ -10926,7 +9894,7 @@
         <v>662</v>
       </c>
       <c r="G305" t="s">
-        <v>893</v>
+        <v>838</v>
       </c>
     </row>
     <row r="306" spans="1:7">
@@ -10949,7 +9917,7 @@
         <v>765</v>
       </c>
       <c r="G306" t="s">
-        <v>1034</v>
+        <v>821</v>
       </c>
     </row>
     <row r="307" spans="1:7">
@@ -10972,7 +9940,7 @@
         <v>766</v>
       </c>
       <c r="G307" t="s">
-        <v>1035</v>
+        <v>825</v>
       </c>
     </row>
     <row r="308" spans="1:7">
@@ -10995,7 +9963,7 @@
         <v>761</v>
       </c>
       <c r="G308" t="s">
-        <v>1036</v>
+        <v>824</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -11018,7 +9986,7 @@
         <v>652</v>
       </c>
       <c r="G309" t="s">
-        <v>1037</v>
+        <v>834</v>
       </c>
     </row>
     <row r="310" spans="1:7">
@@ -11041,7 +10009,7 @@
         <v>653</v>
       </c>
       <c r="G310" t="s">
-        <v>1038</v>
+        <v>835</v>
       </c>
     </row>
     <row r="311" spans="1:7">
@@ -11064,7 +10032,7 @@
         <v>767</v>
       </c>
       <c r="G311" t="s">
-        <v>1039</v>
+        <v>818</v>
       </c>
     </row>
     <row r="312" spans="1:7">
@@ -11087,7 +10055,7 @@
         <v>640</v>
       </c>
       <c r="G312" t="s">
-        <v>1030</v>
+        <v>821</v>
       </c>
     </row>
     <row r="313" spans="1:7">
@@ -11110,7 +10078,7 @@
         <v>702</v>
       </c>
       <c r="G313" t="s">
-        <v>1040</v>
+        <v>835</v>
       </c>
     </row>
     <row r="314" spans="1:7">
@@ -11133,7 +10101,7 @@
         <v>684</v>
       </c>
       <c r="G314" t="s">
-        <v>1041</v>
+        <v>818</v>
       </c>
     </row>
     <row r="315" spans="1:7">
@@ -11156,7 +10124,7 @@
         <v>699</v>
       </c>
       <c r="G315" t="s">
-        <v>1042</v>
+        <v>836</v>
       </c>
     </row>
     <row r="316" spans="1:7">
@@ -11179,7 +10147,7 @@
         <v>657</v>
       </c>
       <c r="G316" t="s">
-        <v>907</v>
+        <v>833</v>
       </c>
     </row>
     <row r="317" spans="1:7">
@@ -11202,7 +10170,7 @@
         <v>653</v>
       </c>
       <c r="G317" t="s">
-        <v>877</v>
+        <v>821</v>
       </c>
     </row>
     <row r="318" spans="1:7">
@@ -11225,7 +10193,7 @@
         <v>653</v>
       </c>
       <c r="G318" t="s">
-        <v>1043</v>
+        <v>819</v>
       </c>
     </row>
     <row r="319" spans="1:7">
@@ -11248,7 +10216,7 @@
         <v>665</v>
       </c>
       <c r="G319" t="s">
-        <v>1044</v>
+        <v>819</v>
       </c>
     </row>
     <row r="320" spans="1:7">
@@ -11271,7 +10239,7 @@
         <v>649</v>
       </c>
       <c r="G320" t="s">
-        <v>874</v>
+        <v>818</v>
       </c>
     </row>
     <row r="321" spans="1:7">
@@ -11294,7 +10262,7 @@
         <v>657</v>
       </c>
       <c r="G321" t="s">
-        <v>1045</v>
+        <v>818</v>
       </c>
     </row>
     <row r="322" spans="1:7">
@@ -11317,7 +10285,7 @@
         <v>768</v>
       </c>
       <c r="G322" t="s">
-        <v>1046</v>
+        <v>825</v>
       </c>
     </row>
     <row r="323" spans="1:7">
@@ -11340,7 +10308,7 @@
         <v>641</v>
       </c>
       <c r="G323" t="s">
-        <v>873</v>
+        <v>822</v>
       </c>
     </row>
     <row r="324" spans="1:7">
@@ -11363,7 +10331,7 @@
         <v>722</v>
       </c>
       <c r="G324" t="s">
-        <v>1047</v>
+        <v>820</v>
       </c>
     </row>
     <row r="325" spans="1:7">
@@ -11386,7 +10354,7 @@
         <v>744</v>
       </c>
       <c r="G325" t="s">
-        <v>1048</v>
+        <v>825</v>
       </c>
     </row>
     <row r="326" spans="1:7">
@@ -11409,7 +10377,7 @@
         <v>649</v>
       </c>
       <c r="G326" t="s">
-        <v>1049</v>
+        <v>824</v>
       </c>
     </row>
     <row r="327" spans="1:7">
@@ -11432,7 +10400,7 @@
         <v>647</v>
       </c>
       <c r="G327" t="s">
-        <v>1050</v>
+        <v>829</v>
       </c>
     </row>
     <row r="328" spans="1:7">
@@ -11455,7 +10423,7 @@
         <v>657</v>
       </c>
       <c r="G328" t="s">
-        <v>878</v>
+        <v>822</v>
       </c>
     </row>
     <row r="329" spans="1:7">
@@ -11478,7 +10446,7 @@
         <v>665</v>
       </c>
       <c r="G329" t="s">
-        <v>829</v>
+        <v>818</v>
       </c>
     </row>
     <row r="330" spans="1:7">
@@ -11501,7 +10469,7 @@
         <v>769</v>
       </c>
       <c r="G330" t="s">
-        <v>1051</v>
+        <v>836</v>
       </c>
     </row>
     <row r="331" spans="1:7">
@@ -11524,7 +10492,7 @@
         <v>653</v>
       </c>
       <c r="G331" t="s">
-        <v>908</v>
+        <v>831</v>
       </c>
     </row>
     <row r="332" spans="1:7">
@@ -11547,7 +10515,7 @@
         <v>680</v>
       </c>
       <c r="G332" t="s">
-        <v>1052</v>
+        <v>818</v>
       </c>
     </row>
     <row r="333" spans="1:7">
@@ -11570,7 +10538,7 @@
         <v>770</v>
       </c>
       <c r="G333" t="s">
-        <v>1053</v>
+        <v>827</v>
       </c>
     </row>
     <row r="334" spans="1:7">
@@ -11593,7 +10561,7 @@
         <v>685</v>
       </c>
       <c r="G334" t="s">
-        <v>815</v>
+        <v>824</v>
       </c>
     </row>
     <row r="335" spans="1:7">
@@ -11616,7 +10584,7 @@
         <v>653</v>
       </c>
       <c r="G335" t="s">
-        <v>1054</v>
+        <v>834</v>
       </c>
     </row>
     <row r="336" spans="1:7">
@@ -11639,7 +10607,7 @@
         <v>771</v>
       </c>
       <c r="G336" t="s">
-        <v>1055</v>
+        <v>838</v>
       </c>
     </row>
     <row r="337" spans="1:7">
@@ -11662,7 +10630,7 @@
         <v>657</v>
       </c>
       <c r="G337" t="s">
-        <v>1056</v>
+        <v>825</v>
       </c>
     </row>
     <row r="338" spans="1:7">
@@ -11685,7 +10653,7 @@
         <v>685</v>
       </c>
       <c r="G338" t="s">
-        <v>998</v>
+        <v>825</v>
       </c>
     </row>
     <row r="339" spans="1:7">
@@ -11708,7 +10676,7 @@
         <v>772</v>
       </c>
       <c r="G339" t="s">
-        <v>1057</v>
+        <v>820</v>
       </c>
     </row>
     <row r="340" spans="1:7">
@@ -11731,7 +10699,7 @@
         <v>773</v>
       </c>
       <c r="G340" t="s">
-        <v>1058</v>
+        <v>822</v>
       </c>
     </row>
     <row r="341" spans="1:7">
@@ -11754,7 +10722,7 @@
         <v>649</v>
       </c>
       <c r="G341" t="s">
-        <v>1059</v>
+        <v>827</v>
       </c>
     </row>
     <row r="342" spans="1:7">
@@ -11777,7 +10745,7 @@
         <v>656</v>
       </c>
       <c r="G342" t="s">
-        <v>1060</v>
+        <v>824</v>
       </c>
     </row>
     <row r="343" spans="1:7">
@@ -11800,7 +10768,7 @@
         <v>774</v>
       </c>
       <c r="G343" t="s">
-        <v>829</v>
+        <v>818</v>
       </c>
     </row>
     <row r="344" spans="1:7">
@@ -11823,7 +10791,7 @@
         <v>691</v>
       </c>
       <c r="G344" t="s">
-        <v>1038</v>
+        <v>837</v>
       </c>
     </row>
     <row r="345" spans="1:7">
@@ -11846,7 +10814,7 @@
         <v>775</v>
       </c>
       <c r="G345" t="s">
-        <v>1061</v>
+        <v>831</v>
       </c>
     </row>
     <row r="346" spans="1:7">
@@ -11869,7 +10837,7 @@
         <v>776</v>
       </c>
       <c r="G346" t="s">
-        <v>874</v>
+        <v>833</v>
       </c>
     </row>
     <row r="347" spans="1:7">
@@ -11915,7 +10883,7 @@
         <v>640</v>
       </c>
       <c r="G348" t="s">
-        <v>1062</v>
+        <v>827</v>
       </c>
     </row>
     <row r="349" spans="1:7">
@@ -11938,7 +10906,7 @@
         <v>665</v>
       </c>
       <c r="G349" t="s">
-        <v>1063</v>
+        <v>835</v>
       </c>
     </row>
     <row r="350" spans="1:7">
@@ -11961,7 +10929,7 @@
         <v>652</v>
       </c>
       <c r="G350" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="351" spans="1:7">
@@ -11984,7 +10952,7 @@
         <v>777</v>
       </c>
       <c r="G351" t="s">
-        <v>1064</v>
+        <v>823</v>
       </c>
     </row>
     <row r="352" spans="1:7">
@@ -12007,7 +10975,7 @@
         <v>658</v>
       </c>
       <c r="G352" t="s">
-        <v>1065</v>
+        <v>833</v>
       </c>
     </row>
     <row r="353" spans="1:7">
@@ -12030,7 +10998,7 @@
         <v>700</v>
       </c>
       <c r="G353" t="s">
-        <v>1049</v>
+        <v>837</v>
       </c>
     </row>
     <row r="354" spans="1:7">
@@ -12053,7 +11021,7 @@
         <v>636</v>
       </c>
       <c r="G354" t="s">
-        <v>1066</v>
+        <v>819</v>
       </c>
     </row>
     <row r="355" spans="1:7">
@@ -12076,7 +11044,7 @@
         <v>668</v>
       </c>
       <c r="G355" t="s">
-        <v>829</v>
+        <v>818</v>
       </c>
     </row>
     <row r="356" spans="1:7">
@@ -12099,7 +11067,7 @@
         <v>778</v>
       </c>
       <c r="G356" t="s">
-        <v>1067</v>
+        <v>836</v>
       </c>
     </row>
     <row r="357" spans="1:7">
@@ -12122,7 +11090,7 @@
         <v>705</v>
       </c>
       <c r="G357" t="s">
-        <v>1068</v>
+        <v>826</v>
       </c>
     </row>
     <row r="358" spans="1:7">
@@ -12145,7 +11113,7 @@
         <v>652</v>
       </c>
       <c r="G358" t="s">
-        <v>1069</v>
+        <v>836</v>
       </c>
     </row>
     <row r="359" spans="1:7">
@@ -12168,7 +11136,7 @@
         <v>652</v>
       </c>
       <c r="G359" t="s">
-        <v>1070</v>
+        <v>834</v>
       </c>
     </row>
     <row r="360" spans="1:7">
@@ -12191,7 +11159,7 @@
         <v>779</v>
       </c>
       <c r="G360" t="s">
-        <v>844</v>
+        <v>819</v>
       </c>
     </row>
     <row r="361" spans="1:7">
@@ -12214,7 +11182,7 @@
         <v>649</v>
       </c>
       <c r="G361" t="s">
-        <v>829</v>
+        <v>818</v>
       </c>
     </row>
     <row r="362" spans="1:7">
@@ -12237,7 +11205,7 @@
         <v>780</v>
       </c>
       <c r="G362" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
     </row>
     <row r="363" spans="1:7">
@@ -12260,7 +11228,7 @@
         <v>653</v>
       </c>
       <c r="G363" t="s">
-        <v>1071</v>
+        <v>837</v>
       </c>
     </row>
     <row r="364" spans="1:7">
@@ -12283,7 +11251,7 @@
         <v>640</v>
       </c>
       <c r="G364" t="s">
-        <v>849</v>
+        <v>824</v>
       </c>
     </row>
     <row r="365" spans="1:7">
@@ -12306,7 +11274,7 @@
         <v>652</v>
       </c>
       <c r="G365" t="s">
-        <v>1072</v>
+        <v>834</v>
       </c>
     </row>
     <row r="366" spans="1:7">
@@ -12329,7 +11297,7 @@
         <v>653</v>
       </c>
       <c r="G366" t="s">
-        <v>1073</v>
+        <v>819</v>
       </c>
     </row>
     <row r="367" spans="1:7">
@@ -12352,7 +11320,7 @@
         <v>781</v>
       </c>
       <c r="G367" t="s">
-        <v>1074</v>
+        <v>837</v>
       </c>
     </row>
     <row r="368" spans="1:7">
@@ -12375,7 +11343,7 @@
         <v>691</v>
       </c>
       <c r="G368" t="s">
-        <v>874</v>
+        <v>836</v>
       </c>
     </row>
     <row r="369" spans="1:7">
@@ -12398,7 +11366,7 @@
         <v>780</v>
       </c>
       <c r="G369" t="s">
-        <v>847</v>
+        <v>825</v>
       </c>
     </row>
     <row r="370" spans="1:7">
@@ -12421,7 +11389,7 @@
         <v>653</v>
       </c>
       <c r="G370" t="s">
-        <v>1075</v>
+        <v>823</v>
       </c>
     </row>
     <row r="371" spans="1:7">
@@ -12444,7 +11412,7 @@
         <v>647</v>
       </c>
       <c r="G371" t="s">
-        <v>994</v>
+        <v>834</v>
       </c>
     </row>
     <row r="372" spans="1:7">
@@ -12467,7 +11435,7 @@
         <v>653</v>
       </c>
       <c r="G372" t="s">
-        <v>1076</v>
+        <v>818</v>
       </c>
     </row>
     <row r="373" spans="1:7">
@@ -12490,7 +11458,7 @@
         <v>653</v>
       </c>
       <c r="G373" t="s">
-        <v>1077</v>
+        <v>823</v>
       </c>
     </row>
     <row r="374" spans="1:7">
@@ -12513,7 +11481,7 @@
         <v>657</v>
       </c>
       <c r="G374" t="s">
-        <v>1078</v>
+        <v>839</v>
       </c>
     </row>
     <row r="375" spans="1:7">
@@ -12559,7 +11527,7 @@
         <v>665</v>
       </c>
       <c r="G376" t="s">
-        <v>1079</v>
+        <v>819</v>
       </c>
     </row>
     <row r="377" spans="1:7">
@@ -12582,7 +11550,7 @@
         <v>700</v>
       </c>
       <c r="G377" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
     </row>
     <row r="378" spans="1:7">
@@ -12605,7 +11573,7 @@
         <v>642</v>
       </c>
       <c r="G378" t="s">
-        <v>1080</v>
+        <v>822</v>
       </c>
     </row>
     <row r="379" spans="1:7">
@@ -12628,7 +11596,7 @@
         <v>782</v>
       </c>
       <c r="G379" t="s">
-        <v>1081</v>
+        <v>830</v>
       </c>
     </row>
     <row r="380" spans="1:7">
@@ -12651,7 +11619,7 @@
         <v>758</v>
       </c>
       <c r="G380" t="s">
-        <v>1082</v>
+        <v>834</v>
       </c>
     </row>
     <row r="381" spans="1:7">
@@ -12674,7 +11642,7 @@
         <v>652</v>
       </c>
       <c r="G381" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
     </row>
     <row r="382" spans="1:7">
@@ -12697,7 +11665,7 @@
         <v>652</v>
       </c>
       <c r="G382" t="s">
-        <v>1083</v>
+        <v>819</v>
       </c>
     </row>
     <row r="383" spans="1:7">
@@ -12720,7 +11688,7 @@
         <v>697</v>
       </c>
       <c r="G383" t="s">
-        <v>1084</v>
+        <v>831</v>
       </c>
     </row>
     <row r="384" spans="1:7">
@@ -12743,7 +11711,7 @@
         <v>647</v>
       </c>
       <c r="G384" t="s">
-        <v>1085</v>
+        <v>829</v>
       </c>
     </row>
     <row r="385" spans="1:7">
@@ -12763,7 +11731,7 @@
         <v>783</v>
       </c>
       <c r="G385" t="s">
-        <v>844</v>
+        <v>820</v>
       </c>
     </row>
     <row r="386" spans="1:7">
@@ -12786,7 +11754,7 @@
         <v>653</v>
       </c>
       <c r="G386" t="s">
-        <v>1086</v>
+        <v>827</v>
       </c>
     </row>
     <row r="387" spans="1:7">
@@ -12809,7 +11777,7 @@
         <v>658</v>
       </c>
       <c r="G387" t="s">
-        <v>1087</v>
+        <v>818</v>
       </c>
     </row>
     <row r="388" spans="1:7">
@@ -12832,7 +11800,7 @@
         <v>640</v>
       </c>
       <c r="G388" t="s">
-        <v>1088</v>
+        <v>833</v>
       </c>
     </row>
     <row r="389" spans="1:7">
@@ -12855,7 +11823,7 @@
         <v>657</v>
       </c>
       <c r="G389" t="s">
-        <v>1089</v>
+        <v>822</v>
       </c>
     </row>
     <row r="390" spans="1:7">
@@ -12878,7 +11846,7 @@
         <v>641</v>
       </c>
       <c r="G390" t="s">
-        <v>1090</v>
+        <v>819</v>
       </c>
     </row>
     <row r="391" spans="1:7">
@@ -12901,7 +11869,7 @@
         <v>680</v>
       </c>
       <c r="G391" t="s">
-        <v>1091</v>
+        <v>819</v>
       </c>
     </row>
     <row r="392" spans="1:7">
@@ -12924,7 +11892,7 @@
         <v>702</v>
       </c>
       <c r="G392" t="s">
-        <v>965</v>
+        <v>828</v>
       </c>
     </row>
     <row r="393" spans="1:7">
@@ -12947,7 +11915,7 @@
         <v>702</v>
       </c>
       <c r="G393" t="s">
-        <v>1036</v>
+        <v>819</v>
       </c>
     </row>
     <row r="394" spans="1:7">
@@ -12970,7 +11938,7 @@
         <v>784</v>
       </c>
       <c r="G394" t="s">
-        <v>1092</v>
+        <v>828</v>
       </c>
     </row>
     <row r="395" spans="1:7">
@@ -12993,7 +11961,7 @@
         <v>785</v>
       </c>
       <c r="G395" t="s">
-        <v>1093</v>
+        <v>821</v>
       </c>
     </row>
     <row r="396" spans="1:7">
@@ -13016,7 +11984,7 @@
         <v>653</v>
       </c>
       <c r="G396" t="s">
-        <v>1094</v>
+        <v>821</v>
       </c>
     </row>
     <row r="397" spans="1:7">
@@ -13039,7 +12007,7 @@
         <v>652</v>
       </c>
       <c r="G397" t="s">
-        <v>1095</v>
+        <v>830</v>
       </c>
     </row>
     <row r="398" spans="1:7">
@@ -13062,7 +12030,7 @@
         <v>739</v>
       </c>
       <c r="G398" t="s">
-        <v>1096</v>
+        <v>833</v>
       </c>
     </row>
     <row r="399" spans="1:7">
@@ -13085,7 +12053,7 @@
         <v>653</v>
       </c>
       <c r="G399" t="s">
-        <v>1097</v>
+        <v>831</v>
       </c>
     </row>
     <row r="400" spans="1:7">
@@ -13108,7 +12076,7 @@
         <v>653</v>
       </c>
       <c r="G400" t="s">
-        <v>1098</v>
+        <v>818</v>
       </c>
     </row>
     <row r="401" spans="1:7">
@@ -13131,7 +12099,7 @@
         <v>653</v>
       </c>
       <c r="G401" t="s">
-        <v>1063</v>
+        <v>835</v>
       </c>
     </row>
     <row r="402" spans="1:7">
@@ -13154,7 +12122,7 @@
         <v>786</v>
       </c>
       <c r="G402" t="s">
-        <v>1099</v>
+        <v>818</v>
       </c>
     </row>
     <row r="403" spans="1:7">
@@ -13177,7 +12145,7 @@
         <v>665</v>
       </c>
       <c r="G403" t="s">
-        <v>1100</v>
+        <v>825</v>
       </c>
     </row>
     <row r="404" spans="1:7">
@@ -13200,7 +12168,7 @@
         <v>646</v>
       </c>
       <c r="G404" t="s">
-        <v>1095</v>
+        <v>820</v>
       </c>
     </row>
     <row r="405" spans="1:7">
@@ -13223,7 +12191,7 @@
         <v>744</v>
       </c>
       <c r="G405" t="s">
-        <v>1101</v>
+        <v>826</v>
       </c>
     </row>
     <row r="406" spans="1:7">
@@ -13246,7 +12214,7 @@
         <v>640</v>
       </c>
       <c r="G406" t="s">
-        <v>1020</v>
+        <v>830</v>
       </c>
     </row>
     <row r="407" spans="1:7">
@@ -13269,7 +12237,7 @@
         <v>653</v>
       </c>
       <c r="G407" t="s">
-        <v>1102</v>
+        <v>837</v>
       </c>
     </row>
     <row r="408" spans="1:7">
@@ -13292,7 +12260,7 @@
         <v>653</v>
       </c>
       <c r="G408" t="s">
-        <v>1103</v>
+        <v>821</v>
       </c>
     </row>
     <row r="409" spans="1:7">
@@ -13315,7 +12283,7 @@
         <v>787</v>
       </c>
       <c r="G409" t="s">
-        <v>1104</v>
+        <v>833</v>
       </c>
     </row>
     <row r="410" spans="1:7">
@@ -13338,7 +12306,7 @@
         <v>702</v>
       </c>
       <c r="G410" t="s">
-        <v>1048</v>
+        <v>818</v>
       </c>
     </row>
     <row r="411" spans="1:7">
@@ -13361,7 +12329,7 @@
         <v>788</v>
       </c>
       <c r="G411" t="s">
-        <v>1105</v>
+        <v>819</v>
       </c>
     </row>
     <row r="412" spans="1:7">
@@ -13384,7 +12352,7 @@
         <v>683</v>
       </c>
       <c r="G412" t="s">
-        <v>1106</v>
+        <v>840</v>
       </c>
     </row>
     <row r="413" spans="1:7">
@@ -13407,7 +12375,7 @@
         <v>702</v>
       </c>
       <c r="G413" t="s">
-        <v>1107</v>
+        <v>822</v>
       </c>
     </row>
     <row r="414" spans="1:7">
@@ -13430,7 +12398,7 @@
         <v>659</v>
       </c>
       <c r="G414" t="s">
-        <v>1108</v>
+        <v>821</v>
       </c>
     </row>
     <row r="415" spans="1:7">
@@ -13453,7 +12421,7 @@
         <v>642</v>
       </c>
       <c r="G415" t="s">
-        <v>1030</v>
+        <v>820</v>
       </c>
     </row>
     <row r="416" spans="1:7">
@@ -13476,7 +12444,7 @@
         <v>657</v>
       </c>
       <c r="G416" t="s">
-        <v>1109</v>
+        <v>821</v>
       </c>
     </row>
     <row r="417" spans="1:7">
@@ -13499,7 +12467,7 @@
         <v>653</v>
       </c>
       <c r="G417" t="s">
-        <v>1072</v>
+        <v>836</v>
       </c>
     </row>
     <row r="418" spans="1:7">
@@ -13522,7 +12490,7 @@
         <v>763</v>
       </c>
       <c r="G418" t="s">
-        <v>1110</v>
+        <v>822</v>
       </c>
     </row>
     <row r="419" spans="1:7">
@@ -13545,7 +12513,7 @@
         <v>699</v>
       </c>
       <c r="G419" t="s">
-        <v>1111</v>
+        <v>825</v>
       </c>
     </row>
     <row r="420" spans="1:7">
@@ -13568,7 +12536,7 @@
         <v>789</v>
       </c>
       <c r="G420" t="s">
-        <v>1112</v>
+        <v>820</v>
       </c>
     </row>
     <row r="421" spans="1:7">
@@ -13591,7 +12559,7 @@
         <v>653</v>
       </c>
       <c r="G421" t="s">
-        <v>1113</v>
+        <v>819</v>
       </c>
     </row>
     <row r="422" spans="1:7">
@@ -13614,7 +12582,7 @@
         <v>640</v>
       </c>
       <c r="G422" t="s">
-        <v>1114</v>
+        <v>825</v>
       </c>
     </row>
     <row r="423" spans="1:7">
@@ -13637,7 +12605,7 @@
         <v>649</v>
       </c>
       <c r="G423" t="s">
-        <v>1065</v>
+        <v>818</v>
       </c>
     </row>
     <row r="424" spans="1:7">
@@ -13660,7 +12628,7 @@
         <v>658</v>
       </c>
       <c r="G424" t="s">
-        <v>936</v>
+        <v>820</v>
       </c>
     </row>
     <row r="425" spans="1:7">
@@ -13683,7 +12651,7 @@
         <v>653</v>
       </c>
       <c r="G425" t="s">
-        <v>1115</v>
+        <v>823</v>
       </c>
     </row>
     <row r="426" spans="1:7">
@@ -13706,7 +12674,7 @@
         <v>766</v>
       </c>
       <c r="G426" t="s">
-        <v>1116</v>
+        <v>822</v>
       </c>
     </row>
     <row r="427" spans="1:7">
@@ -13729,7 +12697,7 @@
         <v>665</v>
       </c>
       <c r="G427" t="s">
-        <v>1117</v>
+        <v>819</v>
       </c>
     </row>
     <row r="428" spans="1:7">
@@ -13752,7 +12720,7 @@
         <v>790</v>
       </c>
       <c r="G428" t="s">
-        <v>1118</v>
+        <v>819</v>
       </c>
     </row>
     <row r="429" spans="1:7">
@@ -13775,7 +12743,7 @@
         <v>657</v>
       </c>
       <c r="G429" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="430" spans="1:7">
@@ -13798,7 +12766,7 @@
         <v>685</v>
       </c>
       <c r="G430" t="s">
-        <v>1094</v>
+        <v>832</v>
       </c>
     </row>
     <row r="431" spans="1:7">
@@ -13821,7 +12789,7 @@
         <v>665</v>
       </c>
       <c r="G431" t="s">
-        <v>878</v>
+        <v>835</v>
       </c>
     </row>
     <row r="432" spans="1:7">
@@ -13844,7 +12812,7 @@
         <v>697</v>
       </c>
       <c r="G432" t="s">
-        <v>1119</v>
+        <v>836</v>
       </c>
     </row>
     <row r="433" spans="1:7">
@@ -13867,7 +12835,7 @@
         <v>705</v>
       </c>
       <c r="G433" t="s">
-        <v>922</v>
+        <v>826</v>
       </c>
     </row>
     <row r="434" spans="1:7">
@@ -13890,7 +12858,7 @@
         <v>727</v>
       </c>
       <c r="G434" t="s">
-        <v>1120</v>
+        <v>819</v>
       </c>
     </row>
     <row r="435" spans="1:7">
@@ -13913,7 +12881,7 @@
         <v>791</v>
       </c>
       <c r="G435" t="s">
-        <v>1121</v>
+        <v>837</v>
       </c>
     </row>
     <row r="436" spans="1:7">
@@ -13936,7 +12904,7 @@
         <v>690</v>
       </c>
       <c r="G436" t="s">
-        <v>837</v>
+        <v>820</v>
       </c>
     </row>
     <row r="437" spans="1:7">
@@ -13959,7 +12927,7 @@
         <v>710</v>
       </c>
       <c r="G437" t="s">
-        <v>1122</v>
+        <v>818</v>
       </c>
     </row>
     <row r="438" spans="1:7">
@@ -13982,7 +12950,7 @@
         <v>649</v>
       </c>
       <c r="G438" t="s">
-        <v>1123</v>
+        <v>836</v>
       </c>
     </row>
     <row r="439" spans="1:7">
@@ -14005,7 +12973,7 @@
         <v>792</v>
       </c>
       <c r="G439" t="s">
-        <v>1124</v>
+        <v>831</v>
       </c>
     </row>
     <row r="440" spans="1:7">
@@ -14028,7 +12996,7 @@
         <v>665</v>
       </c>
       <c r="G440" t="s">
-        <v>874</v>
+        <v>835</v>
       </c>
     </row>
     <row r="441" spans="1:7">
@@ -14074,7 +13042,7 @@
         <v>649</v>
       </c>
       <c r="G442" t="s">
-        <v>874</v>
+        <v>819</v>
       </c>
     </row>
     <row r="443" spans="1:7">
@@ -14097,7 +13065,7 @@
         <v>725</v>
       </c>
       <c r="G443" t="s">
-        <v>1125</v>
+        <v>818</v>
       </c>
     </row>
     <row r="444" spans="1:7">
@@ -14120,7 +13088,7 @@
         <v>793</v>
       </c>
       <c r="G444" t="s">
-        <v>1126</v>
+        <v>818</v>
       </c>
     </row>
     <row r="445" spans="1:7">
@@ -14143,7 +13111,7 @@
         <v>653</v>
       </c>
       <c r="G445" t="s">
-        <v>1127</v>
+        <v>822</v>
       </c>
     </row>
     <row r="446" spans="1:7">
@@ -14166,7 +13134,7 @@
         <v>652</v>
       </c>
       <c r="G446" t="s">
-        <v>1128</v>
+        <v>836</v>
       </c>
     </row>
     <row r="447" spans="1:7">
@@ -14189,7 +13157,7 @@
         <v>794</v>
       </c>
       <c r="G447" t="s">
-        <v>964</v>
+        <v>818</v>
       </c>
     </row>
     <row r="448" spans="1:7">
@@ -14212,7 +13180,7 @@
         <v>710</v>
       </c>
       <c r="G448" t="s">
-        <v>1129</v>
+        <v>824</v>
       </c>
     </row>
     <row r="449" spans="1:7">
@@ -14235,7 +13203,7 @@
         <v>653</v>
       </c>
       <c r="G449" t="s">
-        <v>986</v>
+        <v>831</v>
       </c>
     </row>
     <row r="450" spans="1:7">
@@ -14258,7 +13226,7 @@
         <v>665</v>
       </c>
       <c r="G450" t="s">
-        <v>963</v>
+        <v>836</v>
       </c>
     </row>
     <row r="451" spans="1:7">
@@ -14281,7 +13249,7 @@
         <v>652</v>
       </c>
       <c r="G451" t="s">
-        <v>844</v>
+        <v>820</v>
       </c>
     </row>
     <row r="452" spans="1:7">
@@ -14304,7 +13272,7 @@
         <v>762</v>
       </c>
       <c r="G452" t="s">
-        <v>1130</v>
+        <v>825</v>
       </c>
     </row>
     <row r="453" spans="1:7">
@@ -14327,7 +13295,7 @@
         <v>795</v>
       </c>
       <c r="G453" t="s">
-        <v>1131</v>
+        <v>818</v>
       </c>
     </row>
     <row r="454" spans="1:7">
@@ -14350,7 +13318,7 @@
         <v>665</v>
       </c>
       <c r="G454" t="s">
-        <v>1132</v>
+        <v>831</v>
       </c>
     </row>
     <row r="455" spans="1:7">
@@ -14373,7 +13341,7 @@
         <v>796</v>
       </c>
       <c r="G455" t="s">
-        <v>1133</v>
+        <v>825</v>
       </c>
     </row>
     <row r="456" spans="1:7">
@@ -14396,7 +13364,7 @@
         <v>659</v>
       </c>
       <c r="G456" t="s">
-        <v>934</v>
+        <v>837</v>
       </c>
     </row>
     <row r="457" spans="1:7">
@@ -14419,7 +13387,7 @@
         <v>723</v>
       </c>
       <c r="G457" t="s">
-        <v>1134</v>
+        <v>827</v>
       </c>
     </row>
     <row r="458" spans="1:7">
@@ -14442,7 +13410,7 @@
         <v>702</v>
       </c>
       <c r="G458" t="s">
-        <v>1135</v>
+        <v>833</v>
       </c>
     </row>
     <row r="459" spans="1:7">
@@ -14465,7 +13433,7 @@
         <v>767</v>
       </c>
       <c r="G459" t="s">
-        <v>1136</v>
+        <v>820</v>
       </c>
     </row>
     <row r="460" spans="1:7">
@@ -14488,7 +13456,7 @@
         <v>667</v>
       </c>
       <c r="G460" t="s">
-        <v>1137</v>
+        <v>822</v>
       </c>
     </row>
     <row r="461" spans="1:7">
@@ -14511,7 +13479,7 @@
         <v>657</v>
       </c>
       <c r="G461" t="s">
-        <v>1138</v>
+        <v>833</v>
       </c>
     </row>
     <row r="462" spans="1:7">
@@ -14534,7 +13502,7 @@
         <v>797</v>
       </c>
       <c r="G462" t="s">
-        <v>847</v>
+        <v>824</v>
       </c>
     </row>
     <row r="463" spans="1:7">
@@ -14557,7 +13525,7 @@
         <v>667</v>
       </c>
       <c r="G463" t="s">
-        <v>1137</v>
+        <v>833</v>
       </c>
     </row>
     <row r="464" spans="1:7">
@@ -14580,7 +13548,7 @@
         <v>798</v>
       </c>
       <c r="G464" t="s">
-        <v>1139</v>
+        <v>825</v>
       </c>
     </row>
     <row r="465" spans="1:7">
@@ -14603,7 +13571,7 @@
         <v>653</v>
       </c>
       <c r="G465" t="s">
-        <v>1140</v>
+        <v>825</v>
       </c>
     </row>
     <row r="466" spans="1:7">
@@ -14626,7 +13594,7 @@
         <v>646</v>
       </c>
       <c r="G466" t="s">
-        <v>1141</v>
+        <v>833</v>
       </c>
     </row>
     <row r="467" spans="1:7">
@@ -14649,7 +13617,7 @@
         <v>657</v>
       </c>
       <c r="G467" t="s">
-        <v>1142</v>
+        <v>833</v>
       </c>
     </row>
     <row r="468" spans="1:7">
@@ -14672,7 +13640,7 @@
         <v>649</v>
       </c>
       <c r="G468" t="s">
-        <v>874</v>
+        <v>831</v>
       </c>
     </row>
     <row r="469" spans="1:7">
@@ -14695,7 +13663,7 @@
         <v>710</v>
       </c>
       <c r="G469" t="s">
-        <v>1143</v>
+        <v>825</v>
       </c>
     </row>
     <row r="470" spans="1:7">
@@ -14718,7 +13686,7 @@
         <v>657</v>
       </c>
       <c r="G470" t="s">
-        <v>1144</v>
+        <v>827</v>
       </c>
     </row>
     <row r="471" spans="1:7">
@@ -14741,7 +13709,7 @@
         <v>660</v>
       </c>
       <c r="G471" t="s">
-        <v>1023</v>
+        <v>820</v>
       </c>
     </row>
     <row r="472" spans="1:7">
@@ -14764,7 +13732,7 @@
         <v>799</v>
       </c>
       <c r="G472" t="s">
-        <v>916</v>
+        <v>836</v>
       </c>
     </row>
     <row r="473" spans="1:7">
@@ -14787,7 +13755,7 @@
         <v>705</v>
       </c>
       <c r="G473" t="s">
-        <v>899</v>
+        <v>821</v>
       </c>
     </row>
     <row r="474" spans="1:7">
@@ -14810,7 +13778,7 @@
         <v>702</v>
       </c>
       <c r="G474" t="s">
-        <v>844</v>
+        <v>820</v>
       </c>
     </row>
     <row r="475" spans="1:7">
@@ -14833,7 +13801,7 @@
         <v>774</v>
       </c>
       <c r="G475" t="s">
-        <v>829</v>
+        <v>818</v>
       </c>
     </row>
     <row r="476" spans="1:7">
@@ -14856,7 +13824,7 @@
         <v>697</v>
       </c>
       <c r="G476" t="s">
-        <v>1145</v>
+        <v>819</v>
       </c>
     </row>
     <row r="477" spans="1:7">
@@ -14879,7 +13847,7 @@
         <v>653</v>
       </c>
       <c r="G477" t="s">
-        <v>1146</v>
+        <v>823</v>
       </c>
     </row>
     <row r="478" spans="1:7">
@@ -14902,7 +13870,7 @@
         <v>665</v>
       </c>
       <c r="G478" t="s">
-        <v>1147</v>
+        <v>819</v>
       </c>
     </row>
     <row r="479" spans="1:7">
@@ -14925,7 +13893,7 @@
         <v>800</v>
       </c>
       <c r="G479" t="s">
-        <v>1148</v>
+        <v>823</v>
       </c>
     </row>
     <row r="480" spans="1:7">
@@ -14948,7 +13916,7 @@
         <v>659</v>
       </c>
       <c r="G480" t="s">
-        <v>1149</v>
+        <v>818</v>
       </c>
     </row>
     <row r="481" spans="1:7">
@@ -14971,7 +13939,7 @@
         <v>801</v>
       </c>
       <c r="G481" t="s">
-        <v>829</v>
+        <v>818</v>
       </c>
     </row>
     <row r="482" spans="1:7">
@@ -14994,7 +13962,7 @@
         <v>652</v>
       </c>
       <c r="G482" t="s">
-        <v>1050</v>
+        <v>820</v>
       </c>
     </row>
     <row r="483" spans="1:7">
@@ -15017,7 +13985,7 @@
         <v>659</v>
       </c>
       <c r="G483" t="s">
-        <v>1150</v>
+        <v>833</v>
       </c>
     </row>
     <row r="484" spans="1:7">
@@ -15040,7 +14008,7 @@
         <v>802</v>
       </c>
       <c r="G484" t="s">
-        <v>1151</v>
+        <v>825</v>
       </c>
     </row>
     <row r="485" spans="1:7">
@@ -15063,7 +14031,7 @@
         <v>685</v>
       </c>
       <c r="G485" t="s">
-        <v>948</v>
+        <v>824</v>
       </c>
     </row>
     <row r="486" spans="1:7">
@@ -15086,7 +14054,7 @@
         <v>803</v>
       </c>
       <c r="G486" t="s">
-        <v>847</v>
+        <v>834</v>
       </c>
     </row>
     <row r="487" spans="1:7">
@@ -15109,7 +14077,7 @@
         <v>766</v>
       </c>
       <c r="G487" t="s">
-        <v>867</v>
+        <v>820</v>
       </c>
     </row>
     <row r="488" spans="1:7">
@@ -15132,7 +14100,7 @@
         <v>804</v>
       </c>
       <c r="G488" t="s">
-        <v>1111</v>
+        <v>836</v>
       </c>
     </row>
     <row r="489" spans="1:7">
@@ -15155,7 +14123,7 @@
         <v>744</v>
       </c>
       <c r="G489" t="s">
-        <v>1152</v>
+        <v>832</v>
       </c>
     </row>
     <row r="490" spans="1:7">
@@ -15178,7 +14146,7 @@
         <v>805</v>
       </c>
       <c r="G490" t="s">
-        <v>936</v>
+        <v>833</v>
       </c>
     </row>
     <row r="491" spans="1:7">
@@ -15201,7 +14169,7 @@
         <v>684</v>
       </c>
       <c r="G491" t="s">
-        <v>1049</v>
+        <v>818</v>
       </c>
     </row>
     <row r="492" spans="1:7">
@@ -15224,7 +14192,7 @@
         <v>649</v>
       </c>
       <c r="G492" t="s">
-        <v>1153</v>
+        <v>819</v>
       </c>
     </row>
     <row r="493" spans="1:7">
@@ -15247,7 +14215,7 @@
         <v>691</v>
       </c>
       <c r="G493" t="s">
-        <v>1154</v>
+        <v>823</v>
       </c>
     </row>
     <row r="494" spans="1:7">
@@ -15270,7 +14238,7 @@
         <v>680</v>
       </c>
       <c r="G494" t="s">
-        <v>1155</v>
+        <v>822</v>
       </c>
     </row>
     <row r="495" spans="1:7">
@@ -15293,7 +14261,7 @@
         <v>653</v>
       </c>
       <c r="G495" t="s">
-        <v>899</v>
+        <v>836</v>
       </c>
     </row>
     <row r="496" spans="1:7">
@@ -15316,7 +14284,7 @@
         <v>658</v>
       </c>
       <c r="G496" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="497" spans="1:7">
@@ -15339,7 +14307,7 @@
         <v>655</v>
       </c>
       <c r="G497" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="498" spans="1:7">
@@ -15362,7 +14330,7 @@
         <v>657</v>
       </c>
       <c r="G498" t="s">
-        <v>1156</v>
+        <v>821</v>
       </c>
     </row>
     <row r="499" spans="1:7">
@@ -15385,7 +14353,7 @@
         <v>705</v>
       </c>
       <c r="G499" t="s">
-        <v>1157</v>
+        <v>818</v>
       </c>
     </row>
     <row r="500" spans="1:7">
@@ -15408,7 +14376,7 @@
         <v>641</v>
       </c>
       <c r="G500" t="s">
-        <v>1137</v>
+        <v>836</v>
       </c>
     </row>
     <row r="501" spans="1:7">
@@ -15431,7 +14399,7 @@
         <v>730</v>
       </c>
       <c r="G501" t="s">
-        <v>1158</v>
+        <v>836</v>
       </c>
     </row>
     <row r="502" spans="1:7">
@@ -15454,7 +14422,7 @@
         <v>730</v>
       </c>
       <c r="G502" t="s">
-        <v>1159</v>
+        <v>828</v>
       </c>
     </row>
     <row r="503" spans="1:7">
@@ -15477,7 +14445,7 @@
         <v>806</v>
       </c>
       <c r="G503" t="s">
-        <v>1160</v>
+        <v>819</v>
       </c>
     </row>
     <row r="504" spans="1:7">
@@ -15500,7 +14468,7 @@
         <v>653</v>
       </c>
       <c r="G504" t="s">
-        <v>1161</v>
+        <v>823</v>
       </c>
     </row>
     <row r="505" spans="1:7">
@@ -15523,7 +14491,7 @@
         <v>689</v>
       </c>
       <c r="G505" t="s">
-        <v>899</v>
+        <v>832</v>
       </c>
     </row>
     <row r="506" spans="1:7">
@@ -15546,7 +14514,7 @@
         <v>648</v>
       </c>
       <c r="G506" t="s">
-        <v>1162</v>
+        <v>827</v>
       </c>
     </row>
     <row r="507" spans="1:7">
@@ -15569,7 +14537,7 @@
         <v>807</v>
       </c>
       <c r="G507" t="s">
-        <v>1163</v>
+        <v>827</v>
       </c>
     </row>
     <row r="508" spans="1:7">
@@ -15592,7 +14560,7 @@
         <v>646</v>
       </c>
       <c r="G508" t="s">
-        <v>1164</v>
+        <v>824</v>
       </c>
     </row>
     <row r="509" spans="1:7">
@@ -15612,7 +14580,7 @@
         <v>723</v>
       </c>
       <c r="G509" t="s">
-        <v>1165</v>
+        <v>819</v>
       </c>
     </row>
     <row r="510" spans="1:7">
@@ -15635,7 +14603,7 @@
         <v>653</v>
       </c>
       <c r="G510" t="s">
-        <v>1166</v>
+        <v>819</v>
       </c>
     </row>
     <row r="511" spans="1:7">
@@ -15658,7 +14626,7 @@
         <v>773</v>
       </c>
       <c r="G511" t="s">
-        <v>877</v>
+        <v>836</v>
       </c>
     </row>
     <row r="512" spans="1:7">
@@ -15681,7 +14649,7 @@
         <v>655</v>
       </c>
       <c r="G512" t="s">
-        <v>878</v>
+        <v>822</v>
       </c>
     </row>
     <row r="513" spans="1:7">
@@ -15704,7 +14672,7 @@
         <v>702</v>
       </c>
       <c r="G513" t="s">
-        <v>847</v>
+        <v>833</v>
       </c>
     </row>
     <row r="514" spans="1:7">
@@ -15727,7 +14695,7 @@
         <v>641</v>
       </c>
       <c r="G514" t="s">
-        <v>873</v>
+        <v>822</v>
       </c>
     </row>
     <row r="515" spans="1:7">
@@ -15750,7 +14718,7 @@
         <v>702</v>
       </c>
       <c r="G515" t="s">
-        <v>1167</v>
+        <v>836</v>
       </c>
     </row>
     <row r="516" spans="1:7">
@@ -15773,7 +14741,7 @@
         <v>702</v>
       </c>
       <c r="G516" t="s">
-        <v>1168</v>
+        <v>824</v>
       </c>
     </row>
     <row r="517" spans="1:7">
@@ -15796,7 +14764,7 @@
         <v>655</v>
       </c>
       <c r="G517" t="s">
-        <v>1169</v>
+        <v>824</v>
       </c>
     </row>
     <row r="518" spans="1:7">
@@ -15819,7 +14787,7 @@
         <v>652</v>
       </c>
       <c r="G518" t="s">
-        <v>1170</v>
+        <v>820</v>
       </c>
     </row>
     <row r="519" spans="1:7">
@@ -15842,7 +14810,7 @@
         <v>808</v>
       </c>
       <c r="G519" t="s">
-        <v>1171</v>
+        <v>824</v>
       </c>
     </row>
     <row r="520" spans="1:7">
@@ -15865,7 +14833,7 @@
         <v>700</v>
       </c>
       <c r="G520" t="s">
-        <v>878</v>
+        <v>822</v>
       </c>
     </row>
     <row r="521" spans="1:7">
@@ -15888,7 +14856,7 @@
         <v>700</v>
       </c>
       <c r="G521" t="s">
-        <v>1172</v>
+        <v>822</v>
       </c>
     </row>
     <row r="522" spans="1:7">
@@ -15911,7 +14879,7 @@
         <v>652</v>
       </c>
       <c r="G522" t="s">
-        <v>1173</v>
+        <v>819</v>
       </c>
     </row>
     <row r="523" spans="1:7">
@@ -15934,7 +14902,7 @@
         <v>702</v>
       </c>
       <c r="G523" t="s">
-        <v>1174</v>
+        <v>824</v>
       </c>
     </row>
     <row r="524" spans="1:7">
@@ -15957,7 +14925,7 @@
         <v>635</v>
       </c>
       <c r="G524" t="s">
-        <v>1175</v>
+        <v>823</v>
       </c>
     </row>
     <row r="525" spans="1:7">
@@ -15977,7 +14945,7 @@
         <v>625</v>
       </c>
       <c r="G525" t="s">
-        <v>965</v>
+        <v>835</v>
       </c>
     </row>
     <row r="526" spans="1:7">
@@ -16000,7 +14968,7 @@
         <v>639</v>
       </c>
       <c r="G526" t="s">
-        <v>1176</v>
+        <v>825</v>
       </c>
     </row>
     <row r="527" spans="1:7">
@@ -16023,7 +14991,7 @@
         <v>710</v>
       </c>
       <c r="G527" t="s">
-        <v>968</v>
+        <v>840</v>
       </c>
     </row>
     <row r="528" spans="1:7">
@@ -16046,7 +15014,7 @@
         <v>642</v>
       </c>
       <c r="G528" t="s">
-        <v>1177</v>
+        <v>833</v>
       </c>
     </row>
     <row r="529" spans="1:7">
@@ -16069,7 +15037,7 @@
         <v>638</v>
       </c>
       <c r="G529" t="s">
-        <v>1178</v>
+        <v>837</v>
       </c>
     </row>
     <row r="530" spans="1:7">
@@ -16115,7 +15083,7 @@
         <v>640</v>
       </c>
       <c r="G531" t="s">
-        <v>873</v>
+        <v>822</v>
       </c>
     </row>
     <row r="532" spans="1:7">
@@ -16138,7 +15106,7 @@
         <v>668</v>
       </c>
       <c r="G532" t="s">
-        <v>849</v>
+        <v>822</v>
       </c>
     </row>
     <row r="533" spans="1:7">
@@ -16161,7 +15129,7 @@
         <v>677</v>
       </c>
       <c r="G533" t="s">
-        <v>873</v>
+        <v>822</v>
       </c>
     </row>
     <row r="534" spans="1:7">
@@ -16207,7 +15175,7 @@
         <v>809</v>
       </c>
       <c r="G535" t="s">
-        <v>1155</v>
+        <v>822</v>
       </c>
     </row>
     <row r="536" spans="1:7">
@@ -16230,7 +15198,7 @@
         <v>699</v>
       </c>
       <c r="G536" t="s">
-        <v>1179</v>
+        <v>833</v>
       </c>
     </row>
     <row r="537" spans="1:7">
@@ -16253,7 +15221,7 @@
         <v>674</v>
       </c>
       <c r="G537" t="s">
-        <v>1180</v>
+        <v>827</v>
       </c>
     </row>
     <row r="538" spans="1:7">
@@ -16276,7 +15244,7 @@
         <v>659</v>
       </c>
       <c r="G538" t="s">
-        <v>1181</v>
+        <v>839</v>
       </c>
     </row>
     <row r="539" spans="1:7">
@@ -16299,7 +15267,7 @@
         <v>640</v>
       </c>
       <c r="G539" t="s">
-        <v>849</v>
+        <v>825</v>
       </c>
     </row>
     <row r="540" spans="1:7">
@@ -16322,7 +15290,7 @@
         <v>649</v>
       </c>
       <c r="G540" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
     </row>
     <row r="541" spans="1:7">
@@ -16345,7 +15313,7 @@
         <v>810</v>
       </c>
       <c r="G541" t="s">
-        <v>1182</v>
+        <v>824</v>
       </c>
     </row>
     <row r="542" spans="1:7">
@@ -16368,7 +15336,7 @@
         <v>811</v>
       </c>
       <c r="G542" t="s">
-        <v>1183</v>
+        <v>825</v>
       </c>
     </row>
     <row r="543" spans="1:7">
@@ -16391,7 +15359,7 @@
         <v>702</v>
       </c>
       <c r="G543" t="s">
-        <v>965</v>
+        <v>835</v>
       </c>
     </row>
     <row r="544" spans="1:7">
@@ -16414,7 +15382,7 @@
         <v>711</v>
       </c>
       <c r="G544" t="s">
-        <v>1184</v>
+        <v>828</v>
       </c>
     </row>
     <row r="545" spans="1:7">
@@ -16437,7 +15405,7 @@
         <v>812</v>
       </c>
       <c r="G545" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
   </sheetData>

--- a/中药材数据/中药材分类标签列表/中药材分类多维标签表.xlsx
+++ b/中药材数据/中药材分类标签列表/中药材分类多维标签表.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3807" uniqueCount="1185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3804" uniqueCount="983">
   <si>
     <t>药材名称</t>
   </si>
@@ -22,7 +22,7 @@
     <t>功效分类</t>
   </si>
   <si>
-    <t>药性 (四气)</t>
+    <t>药性（四气）</t>
   </si>
   <si>
     <t>五味</t>
@@ -34,7 +34,7 @@
     <t>归经</t>
   </si>
   <si>
-    <t>详细功效 (21类)</t>
+    <t>具体功效</t>
   </si>
   <si>
     <t>阿魏</t>
@@ -1753,13 +1753,13 @@
     <t>凉</t>
   </si>
   <si>
-    <t>微温</t>
+    <t>微温、温</t>
   </si>
   <si>
     <t>寒</t>
   </si>
   <si>
-    <t>微寒</t>
+    <t>微寒、寒</t>
   </si>
   <si>
     <t>热</t>
@@ -1777,10 +1777,10 @@
     <t>平、温</t>
   </si>
   <si>
-    <t>微寒、凉</t>
-  </si>
-  <si>
-    <t>平、微温</t>
+    <t>微寒、寒、凉</t>
+  </si>
+  <si>
+    <t>平、微温、温</t>
   </si>
   <si>
     <t>辛</t>
@@ -2206,18 +2206,18 @@
     <t>心、肝、小肠</t>
   </si>
   <si>
+    <t>肝、肾、肺</t>
+  </si>
+  <si>
+    <t>肾、肺、大肠</t>
+  </si>
+  <si>
+    <t>小肠、膀胱、肝</t>
+  </si>
+  <si>
     <t>心、肾</t>
   </si>
   <si>
-    <t>肝、肾、肺</t>
-  </si>
-  <si>
-    <t>肾、肺、大肠</t>
-  </si>
-  <si>
-    <t>小肠、膀胱、肝</t>
-  </si>
-  <si>
     <t>肺、胃、心、肾</t>
   </si>
   <si>
@@ -2455,1120 +2455,514 @@
     <t>脾、肾、肺、膀胱</t>
   </si>
   <si>
-    <t>健脾养胃、增强免疫、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气养血、滋阴润燥、润肺止咳、增强免疫、泻下通便</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、补气固表</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、补气固表、散寒止痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>清热降火、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、增强免疫、活血化瘀</t>
-  </si>
-  <si>
-    <t>收敛止血</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、疏肝理气、祛风湿痛</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、疏肝理气</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、滋阴养颜、补气固表、健脾升阳、增强免疫、疏肝理气、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、散寒止痛</t>
-  </si>
-  <si>
-    <t>润肺止咳、利水渗湿、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、养心安神、润肺止咳、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、增强免疫、利水渗湿</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、活血化瘀、祛风湿痛</t>
+    <t>消食导滞</t>
+  </si>
+  <si>
+    <t>化痰止咳、宁血止血、扶正补虚</t>
+  </si>
+  <si>
+    <t>宁心安神</t>
+  </si>
+  <si>
+    <t>温阳散寒、宁血止血</t>
+  </si>
+  <si>
+    <t>活血化瘀、祛风湿痛、清热解毒</t>
+  </si>
+  <si>
+    <t>驱虫杀虫、消食导滞、清热解毒、宁血止血</t>
+  </si>
+  <si>
+    <t>活血化瘀</t>
+  </si>
+  <si>
+    <t>宁血止血</t>
+  </si>
+  <si>
+    <t>扶正补虚</t>
+  </si>
+  <si>
+    <t>化痰止咳</t>
+  </si>
+  <si>
+    <t>活血化瘀、温阳散寒</t>
+  </si>
+  <si>
+    <t>清热解毒</t>
+  </si>
+  <si>
+    <t>宁心安神、疏肝理气、化痰止咳</t>
+  </si>
+  <si>
+    <t>宁血止血、扶正补虚</t>
+  </si>
+  <si>
+    <t>活血化瘀、宁血止血</t>
+  </si>
+  <si>
+    <t>疏肝理气</t>
   </si>
   <si>
     <t>利水渗湿</t>
   </si>
   <si>
-    <t>滋阴润燥、清热降火、健脾升阳、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养肝明目、清热降火、润肺止咳、疏肝理气、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、增强免疫、散寒止痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、润肺止咳、活血化瘀</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养心安神、补气固表、活血化瘀</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>润肺止咳、健脾升阳</t>
-  </si>
-  <si>
-    <t>增强免疫、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、补气固表、增强免疫、散寒止痛、疏肝理气</t>
-  </si>
-  <si>
-    <t>散寒止痛、祛风湿痛</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、散寒止痛、利水渗湿</t>
-  </si>
-  <si>
-    <t>滋阴润燥、散寒止痛</t>
-  </si>
-  <si>
-    <t>清热降火、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表</t>
-  </si>
-  <si>
-    <t>活血化瘀</t>
-  </si>
-  <si>
-    <t>清热降火、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、疏肝理气、活血化瘀、泻下通便</t>
-  </si>
-  <si>
-    <t>健脾养胃</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养肝明目、润肺止咳、补气固表</t>
-  </si>
-  <si>
-    <t>补气固表、散寒止痛、活血化瘀</t>
-  </si>
-  <si>
-    <t>清热降火、养心安神、润肺止咳、补气固表、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、散寒止痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、补气固表、健脾升阳、增强免疫、疏肝理气、泻下通便、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、补气固表、增强免疫、宁心安神、祛风湿痛</t>
-  </si>
-  <si>
-    <t>补气固表、健脾升阳、散寒止痛、利水渗湿、疏肝理气、泻下通便、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、泻下通便、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、润肺止咳、补气固表、健脾升阳、利水渗湿、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>清热降火、增强免疫、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、增强免疫</t>
-  </si>
-  <si>
-    <t>清热降火、利水渗湿、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、增强免疫、疏肝理气</t>
-  </si>
-  <si>
-    <t>散寒止痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>散寒止痛</t>
-  </si>
-  <si>
-    <t>养肝明目、补气固表、健脾升阳、增强免疫、散寒止痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、养肝明目、清热降火、润肺止咳、散寒止痛、补虚暖身、利水渗湿、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>补气固表、健脾升阳、散寒止痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、润肺止咳、疏肝理气</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养肝明目、养心安神、健脾升阳、散寒止痛</t>
-  </si>
-  <si>
-    <t>润肺止咳</t>
+    <t>驱虫杀虫、宁心安神、化痰止咳、扶正补虚</t>
+  </si>
+  <si>
+    <t>宁心安神、扶正补虚</t>
+  </si>
+  <si>
+    <t>温阳散寒</t>
+  </si>
+  <si>
+    <t>泻下通便</t>
+  </si>
+  <si>
+    <t>温阳散寒、疏肝理气</t>
+  </si>
+  <si>
+    <t>活血化瘀、清热解毒</t>
+  </si>
+  <si>
+    <t>祛风湿痛、清热解毒</t>
+  </si>
+  <si>
+    <t>活血化瘀、泻下通便、清热解毒</t>
+  </si>
+  <si>
+    <t>化痰止咳、发散表邪、宁血止血</t>
+  </si>
+  <si>
+    <t>宁血止血、发散表邪、扶正补虚</t>
+  </si>
+  <si>
+    <t>发散表邪</t>
+  </si>
+  <si>
+    <t>泻下通便、消食导滞、扶正补虚</t>
+  </si>
+  <si>
+    <t>驱虫杀虫、发散表邪、消食导滞</t>
+  </si>
+  <si>
+    <t>活血化瘀、清热解毒、宁血止血</t>
+  </si>
+  <si>
+    <t>利水渗湿、清热解毒</t>
+  </si>
+  <si>
+    <t>收敛固涩、化痰止咳、宁血止血</t>
   </si>
   <si>
     <t>祛风湿痛</t>
   </si>
   <si>
-    <t>补气养血、活血化瘀</t>
-  </si>
-  <si>
-    <t>散寒止痛、疏肝理气、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火</t>
-  </si>
-  <si>
-    <t>润肺止咳、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养肝明目、清热降火、润肺止咳、补气固表、增强免疫、疏肝理气、泻下通便</t>
-  </si>
-  <si>
-    <t>增强免疫、散寒止痛、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、补气固表、增强免疫、疏肝理气、泻下通便</t>
-  </si>
-  <si>
-    <t>润肺止咳、散寒止痛、活血化瘀、祛风湿痛</t>
+    <t>祛风湿痛、宁血止血</t>
+  </si>
+  <si>
+    <t>发散表邪、温阳散寒</t>
+  </si>
+  <si>
+    <t>利水渗湿、宁血止血</t>
+  </si>
+  <si>
+    <t>宁血止血、消食导滞、疏肝理气、化痰止咳</t>
+  </si>
+  <si>
+    <t>祛风湿痛、发散表邪</t>
+  </si>
+  <si>
+    <t>活血化瘀、清热解毒、扶正补虚</t>
+  </si>
+  <si>
+    <t>驱虫杀虫、疏肝理气</t>
+  </si>
+  <si>
+    <t>泻下通便、疏肝理气、宁血止血</t>
+  </si>
+  <si>
+    <t>活血化瘀、祛风湿痛、化痰止咳</t>
   </si>
   <si>
     <t>收敛固涩</t>
   </si>
   <si>
-    <t>补气固表、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、润肺止咳、补气固表、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、补气固表、利水渗湿、疏肝理气、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、补气固表、健脾升阳、利水渗湿、疏肝理气</t>
-  </si>
-  <si>
-    <t>养肝明目、补气固表、健脾升阳</t>
-  </si>
-  <si>
-    <t>润肺止咳、利水渗湿</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气固表、健脾升阳、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>增强免疫、散寒止痛</t>
-  </si>
-  <si>
-    <t>疏肝理气</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、增强免疫、散寒止痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、散寒止痛、活血化瘀</t>
-  </si>
-  <si>
-    <t>补虚暖身、利水渗湿</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、增强免疫</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、利水渗湿、活血化瘀、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥</t>
-  </si>
-  <si>
-    <t>润肺止咳、温经养血、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、养心安神、补气固表、利水渗湿</t>
-  </si>
-  <si>
-    <t>活血化瘀、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、补气固表、散寒止痛</t>
-  </si>
-  <si>
-    <t>补气养血、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、利水渗湿</t>
-  </si>
-  <si>
-    <t>养肝明目、补气固表</t>
-  </si>
-  <si>
-    <t>补气固表、泻下通便、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>补气固表、温经养血、散寒止痛、活血化瘀</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、祛风湿痛</t>
-  </si>
-  <si>
-    <t>补气养血、滋阴润燥、清热降火、补气固表、健脾升阳</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气固表、健脾升阳、利水渗湿</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、补气固表、增强免疫、散寒止痛、疏肝理气、活血化瘀、泻下通便</t>
-  </si>
-  <si>
-    <t>增强免疫、补虚暖身</t>
-  </si>
-  <si>
-    <t>补气养血、补气固表、增强免疫、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、润肺止咳、活血化瘀、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、泻下通便、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>利水渗湿、疏肝理气</t>
-  </si>
-  <si>
-    <t>补气固表</t>
-  </si>
-  <si>
-    <t>健脾养胃、增强免疫、泻下通便</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、补气固表、泻下通便、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、补气固表、增强免疫、温经养血、散寒止痛、利水渗湿、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、补气固表、利水渗湿、疏肝理气</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、泻下通便、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养心安神、补气固表、健脾升阳、利水渗湿</t>
-  </si>
-  <si>
-    <t>健脾养胃、润肺止咳、散寒止痛、疏肝理气</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养肝明目、清热降火、润肺止咳、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气固表、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、散寒止痛、宁心安神、活血化瘀、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、润肺止咳、补气固表、增强免疫、散寒止痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、温经养血、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、增强免疫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、散寒止痛、疏肝理气</t>
-  </si>
-  <si>
-    <t>清热降火、养心安神、补气固表、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、润肺止咳</t>
-  </si>
-  <si>
-    <t>增强免疫、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、养心安神、润肺止咳、增强免疫、补虚暖身、祛风湿痛</t>
-  </si>
-  <si>
-    <t>养肝明目</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、利水渗湿</t>
-  </si>
-  <si>
-    <t>健脾养胃、润肺止咳、增强免疫</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气养血、滋阴润燥、养心安神、滋阴养颜、增强免疫、补虚暖身、祛风湿痛</t>
-  </si>
-  <si>
-    <t>补气养血、滋阴润燥、清热降火、养心安神、润肺止咳、补气固表、增强免疫</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气固表、增强免疫</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、补气固表、健脾升阳</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、增强免疫、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、润肺止咳、散寒止痛、补虚暖身、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养肝明目、清热降火、养心安神、散寒止痛、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、利水渗湿、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、利水渗湿、活血化瘀、泻下通便</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、散寒止痛、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、补气固表、疏肝理气、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、泻下通便</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养肝明目、清热降火、补气固表、增强免疫、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、补气固表、疏肝理气</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、散寒止痛、疏肝理气、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、养肝明目、增强免疫、疏肝理气、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、散寒止痛、利水渗湿、疏肝理气、活血化瘀、祛风湿痛</t>
+    <t>发散表邪、疏肝理气</t>
+  </si>
+  <si>
+    <t>疏肝理气、化痰止咳</t>
+  </si>
+  <si>
+    <t>宁心安神、清热解毒</t>
+  </si>
+  <si>
+    <t>收敛固涩、活血化瘀、清热解毒、宁血止血</t>
+  </si>
+  <si>
+    <t>宁心安神、利水渗湿、清热解毒</t>
   </si>
   <si>
     <t>活血化瘀、祛风湿痛</t>
   </si>
   <si>
-    <t>健脾升阳</t>
-  </si>
-  <si>
-    <t>养心安神</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养心安神、疏肝理气、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、补气固表、利水渗湿、活血化瘀</t>
-  </si>
-  <si>
-    <t>滋阴润燥、补气固表、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、散寒止痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气养血、滋阴润燥、清热降火、润肺止咳、补气固表、健脾升阳、增强免疫、散寒止痛、补虚暖身、疏肝理气、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、补气固表、散寒止痛、活血化瘀、泻下通便</t>
-  </si>
-  <si>
-    <t>养心安神、润肺止咳、散寒止痛、疏肝理气、活血化瘀、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、养心安神、补气固表、散寒止痛、泻下通便、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、补气固表、疏肝理气、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、健脾升阳、利水渗湿、疏肝理气、泻下通便</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、健脾升阳、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、养心安神、润肺止咳、补气固表、增强免疫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、散寒止痛、利水渗湿、活血化瘀、泻下通便、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气养血、清热降火、养心安神、润肺止咳、补气固表、健脾升阳、增强免疫、散寒止痛、活血化瘀、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>散寒止痛、疏肝理气</t>
-  </si>
-  <si>
-    <t>滋阴润燥、散寒止痛、补虚暖身、疏肝理气</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、散寒止痛、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、润肺止咳、利水渗湿、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>补气养血、滋阴润燥、清热降火、健脾升阳、泻下通便</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养心安神、润肺止咳、补气固表、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、补气固表、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、补气固表、健脾升阳、活血化瘀</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、增强免疫、散寒止痛、利水渗湿、活血化瘀、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、泻下通便</t>
-  </si>
-  <si>
-    <t>补气养血、滋阴润燥、清热降火、祛风湿痛</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、补气固表</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、活血化瘀</t>
+    <t>驱虫杀虫、宁血止血</t>
+  </si>
+  <si>
+    <t>泻下通便、疏肝理气</t>
+  </si>
+  <si>
+    <t>发散表邪、清热解毒</t>
+  </si>
+  <si>
+    <t>宁心安神、宁血止血、发散表邪</t>
+  </si>
+  <si>
+    <t>清热解毒、扶正补虚</t>
+  </si>
+  <si>
+    <t>泻下通便、宁血止血</t>
+  </si>
+  <si>
+    <t>活血化瘀、祛风湿痛、发散表邪、清热解毒</t>
+  </si>
+  <si>
+    <t>清热解毒、宁血止血</t>
+  </si>
+  <si>
+    <t>收敛固涩、发散表邪、宁血止血</t>
+  </si>
+  <si>
+    <t>发散表邪、温阳散寒、宁血止血</t>
+  </si>
+  <si>
+    <t>发散表邪、扶正补虚</t>
+  </si>
+  <si>
+    <t>宁心安神、利水渗湿、发散表邪</t>
+  </si>
+  <si>
+    <t>活血化瘀、清热解毒、宁心安神、祛风湿痛、宁血止血</t>
+  </si>
+  <si>
+    <t>活血化瘀、扶正补虚</t>
+  </si>
+  <si>
+    <t>收敛固涩、祛风湿痛</t>
+  </si>
+  <si>
+    <t>收敛固涩、消食导滞</t>
+  </si>
+  <si>
+    <t>活血化瘀、清热解毒、化痰止咳、疏肝理气</t>
+  </si>
+  <si>
+    <t>宁心安神、发散表邪、温阳散寒、扶正补虚</t>
+  </si>
+  <si>
+    <t>发散表邪、宁血止血</t>
+  </si>
+  <si>
+    <t>发散表邪、清热解毒、宁血止血</t>
+  </si>
+  <si>
+    <t>宁心安神、温阳散寒、扶正补虚</t>
+  </si>
+  <si>
+    <t>宁血止血、宁心安神、扶正补虚</t>
+  </si>
+  <si>
+    <t>宁心安神、清热解毒、宁血止血</t>
+  </si>
+  <si>
+    <t>宁血止血、化痰止咳</t>
+  </si>
+  <si>
+    <t>清热解毒、化痰止咳</t>
+  </si>
+  <si>
+    <t>收敛固涩、清热解毒、疏肝理气</t>
+  </si>
+  <si>
+    <t>收敛固涩、宁血止血</t>
+  </si>
+  <si>
+    <t>清热解毒、宁心安神、疏肝理气、化痰止咳</t>
+  </si>
+  <si>
+    <t>温阳散寒、化痰止咳</t>
+  </si>
+  <si>
+    <t>活血化瘀、祛风湿痛、疏肝理气</t>
+  </si>
+  <si>
+    <t>活血化瘀、宁心安神、疏肝理气</t>
+  </si>
+  <si>
+    <t>收敛固涩、扶正补虚</t>
+  </si>
+  <si>
+    <t>化痰止咳、活血化瘀、温阳散寒、扶正补虚</t>
+  </si>
+  <si>
+    <t>泻下通便、清热解毒</t>
+  </si>
+  <si>
+    <t>活血化瘀、宁心安神、驱虫杀虫、疏肝理气</t>
+  </si>
+  <si>
+    <t>收敛固涩、疏肝理气</t>
+  </si>
+  <si>
+    <t>化痰止咳、宁心安神、清热解毒、扶正补虚</t>
+  </si>
+  <si>
+    <t>活血化瘀、清热解毒、收敛固涩、祛风湿痛、宁血止血、化痰止咳</t>
+  </si>
+  <si>
+    <t>活血化瘀、消食导滞、清热解毒、扶正补虚、祛风湿痛、温阳散寒</t>
+  </si>
+  <si>
+    <t>活血化瘀、疏肝理气</t>
+  </si>
+  <si>
+    <t>收敛固涩、泻下通便、扶正补虚</t>
+  </si>
+  <si>
+    <t>活血化瘀、祛风湿痛、清热解毒、宁血止血</t>
+  </si>
+  <si>
+    <t>活血化瘀、祛风湿痛、扶正补虚</t>
   </si>
   <si>
     <t>驱虫杀虫</t>
   </si>
   <si>
-    <t>健脾养胃、健脾升阳、散寒止痛、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、散寒止痛、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、补气固表、泻下通便</t>
-  </si>
-  <si>
-    <t>补气固表、散寒止痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、散寒止痛、祛风湿痛</t>
-  </si>
-  <si>
-    <t>增强免疫、利水渗湿</t>
-  </si>
-  <si>
-    <t>补气固表、增强免疫</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、增强免疫、疏肝理气、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、增强免疫、宁心安神、泻下通便</t>
-  </si>
-  <si>
-    <t>利水渗湿、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、养心安神、补气固表、增强免疫、温经养血、补虚暖身、利水渗湿</t>
-  </si>
-  <si>
-    <t>滋阴润燥、补气固表</t>
-  </si>
-  <si>
-    <t>健脾养胃、养心安神</t>
-  </si>
-  <si>
-    <t>健脾养胃、润肺止咳、补气固表、活血化瘀</t>
-  </si>
-  <si>
-    <t>清热降火、养心安神、补气固表、健脾升阳</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、健脾升阳、利水渗湿、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、润肺止咳、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气养血、养心安神、润肺止咳、散寒止痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、补气固表、增强免疫、散寒止痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、散寒止痛、宁心安神、泻下通便</t>
-  </si>
-  <si>
-    <t>温经养血、补虚暖身、活血化瘀</t>
-  </si>
-  <si>
-    <t>养肝明目、养心安神、补气固表</t>
-  </si>
-  <si>
-    <t>散寒止痛、补虚暖身、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、增强免疫、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、散寒止痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、润肺止咳、补气固表、健脾升阳</t>
-  </si>
-  <si>
-    <t>清热降火、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾升阳、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>拔毒生肌</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、润肺止咳、温经养血、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、润肺止咳、增强免疫、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、润肺止咳、补气固表</t>
-  </si>
-  <si>
-    <t>健脾养胃、健脾升阳、增强免疫</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、补气固表、增强免疫、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>养心安神、活血化瘀</t>
-  </si>
-  <si>
-    <t>补气固表、增强免疫、活血化瘀</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、补气固表、增强免疫、利水渗湿、疏肝理气</t>
-  </si>
-  <si>
-    <t>清热降火、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>补气固表、利水渗湿、泻下通便</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、补气固表、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、宁心安神</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、润肺止咳、补气固表、增强免疫、利水渗湿、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、健脾升阳、增强免疫、利水渗湿、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>增强免疫、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、散寒止痛</t>
-  </si>
-  <si>
-    <t>清热降火、补气固表</t>
-  </si>
-  <si>
-    <t>滋阴润燥、健脾升阳、散寒止痛、疏肝理气、活血化瘀</t>
-  </si>
-  <si>
-    <t>增强免疫</t>
-  </si>
-  <si>
-    <t>健脾养胃、增强免疫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、补气固表</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、增强免疫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、利水渗湿</t>
-  </si>
-  <si>
-    <t>健脾养胃、养肝明目、补气固表、利水渗湿</t>
-  </si>
-  <si>
-    <t>补气固表、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气固表、散寒止痛、利水渗湿、疏肝理气、泻下通便、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>润肺止咳、散寒止痛、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、养心安神、滋阴养颜、补气固表、活血化瘀</t>
-  </si>
-  <si>
-    <t>润肺止咳、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、利水渗湿</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、润肺止咳</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、补气固表、疏肝理气、祛风湿痛</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、润肺止咳、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>平肝息风</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、增强免疫、泻下通便、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、散寒止痛、活血化瘀</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、补气固表、散寒止痛、补虚暖身、利水渗湿、疏肝理气、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、养心安神、润肺止咳、补气固表、增强免疫、疏肝理气、泻下通便</t>
-  </si>
-  <si>
-    <t>泻下通便、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>清热降火、泻下通便、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、养心安神、补气固表、散寒止痛</t>
-  </si>
-  <si>
-    <t>祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养肝明目、清热降火、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、健脾升阳、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>补虚暖身</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、利水渗湿、疏肝理气、活血化瘀、泻下通便、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、泻下通便</t>
-  </si>
-  <si>
-    <t>润肺止咳、增强免疫、散寒止痛、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、宁心安神、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>润肺止咳、利水渗湿、疏肝理气、祛风湿痛</t>
-  </si>
-  <si>
-    <t>开窍醒神</t>
-  </si>
-  <si>
-    <t>健脾升阳、补虚暖身、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>补气固表、活血化瘀</t>
-  </si>
-  <si>
-    <t>利水渗湿、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、润肺止咳、补气固表、健脾升阳、散寒止痛、疏肝理气</t>
-  </si>
-  <si>
-    <t>增强免疫、散寒止痛、利水渗湿、活血化瘀</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、活血化瘀、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>养肝明目、润肺止咳、健脾升阳、散寒止痛、祛风湿痛</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、润肺止咳、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、散寒止痛、疏肝理气、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>养心安神、补气固表</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火</t>
-  </si>
-  <si>
-    <t>泻下通便</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、活血化瘀</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养肝明目、清热降火、养心安神、润肺止咳、补气固表、健脾升阳、散寒止痛</t>
-  </si>
-  <si>
-    <t>补气养血、滋阴润燥、清热降火、润肺止咳、补气固表、健脾升阳、增强免疫、补虚暖身、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、利水渗湿、疏肝理气、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>增强免疫、散寒止痛、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、润肺止咳、散寒止痛、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、增强免疫、散寒止痛</t>
-  </si>
-  <si>
-    <t>养肝明目、养心安神、补气固表、增强免疫、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、增强免疫、疏肝理气、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、润肺止咳、补气固表、疏肝理气、祛风湿痛</t>
-  </si>
-  <si>
-    <t>散寒止痛、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气固表、增强免疫、散寒止痛</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、宁心安神</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、泻下通便</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、润肺止咳、增强免疫、利水渗湿</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、散寒止痛、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、润肺止咳、健脾升阳、散寒止痛、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、利水渗湿、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、散寒止痛、利水渗湿、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>补气养血、滋阴润燥、养肝明目、清热降火、养心安神、增强免疫、散寒止痛、补虚暖身</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、补气固表、祛风湿痛</t>
-  </si>
-  <si>
-    <t>增强免疫、活血化瘀</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、补气固表、活血化瘀</t>
-  </si>
-  <si>
-    <t>增强免疫、散寒止痛、活血化瘀</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、润肺止咳、利水渗湿、活血化瘀</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、润肺止咳、健脾升阳、疏肝理气、泻下通便</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、补气固表、增强免疫、散寒止痛、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气固表、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>补气养血、养肝明目、清热降火、利水渗湿、泻下通便</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、润肺止咳、利水渗湿、泻下通便、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、润肺止咳、补气固表</t>
-  </si>
-  <si>
-    <t>养肝明目、散寒止痛、活血化瘀</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、补气固表、健脾升阳、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、润肺止咳、补气固表、散寒止痛、利水渗湿、疏肝理气、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、活血化瘀、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>清热降火、疏肝理气、活血化瘀、祛风湿痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、补气固表、疏肝理气、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、补气固表、活血化瘀</t>
-  </si>
-  <si>
-    <t>润肺止咳、增强免疫、散寒止痛、活血化瘀</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、补气固表、散寒止痛、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、润肺止咳、补气固表、散寒止痛、疏肝理气</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、利水渗湿、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、散寒止痛、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、补气固表、利水渗湿</t>
-  </si>
-  <si>
-    <t>滋阴润燥、补气固表、散寒止痛、疏肝理气</t>
-  </si>
-  <si>
-    <t>养心安神、补气固表、利水渗湿、活血化瘀</t>
-  </si>
-  <si>
-    <t>散寒止痛、补虚暖身、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>增强免疫、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>散寒止痛、疏肝理气、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养肝明目、清热降火、润肺止咳、补虚暖身</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥</t>
-  </si>
-  <si>
-    <t>滋阴润燥、润肺止咳、补气固表、利水渗湿</t>
-  </si>
-  <si>
-    <t>滋阴润燥、补气固表、疏肝理气、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、润肺止咳、增强免疫、利水渗湿、疏肝理气、泻下通便</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、补气固表、散寒止痛、活血化瘀</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、补气固表、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、润肺止咳</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、养心安神、润肺止咳、补气固表、疏肝理气</t>
-  </si>
-  <si>
-    <t>养肝明目、清热降火、利水渗湿</t>
-  </si>
-  <si>
-    <t>散寒止痛、利水渗湿、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、养心安神、散寒止痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、补气固表、疏肝理气</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、增强免疫、温经养血、散寒止痛、补虚暖身、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、健脾升阳、利水渗湿、祛风湿痛</t>
-  </si>
-  <si>
-    <t>清热降火、利水渗湿</t>
-  </si>
-  <si>
-    <t>润肺止咳、补气固表、增强免疫、散寒止痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、利水渗湿、活血化瘀</t>
-  </si>
-  <si>
-    <t>润肺止咳、活血化瘀</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、养心安神、增强免疫</t>
-  </si>
-  <si>
-    <t>清热降火、润肺止咳、补气固表、健脾升阳、增强免疫、散寒止痛、宁心安神、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气养血、滋阴润燥、清热降火、润肺止咳、补气固表、增强免疫、补虚暖身</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、疏肝理气、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、润肺止咳、利水渗湿、活血化瘀、祛风湿痛</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、润肺止咳、补气固表、祛风湿痛</t>
-  </si>
-  <si>
-    <t>利水渗湿、活血化瘀</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气固表、增强免疫、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、清热降火、补气固表、增强免疫</t>
-  </si>
-  <si>
-    <t>补气养血、养心安神</t>
-  </si>
-  <si>
-    <t>健脾养胃、滋阴润燥、润肺止咳、散寒止痛、疏肝理气、祛风湿痛</t>
-  </si>
-  <si>
-    <t>补气固表、散寒止痛、驱虫杀虫</t>
-  </si>
-  <si>
-    <t>润肺止咳、散寒止痛、利水渗湿、疏肝理气</t>
-  </si>
-  <si>
-    <t>滋阴润燥、利水渗湿、疏肝理气、祛风湿痛</t>
-  </si>
-  <si>
-    <t>滋阴润燥、清热降火、润肺止咳、增强免疫</t>
-  </si>
-  <si>
-    <t>健脾养胃、清热降火、散寒止痛、利水渗湿、疏肝理气</t>
-  </si>
-  <si>
-    <t>健脾养胃、补气固表、健脾升阳、增强免疫、祛风湿痛</t>
-  </si>
-  <si>
-    <t>养肝明目、养心安神</t>
+    <t>驱虫杀虫、利水渗湿、清热解毒</t>
+  </si>
+  <si>
+    <t>活血化瘀、祛风湿痛、发散表邪、温阳散寒</t>
+  </si>
+  <si>
+    <t>活血化瘀、消食导滞、清热解毒、宁血止血</t>
+  </si>
+  <si>
+    <t>温阳散寒、宁血止血、扶正补虚</t>
+  </si>
+  <si>
+    <t>活血化瘀、消食导滞</t>
+  </si>
+  <si>
+    <t>收敛固涩、宁心安神、宁血止血</t>
+  </si>
+  <si>
+    <t>驱虫杀虫、利水渗湿、清热解毒、宁血止血</t>
+  </si>
+  <si>
+    <t>活血化瘀、祛风湿痛、清热解毒、化痰止咳</t>
+  </si>
+  <si>
+    <t>活血化瘀、温阳散寒、扶正补虚</t>
+  </si>
+  <si>
+    <t>清热解毒、宁心安神、发散表邪、收敛固涩、宁血止血</t>
+  </si>
+  <si>
+    <t>祛风湿痛、宁心安神</t>
+  </si>
+  <si>
+    <t>疏肝理气、宁血止血</t>
+  </si>
+  <si>
+    <t>清热解毒、化痰止咳、疏肝理气</t>
+  </si>
+  <si>
+    <t>活血化瘀、清热解毒、化痰止咳</t>
+  </si>
+  <si>
+    <t>利水渗湿、发散表邪、化痰止咳</t>
+  </si>
+  <si>
+    <t>化痰止咳、扶正补虚</t>
+  </si>
+  <si>
+    <t>活血化瘀、发散表邪、清热解毒、宁血止血</t>
+  </si>
+  <si>
+    <t>收敛固涩、清热解毒</t>
+  </si>
+  <si>
+    <t>收敛固涩、活血化瘀、祛风湿痛</t>
+  </si>
+  <si>
+    <t>收敛固涩、利水渗湿、清热解毒、宁血止血</t>
+  </si>
+  <si>
+    <t>清热解毒、疏肝理气</t>
+  </si>
+  <si>
+    <t>化痰止咳、活血化瘀、清热解毒、宁血止血</t>
+  </si>
+  <si>
+    <t>发散表邪、温阳散寒、扶正补虚</t>
+  </si>
+  <si>
+    <t>活血化瘀、泻下通便、驱虫杀虫、清热解毒</t>
+  </si>
+  <si>
+    <t>收敛固涩、宁心安神</t>
+  </si>
+  <si>
+    <t>活血化瘀、祛风湿痛、宁心安神</t>
+  </si>
+  <si>
+    <t>清热解毒、疏肝理气、宁血止血</t>
+  </si>
+  <si>
+    <t>驱虫杀虫、消食导滞</t>
+  </si>
+  <si>
+    <t>活血化瘀、驱虫杀虫、清热解毒、扶正补虚</t>
+  </si>
+  <si>
+    <t>活血化瘀、祛风湿痛、温阳散寒、宁血止血、化痰止咳</t>
+  </si>
+  <si>
+    <t>活血化瘀、宁心安神、清热解毒</t>
+  </si>
+  <si>
+    <t>驱虫杀虫、温阳散寒</t>
+  </si>
+  <si>
+    <t>活血化瘀、利水渗湿、清热解毒、宁血止血</t>
+  </si>
+  <si>
+    <t>收敛固涩、消食导滞、温阳散寒、疏肝理气</t>
+  </si>
+  <si>
+    <t>化痰止咳、发散表邪、清热解毒、宁血止血</t>
+  </si>
+  <si>
+    <t>活血化瘀、清热解毒、泻下通便、疏肝理气、宁血止血、化痰止咳</t>
+  </si>
+  <si>
+    <t>活血化瘀、宁心安神、宁血止血</t>
+  </si>
+  <si>
+    <t>发散表邪、清热解毒、宁血止血、扶正补虚</t>
+  </si>
+  <si>
+    <t>活血化瘀、清热解毒、扶正补虚、祛风湿痛、温阳散寒、宁血止血、化痰止咳</t>
+  </si>
+  <si>
+    <t>活血化瘀、清热解毒、疏肝理气、宁血止血、利水渗湿</t>
+  </si>
+  <si>
+    <t>活血化瘀、祛风湿痛、消食导滞、化痰止咳</t>
+  </si>
+  <si>
+    <t>化痰止咳、清热解毒、宁血止血</t>
+  </si>
+  <si>
+    <t>祛风湿痛、发散表邪、宁血止血</t>
+  </si>
+  <si>
+    <t>宁心安神、清热解毒、化痰止咳</t>
+  </si>
+  <si>
+    <t>利水渗湿、化痰止咳</t>
+  </si>
+  <si>
+    <t>活血化瘀、清热解毒、收敛固涩、宁血止血、化痰止咳</t>
+  </si>
+  <si>
+    <t>收敛固涩、泻下通便、清热解毒、宁血止血</t>
+  </si>
+  <si>
+    <t>温阳散寒、扶正补虚</t>
+  </si>
+  <si>
+    <t>发散表邪、化痰止咳</t>
+  </si>
+  <si>
+    <t>收敛固涩、化痰止咳</t>
+  </si>
+  <si>
+    <t>收敛固涩、泻下通便、清热解毒、疏肝理气</t>
+  </si>
+  <si>
+    <t>泻下通便、清热解毒、扶正补虚</t>
+  </si>
+  <si>
+    <t>清热解毒、宁心安神、泻下通便、宁血止血、驱虫杀虫</t>
+  </si>
+  <si>
+    <t>活血化瘀、祛风湿痛、宁血止血</t>
+  </si>
+  <si>
+    <t>活血化瘀、宁血止血、化痰止咳</t>
+  </si>
+  <si>
+    <t>祛风湿痛、疏肝理气、化痰止咳、扶正补虚</t>
+  </si>
+  <si>
+    <t>活血化瘀、祛风湿痛、驱虫杀虫、清热解毒</t>
+  </si>
+  <si>
+    <t>驱虫杀虫、祛风湿痛、清热解毒、疏肝理气</t>
+  </si>
+  <si>
+    <t>祛风湿痛、发散表邪、温阳散寒</t>
+  </si>
+  <si>
+    <t>温阳散寒、活血化瘀、疏肝理气</t>
+  </si>
+  <si>
+    <t>活血化瘀、祛风湿痛、疏肝理气、宁血止血</t>
+  </si>
+  <si>
+    <t>活血化瘀、清热解毒、疏肝理气、宁血止血</t>
+  </si>
+  <si>
+    <t>驱虫杀虫、清热解毒</t>
+  </si>
+  <si>
+    <t>祛风湿痛、温阳散寒</t>
+  </si>
+  <si>
+    <t>祛风湿痛、利水渗湿、宁血止血</t>
+  </si>
+  <si>
+    <t>宁心安神、温阳散寒</t>
+  </si>
+  <si>
+    <t>清热解毒、化痰止咳、扶正补虚</t>
+  </si>
+  <si>
+    <t>清热解毒、收敛固涩、疏肝理气、宁血止血、驱虫杀虫</t>
+  </si>
+  <si>
+    <t>活血化瘀、清热解毒、扶正补虚、发散表邪、宁血止血、利水渗湿</t>
+  </si>
+  <si>
+    <t>活血化瘀、利水渗湿</t>
+  </si>
+  <si>
+    <t>收敛固涩、宁血止血、扶正补虚</t>
+  </si>
+  <si>
+    <t>宁心安神、宁血止血</t>
+  </si>
+  <si>
+    <t>发散表邪、温阳散寒、疏肝理气</t>
+  </si>
+  <si>
+    <t>发散表邪、疏肝理气、化痰止咳</t>
+  </si>
+  <si>
+    <t>收敛固涩、利水渗湿</t>
+  </si>
+  <si>
+    <t>消食导滞、疏肝理气</t>
   </si>
 </sst>
 </file>
@@ -4248,7 +3642,7 @@
         <v>645</v>
       </c>
       <c r="G14" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -4271,7 +3665,7 @@
         <v>646</v>
       </c>
       <c r="G15" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -4294,7 +3688,7 @@
         <v>647</v>
       </c>
       <c r="G16" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -4317,7 +3711,7 @@
         <v>648</v>
       </c>
       <c r="G17" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -4340,7 +3734,7 @@
         <v>649</v>
       </c>
       <c r="G18" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -4363,7 +3757,7 @@
         <v>650</v>
       </c>
       <c r="G19" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -4386,7 +3780,7 @@
         <v>641</v>
       </c>
       <c r="G20" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -4409,7 +3803,7 @@
         <v>651</v>
       </c>
       <c r="G21" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -4432,7 +3826,7 @@
         <v>652</v>
       </c>
       <c r="G22" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -4455,7 +3849,7 @@
         <v>636</v>
       </c>
       <c r="G23" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -4478,7 +3872,7 @@
         <v>653</v>
       </c>
       <c r="G24" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -4501,7 +3895,7 @@
         <v>654</v>
       </c>
       <c r="G25" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -4524,7 +3918,7 @@
         <v>655</v>
       </c>
       <c r="G26" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -4547,7 +3941,7 @@
         <v>642</v>
       </c>
       <c r="G27" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -4570,7 +3964,7 @@
         <v>656</v>
       </c>
       <c r="G28" t="s">
-        <v>839</v>
+        <v>824</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -4593,7 +3987,7 @@
         <v>657</v>
       </c>
       <c r="G29" t="s">
-        <v>840</v>
+        <v>824</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -4616,7 +4010,7 @@
         <v>658</v>
       </c>
       <c r="G30" t="s">
-        <v>841</v>
+        <v>815</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -4639,7 +4033,7 @@
         <v>647</v>
       </c>
       <c r="G31" t="s">
-        <v>842</v>
+        <v>824</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -4662,7 +4056,7 @@
         <v>659</v>
       </c>
       <c r="G32" t="s">
-        <v>843</v>
+        <v>822</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -4682,7 +4076,7 @@
         <v>627</v>
       </c>
       <c r="G33" t="s">
-        <v>844</v>
+        <v>835</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -4705,7 +4099,7 @@
         <v>649</v>
       </c>
       <c r="G34" t="s">
-        <v>845</v>
+        <v>836</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -4728,7 +4122,7 @@
         <v>660</v>
       </c>
       <c r="G35" t="s">
-        <v>846</v>
+        <v>824</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -4751,7 +4145,7 @@
         <v>661</v>
       </c>
       <c r="G36" t="s">
-        <v>847</v>
+        <v>824</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -4774,7 +4168,7 @@
         <v>662</v>
       </c>
       <c r="G37" t="s">
-        <v>848</v>
+        <v>837</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -4797,7 +4191,7 @@
         <v>663</v>
       </c>
       <c r="G38" t="s">
-        <v>829</v>
+        <v>820</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -4820,7 +4214,7 @@
         <v>636</v>
       </c>
       <c r="G39" t="s">
-        <v>849</v>
+        <v>820</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -4843,7 +4237,7 @@
         <v>640</v>
       </c>
       <c r="G40" t="s">
-        <v>850</v>
+        <v>838</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -4866,7 +4260,7 @@
         <v>652</v>
       </c>
       <c r="G41" t="s">
-        <v>851</v>
+        <v>821</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -4889,7 +4283,7 @@
         <v>658</v>
       </c>
       <c r="G42" t="s">
-        <v>852</v>
+        <v>839</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -4912,7 +4306,7 @@
         <v>657</v>
       </c>
       <c r="G43" t="s">
-        <v>853</v>
+        <v>840</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -4935,7 +4329,7 @@
         <v>664</v>
       </c>
       <c r="G44" t="s">
-        <v>844</v>
+        <v>819</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -4958,7 +4352,7 @@
         <v>647</v>
       </c>
       <c r="G45" t="s">
-        <v>854</v>
+        <v>841</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -4981,7 +4375,7 @@
         <v>647</v>
       </c>
       <c r="G46" t="s">
-        <v>855</v>
+        <v>822</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -5004,7 +4398,7 @@
         <v>660</v>
       </c>
       <c r="G47" t="s">
-        <v>856</v>
+        <v>842</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -5027,7 +4421,7 @@
         <v>657</v>
       </c>
       <c r="G48" t="s">
-        <v>857</v>
+        <v>822</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -5050,7 +4444,7 @@
         <v>665</v>
       </c>
       <c r="G49" t="s">
-        <v>858</v>
+        <v>824</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -5073,7 +4467,7 @@
         <v>635</v>
       </c>
       <c r="G50" t="s">
-        <v>859</v>
+        <v>843</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -5096,7 +4490,7 @@
         <v>666</v>
       </c>
       <c r="G51" t="s">
-        <v>829</v>
+        <v>844</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -5119,7 +4513,7 @@
         <v>667</v>
       </c>
       <c r="G52" t="s">
-        <v>860</v>
+        <v>845</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -5142,7 +4536,7 @@
         <v>668</v>
       </c>
       <c r="G53" t="s">
-        <v>861</v>
+        <v>824</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -5165,7 +4559,7 @@
         <v>669</v>
       </c>
       <c r="G54" t="s">
-        <v>862</v>
+        <v>846</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -5188,7 +4582,7 @@
         <v>670</v>
       </c>
       <c r="G55" t="s">
-        <v>863</v>
+        <v>847</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -5211,7 +4605,7 @@
         <v>671</v>
       </c>
       <c r="G56" t="s">
-        <v>864</v>
+        <v>829</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -5234,7 +4628,7 @@
         <v>672</v>
       </c>
       <c r="G57" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -5257,7 +4651,7 @@
         <v>647</v>
       </c>
       <c r="G58" t="s">
-        <v>865</v>
+        <v>824</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -5280,7 +4674,7 @@
         <v>657</v>
       </c>
       <c r="G59" t="s">
-        <v>866</v>
+        <v>848</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -5303,7 +4697,7 @@
         <v>673</v>
       </c>
       <c r="G60" t="s">
-        <v>867</v>
+        <v>820</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -5326,7 +4720,7 @@
         <v>674</v>
       </c>
       <c r="G61" t="s">
-        <v>868</v>
+        <v>849</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -5349,7 +4743,7 @@
         <v>646</v>
       </c>
       <c r="G62" t="s">
-        <v>841</v>
+        <v>815</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -5372,7 +4766,7 @@
         <v>675</v>
       </c>
       <c r="G63" t="s">
-        <v>869</v>
+        <v>816</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -5395,7 +4789,7 @@
         <v>676</v>
       </c>
       <c r="G64" t="s">
-        <v>870</v>
+        <v>824</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -5418,7 +4812,7 @@
         <v>677</v>
       </c>
       <c r="G65" t="s">
-        <v>871</v>
+        <v>850</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -5441,7 +4835,7 @@
         <v>678</v>
       </c>
       <c r="G66" t="s">
-        <v>847</v>
+        <v>824</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -5464,7 +4858,7 @@
         <v>679</v>
       </c>
       <c r="G67" t="s">
-        <v>872</v>
+        <v>831</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -5487,7 +4881,7 @@
         <v>640</v>
       </c>
       <c r="G68" t="s">
-        <v>873</v>
+        <v>840</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -5510,7 +4904,7 @@
         <v>680</v>
       </c>
       <c r="G69" t="s">
-        <v>874</v>
+        <v>846</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -5533,7 +4927,7 @@
         <v>640</v>
       </c>
       <c r="G70" t="s">
-        <v>874</v>
+        <v>851</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -5556,7 +4950,7 @@
         <v>665</v>
       </c>
       <c r="G71" t="s">
-        <v>875</v>
+        <v>852</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -5579,7 +4973,7 @@
         <v>681</v>
       </c>
       <c r="G72" t="s">
-        <v>876</v>
+        <v>853</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -5602,7 +4996,7 @@
         <v>682</v>
       </c>
       <c r="G73" t="s">
-        <v>877</v>
+        <v>821</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -5625,7 +5019,7 @@
         <v>649</v>
       </c>
       <c r="G74" t="s">
-        <v>878</v>
+        <v>824</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -5648,7 +5042,7 @@
         <v>683</v>
       </c>
       <c r="G75" t="s">
-        <v>879</v>
+        <v>820</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -5671,7 +5065,7 @@
         <v>649</v>
       </c>
       <c r="G76" t="s">
-        <v>880</v>
+        <v>819</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -5694,7 +5088,7 @@
         <v>642</v>
       </c>
       <c r="G77" t="s">
-        <v>881</v>
+        <v>854</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -5717,7 +5111,7 @@
         <v>646</v>
       </c>
       <c r="G78" t="s">
-        <v>882</v>
+        <v>855</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -5740,7 +5134,7 @@
         <v>684</v>
       </c>
       <c r="G79" t="s">
-        <v>883</v>
+        <v>856</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -5763,7 +5157,7 @@
         <v>647</v>
       </c>
       <c r="G80" t="s">
-        <v>884</v>
+        <v>820</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -5786,7 +5180,7 @@
         <v>685</v>
       </c>
       <c r="G81" t="s">
-        <v>885</v>
+        <v>819</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -5809,7 +5203,7 @@
         <v>686</v>
       </c>
       <c r="G82" t="s">
-        <v>886</v>
+        <v>824</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -5832,7 +5226,7 @@
         <v>685</v>
       </c>
       <c r="G83" t="s">
-        <v>887</v>
+        <v>857</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -5855,7 +5249,7 @@
         <v>687</v>
       </c>
       <c r="G84" t="s">
-        <v>888</v>
+        <v>858</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -5878,7 +5272,7 @@
         <v>688</v>
       </c>
       <c r="G85" t="s">
-        <v>889</v>
+        <v>849</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -5901,7 +5295,7 @@
         <v>634</v>
       </c>
       <c r="G86" t="s">
-        <v>837</v>
+        <v>851</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -5924,7 +5318,7 @@
         <v>689</v>
       </c>
       <c r="G87" t="s">
-        <v>890</v>
+        <v>829</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -5947,7 +5341,7 @@
         <v>690</v>
       </c>
       <c r="G88" t="s">
-        <v>891</v>
+        <v>820</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -5970,7 +5364,7 @@
         <v>635</v>
       </c>
       <c r="G89" t="s">
-        <v>892</v>
+        <v>824</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -5993,7 +5387,7 @@
         <v>691</v>
       </c>
       <c r="G90" t="s">
-        <v>849</v>
+        <v>824</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -6016,7 +5410,7 @@
         <v>692</v>
       </c>
       <c r="G91" t="s">
-        <v>893</v>
+        <v>828</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -6039,7 +5433,7 @@
         <v>635</v>
       </c>
       <c r="G92" t="s">
-        <v>894</v>
+        <v>824</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -6062,7 +5456,7 @@
         <v>693</v>
       </c>
       <c r="G93" t="s">
-        <v>847</v>
+        <v>859</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -6085,7 +5479,7 @@
         <v>652</v>
       </c>
       <c r="G94" t="s">
-        <v>895</v>
+        <v>820</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -6108,7 +5502,7 @@
         <v>652</v>
       </c>
       <c r="G95" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -6131,7 +5525,7 @@
         <v>694</v>
       </c>
       <c r="G96" t="s">
-        <v>896</v>
+        <v>824</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -6154,7 +5548,7 @@
         <v>685</v>
       </c>
       <c r="G97" t="s">
-        <v>897</v>
+        <v>824</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -6177,7 +5571,7 @@
         <v>695</v>
       </c>
       <c r="G98" t="s">
-        <v>898</v>
+        <v>860</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -6200,7 +5594,7 @@
         <v>696</v>
       </c>
       <c r="G99" t="s">
-        <v>899</v>
+        <v>824</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -6223,7 +5617,7 @@
         <v>697</v>
       </c>
       <c r="G100" t="s">
-        <v>900</v>
+        <v>827</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -6246,7 +5640,7 @@
         <v>698</v>
       </c>
       <c r="G101" t="s">
-        <v>901</v>
+        <v>861</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -6269,7 +5663,7 @@
         <v>690</v>
       </c>
       <c r="G102" t="s">
-        <v>902</v>
+        <v>862</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -6292,7 +5686,7 @@
         <v>699</v>
       </c>
       <c r="G103" t="s">
-        <v>903</v>
+        <v>863</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -6315,7 +5709,7 @@
         <v>647</v>
       </c>
       <c r="G104" t="s">
-        <v>904</v>
+        <v>826</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -6338,7 +5732,7 @@
         <v>674</v>
       </c>
       <c r="G105" t="s">
-        <v>905</v>
+        <v>829</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -6361,7 +5755,7 @@
         <v>700</v>
       </c>
       <c r="G106" t="s">
-        <v>906</v>
+        <v>829</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -6384,7 +5778,7 @@
         <v>701</v>
       </c>
       <c r="G107" t="s">
-        <v>907</v>
+        <v>864</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -6407,7 +5801,7 @@
         <v>674</v>
       </c>
       <c r="G108" t="s">
-        <v>908</v>
+        <v>862</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -6430,7 +5824,7 @@
         <v>702</v>
       </c>
       <c r="G109" t="s">
-        <v>909</v>
+        <v>819</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -6453,7 +5847,7 @@
         <v>703</v>
       </c>
       <c r="G110" t="s">
-        <v>910</v>
+        <v>865</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -6476,7 +5870,7 @@
         <v>704</v>
       </c>
       <c r="G111" t="s">
-        <v>911</v>
+        <v>866</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -6499,7 +5893,7 @@
         <v>653</v>
       </c>
       <c r="G112" t="s">
-        <v>912</v>
+        <v>867</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -6522,7 +5916,7 @@
         <v>705</v>
       </c>
       <c r="G113" t="s">
-        <v>913</v>
+        <v>821</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -6545,7 +5939,7 @@
         <v>706</v>
       </c>
       <c r="G114" t="s">
-        <v>914</v>
+        <v>824</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -6568,7 +5962,7 @@
         <v>651</v>
       </c>
       <c r="G115" t="s">
-        <v>915</v>
+        <v>868</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -6591,7 +5985,7 @@
         <v>659</v>
       </c>
       <c r="G116" t="s">
-        <v>916</v>
+        <v>832</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -6614,7 +6008,7 @@
         <v>707</v>
       </c>
       <c r="G117" t="s">
-        <v>899</v>
+        <v>832</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -6637,7 +6031,7 @@
         <v>636</v>
       </c>
       <c r="G118" t="s">
-        <v>917</v>
+        <v>821</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -6660,7 +6054,7 @@
         <v>708</v>
       </c>
       <c r="G119" t="s">
-        <v>918</v>
+        <v>822</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -6683,7 +6077,7 @@
         <v>640</v>
       </c>
       <c r="G120" t="s">
-        <v>919</v>
+        <v>869</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -6706,7 +6100,7 @@
         <v>709</v>
       </c>
       <c r="G121" t="s">
-        <v>899</v>
+        <v>824</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -6729,7 +6123,7 @@
         <v>710</v>
       </c>
       <c r="G122" t="s">
-        <v>920</v>
+        <v>863</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -6752,7 +6146,7 @@
         <v>674</v>
       </c>
       <c r="G123" t="s">
-        <v>921</v>
+        <v>829</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -6775,7 +6169,7 @@
         <v>674</v>
       </c>
       <c r="G124" t="s">
-        <v>905</v>
+        <v>856</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -6798,7 +6192,7 @@
         <v>711</v>
       </c>
       <c r="G125" t="s">
-        <v>922</v>
+        <v>856</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -6821,7 +6215,7 @@
         <v>712</v>
       </c>
       <c r="G126" t="s">
-        <v>923</v>
+        <v>833</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -6844,7 +6238,7 @@
         <v>713</v>
       </c>
       <c r="G127" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -6867,7 +6261,7 @@
         <v>714</v>
       </c>
       <c r="G128" t="s">
-        <v>924</v>
+        <v>871</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -6890,7 +6284,7 @@
         <v>715</v>
       </c>
       <c r="G129" t="s">
-        <v>925</v>
+        <v>872</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6913,7 +6307,7 @@
         <v>716</v>
       </c>
       <c r="G130" t="s">
-        <v>926</v>
+        <v>847</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -6936,7 +6330,7 @@
         <v>638</v>
       </c>
       <c r="G131" t="s">
-        <v>829</v>
+        <v>815</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -6959,7 +6353,7 @@
         <v>700</v>
       </c>
       <c r="G132" t="s">
-        <v>927</v>
+        <v>873</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -6982,7 +6376,7 @@
         <v>647</v>
       </c>
       <c r="G133" t="s">
-        <v>899</v>
+        <v>820</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -7005,7 +6399,7 @@
         <v>717</v>
       </c>
       <c r="G134" t="s">
-        <v>928</v>
+        <v>874</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -7028,7 +6422,7 @@
         <v>670</v>
       </c>
       <c r="G135" t="s">
-        <v>929</v>
+        <v>858</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -7051,7 +6445,7 @@
         <v>653</v>
       </c>
       <c r="G136" t="s">
-        <v>930</v>
+        <v>875</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -7074,7 +6468,7 @@
         <v>718</v>
       </c>
       <c r="G137" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -7097,7 +6491,7 @@
         <v>719</v>
       </c>
       <c r="G138" t="s">
-        <v>931</v>
+        <v>833</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -7120,7 +6514,7 @@
         <v>653</v>
       </c>
       <c r="G139" t="s">
-        <v>844</v>
+        <v>876</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -7143,7 +6537,7 @@
         <v>649</v>
       </c>
       <c r="G140" t="s">
-        <v>932</v>
+        <v>870</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -7166,7 +6560,7 @@
         <v>699</v>
       </c>
       <c r="G141" t="s">
-        <v>933</v>
+        <v>872</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -7189,7 +6583,7 @@
         <v>657</v>
       </c>
       <c r="G142" t="s">
-        <v>934</v>
+        <v>824</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -7212,7 +6606,7 @@
         <v>653</v>
       </c>
       <c r="G143" t="s">
-        <v>935</v>
+        <v>877</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -7232,7 +6626,7 @@
         <v>720</v>
       </c>
       <c r="G144" t="s">
-        <v>936</v>
+        <v>840</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -7255,7 +6649,7 @@
         <v>647</v>
       </c>
       <c r="G145" t="s">
-        <v>922</v>
+        <v>828</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -7278,7 +6672,7 @@
         <v>659</v>
       </c>
       <c r="G146" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -7301,7 +6695,7 @@
         <v>647</v>
       </c>
       <c r="G147" t="s">
-        <v>937</v>
+        <v>878</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -7324,7 +6718,7 @@
         <v>647</v>
       </c>
       <c r="G148" t="s">
-        <v>938</v>
+        <v>834</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -7347,7 +6741,7 @@
         <v>699</v>
       </c>
       <c r="G149" t="s">
-        <v>939</v>
+        <v>821</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -7370,7 +6764,7 @@
         <v>710</v>
       </c>
       <c r="G150" t="s">
-        <v>940</v>
+        <v>879</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -7393,7 +6787,7 @@
         <v>652</v>
       </c>
       <c r="G151" t="s">
-        <v>941</v>
+        <v>824</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -7416,7 +6810,7 @@
         <v>659</v>
       </c>
       <c r="G152" t="s">
-        <v>942</v>
+        <v>880</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -7439,7 +6833,7 @@
         <v>699</v>
       </c>
       <c r="G153" t="s">
-        <v>877</v>
+        <v>824</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -7462,7 +6856,7 @@
         <v>647</v>
       </c>
       <c r="G154" t="s">
-        <v>911</v>
+        <v>881</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -7485,7 +6879,7 @@
         <v>649</v>
       </c>
       <c r="G155" t="s">
-        <v>943</v>
+        <v>840</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -7505,7 +6899,7 @@
         <v>630</v>
       </c>
       <c r="G156" t="s">
-        <v>864</v>
+        <v>882</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -7528,7 +6922,7 @@
         <v>721</v>
       </c>
       <c r="G157" t="s">
-        <v>944</v>
+        <v>844</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -7551,7 +6945,7 @@
         <v>647</v>
       </c>
       <c r="G158" t="s">
-        <v>945</v>
+        <v>824</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -7574,7 +6968,7 @@
         <v>665</v>
       </c>
       <c r="G159" t="s">
-        <v>874</v>
+        <v>824</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -7597,7 +6991,7 @@
         <v>722</v>
       </c>
       <c r="G160" t="s">
-        <v>874</v>
+        <v>815</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -7620,7 +7014,7 @@
         <v>653</v>
       </c>
       <c r="G161" t="s">
-        <v>946</v>
+        <v>883</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -7643,7 +7037,7 @@
         <v>723</v>
       </c>
       <c r="G162" t="s">
-        <v>947</v>
+        <v>884</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -7666,7 +7060,7 @@
         <v>724</v>
       </c>
       <c r="G163" t="s">
-        <v>912</v>
+        <v>840</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -7689,7 +7083,7 @@
         <v>725</v>
       </c>
       <c r="G164" t="s">
-        <v>948</v>
+        <v>870</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -7712,7 +7106,7 @@
         <v>726</v>
       </c>
       <c r="G165" t="s">
-        <v>911</v>
+        <v>821</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -7735,7 +7129,7 @@
         <v>710</v>
       </c>
       <c r="G166" t="s">
-        <v>949</v>
+        <v>856</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -7758,7 +7152,7 @@
         <v>727</v>
       </c>
       <c r="G167" t="s">
-        <v>950</v>
+        <v>824</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -7781,7 +7175,7 @@
         <v>728</v>
       </c>
       <c r="G168" t="s">
-        <v>916</v>
+        <v>832</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -7804,7 +7198,7 @@
         <v>648</v>
       </c>
       <c r="G169" t="s">
-        <v>951</v>
+        <v>816</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -7827,7 +7221,7 @@
         <v>640</v>
       </c>
       <c r="G170" t="s">
-        <v>847</v>
+        <v>870</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -7850,7 +7244,7 @@
         <v>729</v>
       </c>
       <c r="G171" t="s">
-        <v>952</v>
+        <v>885</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -7869,11 +7263,8 @@
       <c r="E172" t="s">
         <v>624</v>
       </c>
-      <c r="F172" t="s">
-        <v>730</v>
-      </c>
       <c r="G172" t="s">
-        <v>953</v>
+        <v>886</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -7893,10 +7284,10 @@
         <v>625</v>
       </c>
       <c r="F173" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G173" t="s">
-        <v>899</v>
+        <v>824</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -7919,7 +7310,7 @@
         <v>660</v>
       </c>
       <c r="G174" t="s">
-        <v>954</v>
+        <v>833</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -7942,7 +7333,7 @@
         <v>653</v>
       </c>
       <c r="G175" t="s">
-        <v>955</v>
+        <v>887</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -7965,7 +7356,7 @@
         <v>634</v>
       </c>
       <c r="G176" t="s">
-        <v>956</v>
+        <v>888</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -7988,7 +7379,7 @@
         <v>653</v>
       </c>
       <c r="G177" t="s">
-        <v>957</v>
+        <v>889</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -8008,10 +7399,10 @@
         <v>629</v>
       </c>
       <c r="F178" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="G178" t="s">
-        <v>958</v>
+        <v>876</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -8031,10 +7422,10 @@
         <v>627</v>
       </c>
       <c r="F179" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="G179" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -8057,7 +7448,7 @@
         <v>705</v>
       </c>
       <c r="G180" t="s">
-        <v>873</v>
+        <v>824</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -8080,7 +7471,7 @@
         <v>642</v>
       </c>
       <c r="G181" t="s">
-        <v>959</v>
+        <v>890</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -8103,7 +7494,7 @@
         <v>662</v>
       </c>
       <c r="G182" t="s">
-        <v>960</v>
+        <v>891</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -8126,7 +7517,7 @@
         <v>648</v>
       </c>
       <c r="G183" t="s">
-        <v>961</v>
+        <v>821</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -8146,10 +7537,10 @@
         <v>633</v>
       </c>
       <c r="F184" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="G184" t="s">
-        <v>962</v>
+        <v>892</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -8172,7 +7563,7 @@
         <v>734</v>
       </c>
       <c r="G185" t="s">
-        <v>849</v>
+        <v>821</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -8195,7 +7586,7 @@
         <v>735</v>
       </c>
       <c r="G186" t="s">
-        <v>963</v>
+        <v>824</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -8218,7 +7609,7 @@
         <v>636</v>
       </c>
       <c r="G187" t="s">
-        <v>964</v>
+        <v>820</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -8241,7 +7632,7 @@
         <v>653</v>
       </c>
       <c r="G188" t="s">
-        <v>877</v>
+        <v>824</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -8264,7 +7655,7 @@
         <v>736</v>
       </c>
       <c r="G189" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -8287,7 +7678,7 @@
         <v>737</v>
       </c>
       <c r="G190" t="s">
-        <v>965</v>
+        <v>824</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -8310,7 +7701,7 @@
         <v>638</v>
       </c>
       <c r="G191" t="s">
-        <v>966</v>
+        <v>893</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -8333,7 +7724,7 @@
         <v>702</v>
       </c>
       <c r="G192" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -8356,7 +7747,7 @@
         <v>738</v>
       </c>
       <c r="G193" t="s">
-        <v>967</v>
+        <v>870</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -8379,7 +7770,7 @@
         <v>653</v>
       </c>
       <c r="G194" t="s">
-        <v>968</v>
+        <v>894</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -8402,7 +7793,7 @@
         <v>739</v>
       </c>
       <c r="G195" t="s">
-        <v>969</v>
+        <v>824</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -8448,7 +7839,7 @@
         <v>702</v>
       </c>
       <c r="G197" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -8471,7 +7862,7 @@
         <v>642</v>
       </c>
       <c r="G198" t="s">
-        <v>970</v>
+        <v>895</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -8494,7 +7885,7 @@
         <v>674</v>
       </c>
       <c r="G199" t="s">
-        <v>971</v>
+        <v>896</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -8517,7 +7908,7 @@
         <v>702</v>
       </c>
       <c r="G200" t="s">
-        <v>972</v>
+        <v>897</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -8540,7 +7931,7 @@
         <v>741</v>
       </c>
       <c r="G201" t="s">
-        <v>973</v>
+        <v>885</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -8563,7 +7954,7 @@
         <v>706</v>
       </c>
       <c r="G202" t="s">
-        <v>921</v>
+        <v>829</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -8586,7 +7977,7 @@
         <v>742</v>
       </c>
       <c r="G203" t="s">
-        <v>918</v>
+        <v>870</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -8609,7 +8000,7 @@
         <v>660</v>
       </c>
       <c r="G204" t="s">
-        <v>974</v>
+        <v>898</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -8632,7 +8023,7 @@
         <v>743</v>
       </c>
       <c r="G205" t="s">
-        <v>975</v>
+        <v>849</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -8655,7 +8046,7 @@
         <v>641</v>
       </c>
       <c r="G206" t="s">
-        <v>976</v>
+        <v>817</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -8678,7 +8069,7 @@
         <v>722</v>
       </c>
       <c r="G207" t="s">
-        <v>844</v>
+        <v>827</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -8701,7 +8092,7 @@
         <v>744</v>
       </c>
       <c r="G208" t="s">
-        <v>977</v>
+        <v>899</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -8724,7 +8115,7 @@
         <v>653</v>
       </c>
       <c r="G209" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -8747,7 +8138,7 @@
         <v>691</v>
       </c>
       <c r="G210" t="s">
-        <v>893</v>
+        <v>824</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -8767,7 +8158,7 @@
         <v>628</v>
       </c>
       <c r="G211" t="s">
-        <v>978</v>
+        <v>900</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -8790,7 +8181,7 @@
         <v>669</v>
       </c>
       <c r="G212" t="s">
-        <v>979</v>
+        <v>901</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -8809,11 +8200,8 @@
       <c r="E213" t="s">
         <v>626</v>
       </c>
-      <c r="F213" t="s">
-        <v>655</v>
-      </c>
       <c r="G213" t="s">
-        <v>829</v>
+        <v>820</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -8836,7 +8224,7 @@
         <v>709</v>
       </c>
       <c r="G214" t="s">
-        <v>980</v>
+        <v>902</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -8859,7 +8247,7 @@
         <v>653</v>
       </c>
       <c r="G215" t="s">
-        <v>981</v>
+        <v>828</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -8882,7 +8270,7 @@
         <v>697</v>
       </c>
       <c r="G216" t="s">
-        <v>982</v>
+        <v>843</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -8905,7 +8293,7 @@
         <v>745</v>
       </c>
       <c r="G217" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -8928,7 +8316,7 @@
         <v>746</v>
       </c>
       <c r="G218" t="s">
-        <v>983</v>
+        <v>829</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -8951,7 +8339,7 @@
         <v>747</v>
       </c>
       <c r="G219" t="s">
-        <v>984</v>
+        <v>903</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -8974,7 +8362,7 @@
         <v>647</v>
       </c>
       <c r="G220" t="s">
-        <v>911</v>
+        <v>813</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -8997,7 +8385,7 @@
         <v>642</v>
       </c>
       <c r="G221" t="s">
-        <v>985</v>
+        <v>828</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -9020,7 +8408,7 @@
         <v>700</v>
       </c>
       <c r="G222" t="s">
-        <v>873</v>
+        <v>824</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -9040,7 +8428,7 @@
         <v>640</v>
       </c>
       <c r="G223" t="s">
-        <v>986</v>
+        <v>840</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -9063,7 +8451,7 @@
         <v>748</v>
       </c>
       <c r="G224" t="s">
-        <v>987</v>
+        <v>824</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -9086,7 +8474,7 @@
         <v>646</v>
       </c>
       <c r="G225" t="s">
-        <v>841</v>
+        <v>815</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -9109,7 +8497,7 @@
         <v>657</v>
       </c>
       <c r="G226" t="s">
-        <v>899</v>
+        <v>822</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -9132,7 +8520,7 @@
         <v>653</v>
       </c>
       <c r="G227" t="s">
-        <v>964</v>
+        <v>870</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -9155,7 +8543,7 @@
         <v>653</v>
       </c>
       <c r="G228" t="s">
-        <v>943</v>
+        <v>824</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -9178,7 +8566,7 @@
         <v>665</v>
       </c>
       <c r="G229" t="s">
-        <v>829</v>
+        <v>846</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -9201,7 +8589,7 @@
         <v>749</v>
       </c>
       <c r="G230" t="s">
-        <v>988</v>
+        <v>827</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -9224,7 +8612,7 @@
         <v>688</v>
       </c>
       <c r="G231" t="s">
-        <v>989</v>
+        <v>904</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -9247,7 +8635,7 @@
         <v>657</v>
       </c>
       <c r="G232" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -9270,7 +8658,7 @@
         <v>750</v>
       </c>
       <c r="G233" t="s">
-        <v>990</v>
+        <v>820</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -9293,7 +8681,7 @@
         <v>653</v>
       </c>
       <c r="G234" t="s">
-        <v>991</v>
+        <v>905</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -9316,7 +8704,7 @@
         <v>640</v>
       </c>
       <c r="G235" t="s">
-        <v>992</v>
+        <v>840</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -9339,7 +8727,7 @@
         <v>657</v>
       </c>
       <c r="G236" t="s">
-        <v>922</v>
+        <v>824</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -9362,7 +8750,7 @@
         <v>717</v>
       </c>
       <c r="G237" t="s">
-        <v>911</v>
+        <v>824</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -9385,7 +8773,7 @@
         <v>638</v>
       </c>
       <c r="G238" t="s">
-        <v>993</v>
+        <v>843</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -9408,7 +8796,7 @@
         <v>683</v>
       </c>
       <c r="G239" t="s">
-        <v>994</v>
+        <v>906</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -9431,7 +8819,7 @@
         <v>641</v>
       </c>
       <c r="G240" t="s">
-        <v>934</v>
+        <v>822</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -9454,7 +8842,7 @@
         <v>751</v>
       </c>
       <c r="G241" t="s">
-        <v>995</v>
+        <v>824</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -9477,7 +8865,7 @@
         <v>700</v>
       </c>
       <c r="G242" t="s">
-        <v>944</v>
+        <v>907</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -9500,7 +8888,7 @@
         <v>749</v>
       </c>
       <c r="G243" t="s">
-        <v>873</v>
+        <v>822</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -9523,7 +8911,7 @@
         <v>665</v>
       </c>
       <c r="G244" t="s">
-        <v>996</v>
+        <v>908</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -9546,7 +8934,7 @@
         <v>700</v>
       </c>
       <c r="G245" t="s">
-        <v>997</v>
+        <v>886</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -9569,7 +8957,7 @@
         <v>651</v>
       </c>
       <c r="G246" t="s">
-        <v>998</v>
+        <v>824</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -9592,7 +8980,7 @@
         <v>653</v>
       </c>
       <c r="G247" t="s">
-        <v>999</v>
+        <v>826</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -9615,7 +9003,7 @@
         <v>752</v>
       </c>
       <c r="G248" t="s">
-        <v>1000</v>
+        <v>824</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -9638,7 +9026,7 @@
         <v>722</v>
       </c>
       <c r="G249" t="s">
-        <v>1001</v>
+        <v>819</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -9661,7 +9049,7 @@
         <v>715</v>
       </c>
       <c r="G250" t="s">
-        <v>923</v>
+        <v>856</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -9684,7 +9072,7 @@
         <v>638</v>
       </c>
       <c r="G251" t="s">
-        <v>1002</v>
+        <v>909</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -9707,7 +9095,7 @@
         <v>657</v>
       </c>
       <c r="G252" t="s">
-        <v>980</v>
+        <v>824</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -9730,7 +9118,7 @@
         <v>722</v>
       </c>
       <c r="G253" t="s">
-        <v>1003</v>
+        <v>815</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -9753,7 +9141,7 @@
         <v>641</v>
       </c>
       <c r="G254" t="s">
-        <v>1004</v>
+        <v>824</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -9776,7 +9164,7 @@
         <v>647</v>
       </c>
       <c r="G255" t="s">
-        <v>895</v>
+        <v>813</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -9799,7 +9187,7 @@
         <v>653</v>
       </c>
       <c r="G256" t="s">
-        <v>1005</v>
+        <v>910</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -9822,7 +9210,7 @@
         <v>641</v>
       </c>
       <c r="G257" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -9845,7 +9233,7 @@
         <v>702</v>
       </c>
       <c r="G258" t="s">
-        <v>874</v>
+        <v>824</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -9868,7 +9256,7 @@
         <v>653</v>
       </c>
       <c r="G259" t="s">
-        <v>1006</v>
+        <v>824</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -9891,7 +9279,7 @@
         <v>647</v>
       </c>
       <c r="G260" t="s">
-        <v>918</v>
+        <v>824</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -9914,7 +9302,7 @@
         <v>665</v>
       </c>
       <c r="G261" t="s">
-        <v>1007</v>
+        <v>824</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -9937,7 +9325,7 @@
         <v>657</v>
       </c>
       <c r="G262" t="s">
-        <v>1008</v>
+        <v>911</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -9960,7 +9348,7 @@
         <v>753</v>
       </c>
       <c r="G263" t="s">
-        <v>1009</v>
+        <v>912</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -9983,7 +9371,7 @@
         <v>657</v>
       </c>
       <c r="G264" t="s">
-        <v>1010</v>
+        <v>913</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -10003,10 +9391,10 @@
         <v>630</v>
       </c>
       <c r="F265" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="G265" t="s">
-        <v>829</v>
+        <v>856</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -10029,7 +9417,7 @@
         <v>754</v>
       </c>
       <c r="G266" t="s">
-        <v>1011</v>
+        <v>914</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -10052,7 +9440,7 @@
         <v>755</v>
       </c>
       <c r="G267" t="s">
-        <v>1012</v>
+        <v>821</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -10075,7 +9463,7 @@
         <v>709</v>
       </c>
       <c r="G268" t="s">
-        <v>1013</v>
+        <v>820</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -10098,7 +9486,7 @@
         <v>642</v>
       </c>
       <c r="G269" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -10121,7 +9509,7 @@
         <v>653</v>
       </c>
       <c r="G270" t="s">
-        <v>1014</v>
+        <v>846</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -10144,7 +9532,7 @@
         <v>727</v>
       </c>
       <c r="G271" t="s">
-        <v>941</v>
+        <v>824</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -10167,7 +9555,7 @@
         <v>756</v>
       </c>
       <c r="G272" t="s">
-        <v>948</v>
+        <v>824</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -10190,7 +9578,7 @@
         <v>653</v>
       </c>
       <c r="G273" t="s">
-        <v>893</v>
+        <v>828</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -10213,7 +9601,7 @@
         <v>757</v>
       </c>
       <c r="G274" t="s">
-        <v>1015</v>
+        <v>824</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -10236,7 +9624,7 @@
         <v>657</v>
       </c>
       <c r="G275" t="s">
-        <v>873</v>
+        <v>824</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -10259,7 +9647,7 @@
         <v>688</v>
       </c>
       <c r="G276" t="s">
-        <v>1016</v>
+        <v>915</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -10279,10 +9667,10 @@
         <v>624</v>
       </c>
       <c r="F277" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="G277" t="s">
-        <v>1017</v>
+        <v>916</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -10305,7 +9693,7 @@
         <v>653</v>
       </c>
       <c r="G278" t="s">
-        <v>1018</v>
+        <v>847</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -10328,7 +9716,7 @@
         <v>685</v>
       </c>
       <c r="G279" t="s">
-        <v>1019</v>
+        <v>824</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -10351,7 +9739,7 @@
         <v>668</v>
       </c>
       <c r="G280" t="s">
-        <v>847</v>
+        <v>824</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -10374,7 +9762,7 @@
         <v>653</v>
       </c>
       <c r="G281" t="s">
-        <v>1020</v>
+        <v>824</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -10397,7 +9785,7 @@
         <v>758</v>
       </c>
       <c r="G282" t="s">
-        <v>1021</v>
+        <v>863</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -10420,7 +9808,7 @@
         <v>759</v>
       </c>
       <c r="G283" t="s">
-        <v>1022</v>
+        <v>821</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -10443,7 +9831,7 @@
         <v>652</v>
       </c>
       <c r="G284" t="s">
-        <v>874</v>
+        <v>917</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -10466,7 +9854,7 @@
         <v>702</v>
       </c>
       <c r="G285" t="s">
-        <v>1023</v>
+        <v>860</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -10489,7 +9877,7 @@
         <v>652</v>
       </c>
       <c r="G286" t="s">
-        <v>880</v>
+        <v>819</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -10512,7 +9900,7 @@
         <v>673</v>
       </c>
       <c r="G287" t="s">
-        <v>847</v>
+        <v>824</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -10535,7 +9923,7 @@
         <v>652</v>
       </c>
       <c r="G288" t="s">
-        <v>847</v>
+        <v>824</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -10558,7 +9946,7 @@
         <v>760</v>
       </c>
       <c r="G289" t="s">
-        <v>1024</v>
+        <v>840</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -10581,7 +9969,7 @@
         <v>680</v>
       </c>
       <c r="G290" t="s">
-        <v>1025</v>
+        <v>824</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -10604,7 +9992,7 @@
         <v>652</v>
       </c>
       <c r="G291" t="s">
-        <v>1026</v>
+        <v>918</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -10627,7 +10015,7 @@
         <v>647</v>
       </c>
       <c r="G292" t="s">
-        <v>849</v>
+        <v>813</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -10650,7 +10038,7 @@
         <v>640</v>
       </c>
       <c r="G293" t="s">
-        <v>1027</v>
+        <v>919</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -10673,7 +10061,7 @@
         <v>646</v>
       </c>
       <c r="G294" t="s">
-        <v>910</v>
+        <v>920</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -10696,7 +10084,7 @@
         <v>653</v>
       </c>
       <c r="G295" t="s">
-        <v>1028</v>
+        <v>826</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -10719,7 +10107,7 @@
         <v>662</v>
       </c>
       <c r="G296" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
     </row>
     <row r="297" spans="1:7">
@@ -10742,7 +10130,7 @@
         <v>761</v>
       </c>
       <c r="G297" t="s">
-        <v>1029</v>
+        <v>824</v>
       </c>
     </row>
     <row r="298" spans="1:7">
@@ -10765,7 +10153,7 @@
         <v>650</v>
       </c>
       <c r="G298" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="299" spans="1:7">
@@ -10788,7 +10176,7 @@
         <v>762</v>
       </c>
       <c r="G299" t="s">
-        <v>1030</v>
+        <v>870</v>
       </c>
     </row>
     <row r="300" spans="1:7">
@@ -10811,7 +10199,7 @@
         <v>763</v>
       </c>
       <c r="G300" t="s">
-        <v>1031</v>
+        <v>921</v>
       </c>
     </row>
     <row r="301" spans="1:7">
@@ -10834,7 +10222,7 @@
         <v>665</v>
       </c>
       <c r="G301" t="s">
-        <v>1032</v>
+        <v>819</v>
       </c>
     </row>
     <row r="302" spans="1:7">
@@ -10857,7 +10245,7 @@
         <v>764</v>
       </c>
       <c r="G302" t="s">
-        <v>1033</v>
+        <v>844</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -10880,7 +10268,7 @@
         <v>744</v>
       </c>
       <c r="G303" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
     </row>
     <row r="304" spans="1:7">
@@ -10903,7 +10291,7 @@
         <v>641</v>
       </c>
       <c r="G304" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
     </row>
     <row r="305" spans="1:7">
@@ -10926,7 +10314,7 @@
         <v>662</v>
       </c>
       <c r="G305" t="s">
-        <v>893</v>
+        <v>833</v>
       </c>
     </row>
     <row r="306" spans="1:7">
@@ -10949,7 +10337,7 @@
         <v>765</v>
       </c>
       <c r="G306" t="s">
-        <v>1034</v>
+        <v>922</v>
       </c>
     </row>
     <row r="307" spans="1:7">
@@ -10972,7 +10360,7 @@
         <v>766</v>
       </c>
       <c r="G307" t="s">
-        <v>1035</v>
+        <v>828</v>
       </c>
     </row>
     <row r="308" spans="1:7">
@@ -10995,7 +10383,7 @@
         <v>761</v>
       </c>
       <c r="G308" t="s">
-        <v>1036</v>
+        <v>870</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -11018,7 +10406,7 @@
         <v>652</v>
       </c>
       <c r="G309" t="s">
-        <v>1037</v>
+        <v>906</v>
       </c>
     </row>
     <row r="310" spans="1:7">
@@ -11041,7 +10429,7 @@
         <v>653</v>
       </c>
       <c r="G310" t="s">
-        <v>1038</v>
+        <v>815</v>
       </c>
     </row>
     <row r="311" spans="1:7">
@@ -11064,7 +10452,7 @@
         <v>767</v>
       </c>
       <c r="G311" t="s">
-        <v>1039</v>
+        <v>923</v>
       </c>
     </row>
     <row r="312" spans="1:7">
@@ -11087,7 +10475,7 @@
         <v>640</v>
       </c>
       <c r="G312" t="s">
-        <v>1030</v>
+        <v>821</v>
       </c>
     </row>
     <row r="313" spans="1:7">
@@ -11110,7 +10498,7 @@
         <v>702</v>
       </c>
       <c r="G313" t="s">
-        <v>1040</v>
+        <v>859</v>
       </c>
     </row>
     <row r="314" spans="1:7">
@@ -11133,7 +10521,7 @@
         <v>684</v>
       </c>
       <c r="G314" t="s">
-        <v>1041</v>
+        <v>843</v>
       </c>
     </row>
     <row r="315" spans="1:7">
@@ -11156,7 +10544,7 @@
         <v>699</v>
       </c>
       <c r="G315" t="s">
-        <v>1042</v>
+        <v>832</v>
       </c>
     </row>
     <row r="316" spans="1:7">
@@ -11179,7 +10567,7 @@
         <v>657</v>
       </c>
       <c r="G316" t="s">
-        <v>907</v>
+        <v>840</v>
       </c>
     </row>
     <row r="317" spans="1:7">
@@ -11202,7 +10590,7 @@
         <v>653</v>
       </c>
       <c r="G317" t="s">
-        <v>877</v>
+        <v>821</v>
       </c>
     </row>
     <row r="318" spans="1:7">
@@ -11225,7 +10613,7 @@
         <v>653</v>
       </c>
       <c r="G318" t="s">
-        <v>1043</v>
+        <v>862</v>
       </c>
     </row>
     <row r="319" spans="1:7">
@@ -11248,7 +10636,7 @@
         <v>665</v>
       </c>
       <c r="G319" t="s">
-        <v>1044</v>
+        <v>862</v>
       </c>
     </row>
     <row r="320" spans="1:7">
@@ -11271,7 +10659,7 @@
         <v>649</v>
       </c>
       <c r="G320" t="s">
-        <v>874</v>
+        <v>824</v>
       </c>
     </row>
     <row r="321" spans="1:7">
@@ -11294,7 +10682,7 @@
         <v>657</v>
       </c>
       <c r="G321" t="s">
-        <v>1045</v>
+        <v>887</v>
       </c>
     </row>
     <row r="322" spans="1:7">
@@ -11317,7 +10705,7 @@
         <v>768</v>
       </c>
       <c r="G322" t="s">
-        <v>1046</v>
+        <v>924</v>
       </c>
     </row>
     <row r="323" spans="1:7">
@@ -11340,7 +10728,7 @@
         <v>641</v>
       </c>
       <c r="G323" t="s">
-        <v>873</v>
+        <v>822</v>
       </c>
     </row>
     <row r="324" spans="1:7">
@@ -11363,7 +10751,7 @@
         <v>722</v>
       </c>
       <c r="G324" t="s">
-        <v>1047</v>
+        <v>827</v>
       </c>
     </row>
     <row r="325" spans="1:7">
@@ -11386,7 +10774,7 @@
         <v>744</v>
       </c>
       <c r="G325" t="s">
-        <v>1048</v>
+        <v>824</v>
       </c>
     </row>
     <row r="326" spans="1:7">
@@ -11409,7 +10797,7 @@
         <v>649</v>
       </c>
       <c r="G326" t="s">
-        <v>1049</v>
+        <v>824</v>
       </c>
     </row>
     <row r="327" spans="1:7">
@@ -11432,7 +10820,7 @@
         <v>647</v>
       </c>
       <c r="G327" t="s">
-        <v>1050</v>
+        <v>824</v>
       </c>
     </row>
     <row r="328" spans="1:7">
@@ -11455,7 +10843,7 @@
         <v>657</v>
       </c>
       <c r="G328" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
     </row>
     <row r="329" spans="1:7">
@@ -11478,7 +10866,7 @@
         <v>665</v>
       </c>
       <c r="G329" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
     </row>
     <row r="330" spans="1:7">
@@ -11501,7 +10889,7 @@
         <v>769</v>
       </c>
       <c r="G330" t="s">
-        <v>1051</v>
+        <v>824</v>
       </c>
     </row>
     <row r="331" spans="1:7">
@@ -11524,7 +10912,7 @@
         <v>653</v>
       </c>
       <c r="G331" t="s">
-        <v>908</v>
+        <v>925</v>
       </c>
     </row>
     <row r="332" spans="1:7">
@@ -11547,7 +10935,7 @@
         <v>680</v>
       </c>
       <c r="G332" t="s">
-        <v>1052</v>
+        <v>926</v>
       </c>
     </row>
     <row r="333" spans="1:7">
@@ -11570,7 +10958,7 @@
         <v>770</v>
       </c>
       <c r="G333" t="s">
-        <v>1053</v>
+        <v>829</v>
       </c>
     </row>
     <row r="334" spans="1:7">
@@ -11593,7 +10981,7 @@
         <v>685</v>
       </c>
       <c r="G334" t="s">
-        <v>815</v>
+        <v>870</v>
       </c>
     </row>
     <row r="335" spans="1:7">
@@ -11616,7 +11004,7 @@
         <v>653</v>
       </c>
       <c r="G335" t="s">
-        <v>1054</v>
+        <v>824</v>
       </c>
     </row>
     <row r="336" spans="1:7">
@@ -11639,7 +11027,7 @@
         <v>771</v>
       </c>
       <c r="G336" t="s">
-        <v>1055</v>
+        <v>833</v>
       </c>
     </row>
     <row r="337" spans="1:7">
@@ -11662,7 +11050,7 @@
         <v>657</v>
       </c>
       <c r="G337" t="s">
-        <v>1056</v>
+        <v>927</v>
       </c>
     </row>
     <row r="338" spans="1:7">
@@ -11685,7 +11073,7 @@
         <v>685</v>
       </c>
       <c r="G338" t="s">
-        <v>998</v>
+        <v>834</v>
       </c>
     </row>
     <row r="339" spans="1:7">
@@ -11708,7 +11096,7 @@
         <v>772</v>
       </c>
       <c r="G339" t="s">
-        <v>1057</v>
+        <v>843</v>
       </c>
     </row>
     <row r="340" spans="1:7">
@@ -11731,7 +11119,7 @@
         <v>773</v>
       </c>
       <c r="G340" t="s">
-        <v>1058</v>
+        <v>824</v>
       </c>
     </row>
     <row r="341" spans="1:7">
@@ -11754,7 +11142,7 @@
         <v>649</v>
       </c>
       <c r="G341" t="s">
-        <v>1059</v>
+        <v>824</v>
       </c>
     </row>
     <row r="342" spans="1:7">
@@ -11777,7 +11165,7 @@
         <v>656</v>
       </c>
       <c r="G342" t="s">
-        <v>1060</v>
+        <v>870</v>
       </c>
     </row>
     <row r="343" spans="1:7">
@@ -11800,7 +11188,7 @@
         <v>774</v>
       </c>
       <c r="G343" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
     </row>
     <row r="344" spans="1:7">
@@ -11823,7 +11211,7 @@
         <v>691</v>
       </c>
       <c r="G344" t="s">
-        <v>1038</v>
+        <v>856</v>
       </c>
     </row>
     <row r="345" spans="1:7">
@@ -11846,7 +11234,7 @@
         <v>775</v>
       </c>
       <c r="G345" t="s">
-        <v>1061</v>
+        <v>846</v>
       </c>
     </row>
     <row r="346" spans="1:7">
@@ -11869,7 +11257,7 @@
         <v>776</v>
       </c>
       <c r="G346" t="s">
-        <v>874</v>
+        <v>840</v>
       </c>
     </row>
     <row r="347" spans="1:7">
@@ -11915,7 +11303,7 @@
         <v>640</v>
       </c>
       <c r="G348" t="s">
-        <v>1062</v>
+        <v>928</v>
       </c>
     </row>
     <row r="349" spans="1:7">
@@ -11938,7 +11326,7 @@
         <v>665</v>
       </c>
       <c r="G349" t="s">
-        <v>1063</v>
+        <v>815</v>
       </c>
     </row>
     <row r="350" spans="1:7">
@@ -11961,7 +11349,7 @@
         <v>652</v>
       </c>
       <c r="G350" t="s">
-        <v>829</v>
+        <v>846</v>
       </c>
     </row>
     <row r="351" spans="1:7">
@@ -11984,7 +11372,7 @@
         <v>777</v>
       </c>
       <c r="G351" t="s">
-        <v>1064</v>
+        <v>929</v>
       </c>
     </row>
     <row r="352" spans="1:7">
@@ -12007,7 +11395,7 @@
         <v>658</v>
       </c>
       <c r="G352" t="s">
-        <v>1065</v>
+        <v>824</v>
       </c>
     </row>
     <row r="353" spans="1:7">
@@ -12030,7 +11418,7 @@
         <v>700</v>
       </c>
       <c r="G353" t="s">
-        <v>1049</v>
+        <v>856</v>
       </c>
     </row>
     <row r="354" spans="1:7">
@@ -12053,7 +11441,7 @@
         <v>636</v>
       </c>
       <c r="G354" t="s">
-        <v>1066</v>
+        <v>819</v>
       </c>
     </row>
     <row r="355" spans="1:7">
@@ -12076,7 +11464,7 @@
         <v>668</v>
       </c>
       <c r="G355" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
     </row>
     <row r="356" spans="1:7">
@@ -12099,7 +11487,7 @@
         <v>778</v>
       </c>
       <c r="G356" t="s">
-        <v>1067</v>
+        <v>910</v>
       </c>
     </row>
     <row r="357" spans="1:7">
@@ -12122,7 +11510,7 @@
         <v>705</v>
       </c>
       <c r="G357" t="s">
-        <v>1068</v>
+        <v>826</v>
       </c>
     </row>
     <row r="358" spans="1:7">
@@ -12145,7 +11533,7 @@
         <v>652</v>
       </c>
       <c r="G358" t="s">
-        <v>1069</v>
+        <v>824</v>
       </c>
     </row>
     <row r="359" spans="1:7">
@@ -12168,7 +11556,7 @@
         <v>652</v>
       </c>
       <c r="G359" t="s">
-        <v>1070</v>
+        <v>930</v>
       </c>
     </row>
     <row r="360" spans="1:7">
@@ -12191,7 +11579,7 @@
         <v>779</v>
       </c>
       <c r="G360" t="s">
-        <v>844</v>
+        <v>819</v>
       </c>
     </row>
     <row r="361" spans="1:7">
@@ -12214,7 +11602,7 @@
         <v>649</v>
       </c>
       <c r="G361" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
     </row>
     <row r="362" spans="1:7">
@@ -12237,7 +11625,7 @@
         <v>780</v>
       </c>
       <c r="G362" t="s">
-        <v>841</v>
+        <v>832</v>
       </c>
     </row>
     <row r="363" spans="1:7">
@@ -12260,7 +11648,7 @@
         <v>653</v>
       </c>
       <c r="G363" t="s">
-        <v>1071</v>
+        <v>931</v>
       </c>
     </row>
     <row r="364" spans="1:7">
@@ -12283,7 +11671,7 @@
         <v>640</v>
       </c>
       <c r="G364" t="s">
-        <v>849</v>
+        <v>824</v>
       </c>
     </row>
     <row r="365" spans="1:7">
@@ -12306,7 +11694,7 @@
         <v>652</v>
       </c>
       <c r="G365" t="s">
-        <v>1072</v>
+        <v>824</v>
       </c>
     </row>
     <row r="366" spans="1:7">
@@ -12329,7 +11717,7 @@
         <v>653</v>
       </c>
       <c r="G366" t="s">
-        <v>1073</v>
+        <v>932</v>
       </c>
     </row>
     <row r="367" spans="1:7">
@@ -12352,7 +11740,7 @@
         <v>781</v>
       </c>
       <c r="G367" t="s">
-        <v>1074</v>
+        <v>924</v>
       </c>
     </row>
     <row r="368" spans="1:7">
@@ -12375,7 +11763,7 @@
         <v>691</v>
       </c>
       <c r="G368" t="s">
-        <v>874</v>
+        <v>824</v>
       </c>
     </row>
     <row r="369" spans="1:7">
@@ -12398,7 +11786,7 @@
         <v>780</v>
       </c>
       <c r="G369" t="s">
-        <v>847</v>
+        <v>933</v>
       </c>
     </row>
     <row r="370" spans="1:7">
@@ -12421,7 +11809,7 @@
         <v>653</v>
       </c>
       <c r="G370" t="s">
-        <v>1075</v>
+        <v>894</v>
       </c>
     </row>
     <row r="371" spans="1:7">
@@ -12444,7 +11832,7 @@
         <v>647</v>
       </c>
       <c r="G371" t="s">
-        <v>994</v>
+        <v>934</v>
       </c>
     </row>
     <row r="372" spans="1:7">
@@ -12467,7 +11855,7 @@
         <v>653</v>
       </c>
       <c r="G372" t="s">
-        <v>1076</v>
+        <v>935</v>
       </c>
     </row>
     <row r="373" spans="1:7">
@@ -12490,7 +11878,7 @@
         <v>653</v>
       </c>
       <c r="G373" t="s">
-        <v>1077</v>
+        <v>832</v>
       </c>
     </row>
     <row r="374" spans="1:7">
@@ -12513,7 +11901,7 @@
         <v>657</v>
       </c>
       <c r="G374" t="s">
-        <v>1078</v>
+        <v>936</v>
       </c>
     </row>
     <row r="375" spans="1:7">
@@ -12536,7 +11924,7 @@
         <v>657</v>
       </c>
       <c r="G375" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
     </row>
     <row r="376" spans="1:7">
@@ -12559,7 +11947,7 @@
         <v>665</v>
       </c>
       <c r="G376" t="s">
-        <v>1079</v>
+        <v>937</v>
       </c>
     </row>
     <row r="377" spans="1:7">
@@ -12582,7 +11970,7 @@
         <v>700</v>
       </c>
       <c r="G377" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
     </row>
     <row r="378" spans="1:7">
@@ -12605,7 +11993,7 @@
         <v>642</v>
       </c>
       <c r="G378" t="s">
-        <v>1080</v>
+        <v>886</v>
       </c>
     </row>
     <row r="379" spans="1:7">
@@ -12628,7 +12016,7 @@
         <v>782</v>
       </c>
       <c r="G379" t="s">
-        <v>1081</v>
+        <v>815</v>
       </c>
     </row>
     <row r="380" spans="1:7">
@@ -12651,7 +12039,7 @@
         <v>758</v>
       </c>
       <c r="G380" t="s">
-        <v>1082</v>
+        <v>938</v>
       </c>
     </row>
     <row r="381" spans="1:7">
@@ -12674,7 +12062,7 @@
         <v>652</v>
       </c>
       <c r="G381" t="s">
-        <v>817</v>
+        <v>939</v>
       </c>
     </row>
     <row r="382" spans="1:7">
@@ -12697,7 +12085,7 @@
         <v>652</v>
       </c>
       <c r="G382" t="s">
-        <v>1083</v>
+        <v>819</v>
       </c>
     </row>
     <row r="383" spans="1:7">
@@ -12720,7 +12108,7 @@
         <v>697</v>
       </c>
       <c r="G383" t="s">
-        <v>1084</v>
+        <v>862</v>
       </c>
     </row>
     <row r="384" spans="1:7">
@@ -12743,7 +12131,7 @@
         <v>647</v>
       </c>
       <c r="G384" t="s">
-        <v>1085</v>
+        <v>940</v>
       </c>
     </row>
     <row r="385" spans="1:7">
@@ -12763,7 +12151,7 @@
         <v>783</v>
       </c>
       <c r="G385" t="s">
-        <v>844</v>
+        <v>820</v>
       </c>
     </row>
     <row r="386" spans="1:7">
@@ -12786,7 +12174,7 @@
         <v>653</v>
       </c>
       <c r="G386" t="s">
-        <v>1086</v>
+        <v>824</v>
       </c>
     </row>
     <row r="387" spans="1:7">
@@ -12809,7 +12197,7 @@
         <v>658</v>
       </c>
       <c r="G387" t="s">
-        <v>1087</v>
+        <v>843</v>
       </c>
     </row>
     <row r="388" spans="1:7">
@@ -12832,7 +12220,7 @@
         <v>640</v>
       </c>
       <c r="G388" t="s">
-        <v>1088</v>
+        <v>941</v>
       </c>
     </row>
     <row r="389" spans="1:7">
@@ -12855,7 +12243,7 @@
         <v>657</v>
       </c>
       <c r="G389" t="s">
-        <v>1089</v>
+        <v>824</v>
       </c>
     </row>
     <row r="390" spans="1:7">
@@ -12878,7 +12266,7 @@
         <v>641</v>
       </c>
       <c r="G390" t="s">
-        <v>1090</v>
+        <v>819</v>
       </c>
     </row>
     <row r="391" spans="1:7">
@@ -12901,7 +12289,7 @@
         <v>680</v>
       </c>
       <c r="G391" t="s">
-        <v>1091</v>
+        <v>942</v>
       </c>
     </row>
     <row r="392" spans="1:7">
@@ -12924,7 +12312,7 @@
         <v>702</v>
       </c>
       <c r="G392" t="s">
-        <v>965</v>
+        <v>815</v>
       </c>
     </row>
     <row r="393" spans="1:7">
@@ -12947,7 +12335,7 @@
         <v>702</v>
       </c>
       <c r="G393" t="s">
-        <v>1036</v>
+        <v>819</v>
       </c>
     </row>
     <row r="394" spans="1:7">
@@ -12970,7 +12358,7 @@
         <v>784</v>
       </c>
       <c r="G394" t="s">
-        <v>1092</v>
+        <v>931</v>
       </c>
     </row>
     <row r="395" spans="1:7">
@@ -12993,7 +12381,7 @@
         <v>785</v>
       </c>
       <c r="G395" t="s">
-        <v>1093</v>
+        <v>867</v>
       </c>
     </row>
     <row r="396" spans="1:7">
@@ -13016,7 +12404,7 @@
         <v>653</v>
       </c>
       <c r="G396" t="s">
-        <v>1094</v>
+        <v>821</v>
       </c>
     </row>
     <row r="397" spans="1:7">
@@ -13039,7 +12427,7 @@
         <v>652</v>
       </c>
       <c r="G397" t="s">
-        <v>1095</v>
+        <v>943</v>
       </c>
     </row>
     <row r="398" spans="1:7">
@@ -13062,7 +12450,7 @@
         <v>739</v>
       </c>
       <c r="G398" t="s">
-        <v>1096</v>
+        <v>944</v>
       </c>
     </row>
     <row r="399" spans="1:7">
@@ -13085,7 +12473,7 @@
         <v>653</v>
       </c>
       <c r="G399" t="s">
-        <v>1097</v>
+        <v>945</v>
       </c>
     </row>
     <row r="400" spans="1:7">
@@ -13108,7 +12496,7 @@
         <v>653</v>
       </c>
       <c r="G400" t="s">
-        <v>1098</v>
+        <v>946</v>
       </c>
     </row>
     <row r="401" spans="1:7">
@@ -13131,7 +12519,7 @@
         <v>653</v>
       </c>
       <c r="G401" t="s">
-        <v>1063</v>
+        <v>815</v>
       </c>
     </row>
     <row r="402" spans="1:7">
@@ -13154,7 +12542,7 @@
         <v>786</v>
       </c>
       <c r="G402" t="s">
-        <v>1099</v>
+        <v>824</v>
       </c>
     </row>
     <row r="403" spans="1:7">
@@ -13177,7 +12565,7 @@
         <v>665</v>
       </c>
       <c r="G403" t="s">
-        <v>1100</v>
+        <v>947</v>
       </c>
     </row>
     <row r="404" spans="1:7">
@@ -13200,7 +12588,7 @@
         <v>646</v>
       </c>
       <c r="G404" t="s">
-        <v>1095</v>
+        <v>948</v>
       </c>
     </row>
     <row r="405" spans="1:7">
@@ -13223,7 +12611,7 @@
         <v>744</v>
       </c>
       <c r="G405" t="s">
-        <v>1101</v>
+        <v>894</v>
       </c>
     </row>
     <row r="406" spans="1:7">
@@ -13246,7 +12634,7 @@
         <v>640</v>
       </c>
       <c r="G406" t="s">
-        <v>1020</v>
+        <v>815</v>
       </c>
     </row>
     <row r="407" spans="1:7">
@@ -13269,7 +12657,7 @@
         <v>653</v>
       </c>
       <c r="G407" t="s">
-        <v>1102</v>
+        <v>856</v>
       </c>
     </row>
     <row r="408" spans="1:7">
@@ -13292,7 +12680,7 @@
         <v>653</v>
       </c>
       <c r="G408" t="s">
-        <v>1103</v>
+        <v>821</v>
       </c>
     </row>
     <row r="409" spans="1:7">
@@ -13315,7 +12703,7 @@
         <v>787</v>
       </c>
       <c r="G409" t="s">
-        <v>1104</v>
+        <v>949</v>
       </c>
     </row>
     <row r="410" spans="1:7">
@@ -13338,7 +12726,7 @@
         <v>702</v>
       </c>
       <c r="G410" t="s">
-        <v>1048</v>
+        <v>824</v>
       </c>
     </row>
     <row r="411" spans="1:7">
@@ -13361,7 +12749,7 @@
         <v>788</v>
       </c>
       <c r="G411" t="s">
-        <v>1105</v>
+        <v>819</v>
       </c>
     </row>
     <row r="412" spans="1:7">
@@ -13384,7 +12772,7 @@
         <v>683</v>
       </c>
       <c r="G412" t="s">
-        <v>1106</v>
+        <v>813</v>
       </c>
     </row>
     <row r="413" spans="1:7">
@@ -13407,7 +12795,7 @@
         <v>702</v>
       </c>
       <c r="G413" t="s">
-        <v>1107</v>
+        <v>950</v>
       </c>
     </row>
     <row r="414" spans="1:7">
@@ -13430,7 +12818,7 @@
         <v>659</v>
       </c>
       <c r="G414" t="s">
-        <v>1108</v>
+        <v>922</v>
       </c>
     </row>
     <row r="415" spans="1:7">
@@ -13453,7 +12841,7 @@
         <v>642</v>
       </c>
       <c r="G415" t="s">
-        <v>1030</v>
+        <v>928</v>
       </c>
     </row>
     <row r="416" spans="1:7">
@@ -13476,7 +12864,7 @@
         <v>657</v>
       </c>
       <c r="G416" t="s">
-        <v>1109</v>
+        <v>835</v>
       </c>
     </row>
     <row r="417" spans="1:7">
@@ -13499,7 +12887,7 @@
         <v>653</v>
       </c>
       <c r="G417" t="s">
-        <v>1072</v>
+        <v>846</v>
       </c>
     </row>
     <row r="418" spans="1:7">
@@ -13522,7 +12910,7 @@
         <v>763</v>
       </c>
       <c r="G418" t="s">
-        <v>1110</v>
+        <v>951</v>
       </c>
     </row>
     <row r="419" spans="1:7">
@@ -13545,7 +12933,7 @@
         <v>699</v>
       </c>
       <c r="G419" t="s">
-        <v>1111</v>
+        <v>834</v>
       </c>
     </row>
     <row r="420" spans="1:7">
@@ -13568,7 +12956,7 @@
         <v>789</v>
       </c>
       <c r="G420" t="s">
-        <v>1112</v>
+        <v>952</v>
       </c>
     </row>
     <row r="421" spans="1:7">
@@ -13591,7 +12979,7 @@
         <v>653</v>
       </c>
       <c r="G421" t="s">
-        <v>1113</v>
+        <v>819</v>
       </c>
     </row>
     <row r="422" spans="1:7">
@@ -13614,7 +13002,7 @@
         <v>640</v>
       </c>
       <c r="G422" t="s">
-        <v>1114</v>
+        <v>920</v>
       </c>
     </row>
     <row r="423" spans="1:7">
@@ -13637,7 +13025,7 @@
         <v>649</v>
       </c>
       <c r="G423" t="s">
-        <v>1065</v>
+        <v>824</v>
       </c>
     </row>
     <row r="424" spans="1:7">
@@ -13660,7 +13048,7 @@
         <v>658</v>
       </c>
       <c r="G424" t="s">
-        <v>936</v>
+        <v>953</v>
       </c>
     </row>
     <row r="425" spans="1:7">
@@ -13683,7 +13071,7 @@
         <v>653</v>
       </c>
       <c r="G425" t="s">
-        <v>1115</v>
+        <v>954</v>
       </c>
     </row>
     <row r="426" spans="1:7">
@@ -13706,7 +13094,7 @@
         <v>766</v>
       </c>
       <c r="G426" t="s">
-        <v>1116</v>
+        <v>955</v>
       </c>
     </row>
     <row r="427" spans="1:7">
@@ -13729,7 +13117,7 @@
         <v>665</v>
       </c>
       <c r="G427" t="s">
-        <v>1117</v>
+        <v>819</v>
       </c>
     </row>
     <row r="428" spans="1:7">
@@ -13752,7 +13140,7 @@
         <v>790</v>
       </c>
       <c r="G428" t="s">
-        <v>1118</v>
+        <v>819</v>
       </c>
     </row>
     <row r="429" spans="1:7">
@@ -13798,7 +13186,7 @@
         <v>685</v>
       </c>
       <c r="G430" t="s">
-        <v>1094</v>
+        <v>833</v>
       </c>
     </row>
     <row r="431" spans="1:7">
@@ -13821,7 +13209,7 @@
         <v>665</v>
       </c>
       <c r="G431" t="s">
-        <v>878</v>
+        <v>825</v>
       </c>
     </row>
     <row r="432" spans="1:7">
@@ -13844,7 +13232,7 @@
         <v>697</v>
       </c>
       <c r="G432" t="s">
-        <v>1119</v>
+        <v>828</v>
       </c>
     </row>
     <row r="433" spans="1:7">
@@ -13867,7 +13255,7 @@
         <v>705</v>
       </c>
       <c r="G433" t="s">
-        <v>922</v>
+        <v>821</v>
       </c>
     </row>
     <row r="434" spans="1:7">
@@ -13890,7 +13278,7 @@
         <v>727</v>
       </c>
       <c r="G434" t="s">
-        <v>1120</v>
+        <v>928</v>
       </c>
     </row>
     <row r="435" spans="1:7">
@@ -13913,7 +13301,7 @@
         <v>791</v>
       </c>
       <c r="G435" t="s">
-        <v>1121</v>
+        <v>956</v>
       </c>
     </row>
     <row r="436" spans="1:7">
@@ -13936,7 +13324,7 @@
         <v>690</v>
       </c>
       <c r="G436" t="s">
-        <v>837</v>
+        <v>870</v>
       </c>
     </row>
     <row r="437" spans="1:7">
@@ -13959,7 +13347,7 @@
         <v>710</v>
       </c>
       <c r="G437" t="s">
-        <v>1122</v>
+        <v>957</v>
       </c>
     </row>
     <row r="438" spans="1:7">
@@ -13982,7 +13370,7 @@
         <v>649</v>
       </c>
       <c r="G438" t="s">
-        <v>1123</v>
+        <v>832</v>
       </c>
     </row>
     <row r="439" spans="1:7">
@@ -14005,7 +13393,7 @@
         <v>792</v>
       </c>
       <c r="G439" t="s">
-        <v>1124</v>
+        <v>846</v>
       </c>
     </row>
     <row r="440" spans="1:7">
@@ -14028,7 +13416,7 @@
         <v>665</v>
       </c>
       <c r="G440" t="s">
-        <v>874</v>
+        <v>815</v>
       </c>
     </row>
     <row r="441" spans="1:7">
@@ -14047,9 +13435,6 @@
       <c r="E441" t="s">
         <v>629</v>
       </c>
-      <c r="F441" t="s">
-        <v>638</v>
-      </c>
       <c r="G441" t="s">
         <v>820</v>
       </c>
@@ -14074,7 +13459,7 @@
         <v>649</v>
       </c>
       <c r="G442" t="s">
-        <v>874</v>
+        <v>827</v>
       </c>
     </row>
     <row r="443" spans="1:7">
@@ -14097,7 +13482,7 @@
         <v>725</v>
       </c>
       <c r="G443" t="s">
-        <v>1125</v>
+        <v>958</v>
       </c>
     </row>
     <row r="444" spans="1:7">
@@ -14120,7 +13505,7 @@
         <v>793</v>
       </c>
       <c r="G444" t="s">
-        <v>1126</v>
+        <v>959</v>
       </c>
     </row>
     <row r="445" spans="1:7">
@@ -14143,7 +13528,7 @@
         <v>653</v>
       </c>
       <c r="G445" t="s">
-        <v>1127</v>
+        <v>824</v>
       </c>
     </row>
     <row r="446" spans="1:7">
@@ -14166,7 +13551,7 @@
         <v>652</v>
       </c>
       <c r="G446" t="s">
-        <v>1128</v>
+        <v>819</v>
       </c>
     </row>
     <row r="447" spans="1:7">
@@ -14189,7 +13574,7 @@
         <v>794</v>
       </c>
       <c r="G447" t="s">
-        <v>964</v>
+        <v>824</v>
       </c>
     </row>
     <row r="448" spans="1:7">
@@ -14212,7 +13597,7 @@
         <v>710</v>
       </c>
       <c r="G448" t="s">
-        <v>1129</v>
+        <v>871</v>
       </c>
     </row>
     <row r="449" spans="1:7">
@@ -14235,7 +13620,7 @@
         <v>653</v>
       </c>
       <c r="G449" t="s">
-        <v>986</v>
+        <v>846</v>
       </c>
     </row>
     <row r="450" spans="1:7">
@@ -14258,7 +13643,7 @@
         <v>665</v>
       </c>
       <c r="G450" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
     </row>
     <row r="451" spans="1:7">
@@ -14281,7 +13666,7 @@
         <v>652</v>
       </c>
       <c r="G451" t="s">
-        <v>844</v>
+        <v>961</v>
       </c>
     </row>
     <row r="452" spans="1:7">
@@ -14304,7 +13689,7 @@
         <v>762</v>
       </c>
       <c r="G452" t="s">
-        <v>1130</v>
+        <v>962</v>
       </c>
     </row>
     <row r="453" spans="1:7">
@@ -14327,7 +13712,7 @@
         <v>795</v>
       </c>
       <c r="G453" t="s">
-        <v>1131</v>
+        <v>963</v>
       </c>
     </row>
     <row r="454" spans="1:7">
@@ -14350,7 +13735,7 @@
         <v>665</v>
       </c>
       <c r="G454" t="s">
-        <v>1132</v>
+        <v>964</v>
       </c>
     </row>
     <row r="455" spans="1:7">
@@ -14373,7 +13758,7 @@
         <v>796</v>
       </c>
       <c r="G455" t="s">
-        <v>1133</v>
+        <v>902</v>
       </c>
     </row>
     <row r="456" spans="1:7">
@@ -14396,7 +13781,7 @@
         <v>659</v>
       </c>
       <c r="G456" t="s">
-        <v>934</v>
+        <v>856</v>
       </c>
     </row>
     <row r="457" spans="1:7">
@@ -14419,7 +13804,7 @@
         <v>723</v>
       </c>
       <c r="G457" t="s">
-        <v>1134</v>
+        <v>824</v>
       </c>
     </row>
     <row r="458" spans="1:7">
@@ -14442,7 +13827,7 @@
         <v>702</v>
       </c>
       <c r="G458" t="s">
-        <v>1135</v>
+        <v>881</v>
       </c>
     </row>
     <row r="459" spans="1:7">
@@ -14465,7 +13850,7 @@
         <v>767</v>
       </c>
       <c r="G459" t="s">
-        <v>1136</v>
+        <v>881</v>
       </c>
     </row>
     <row r="460" spans="1:7">
@@ -14488,7 +13873,7 @@
         <v>667</v>
       </c>
       <c r="G460" t="s">
-        <v>1137</v>
+        <v>955</v>
       </c>
     </row>
     <row r="461" spans="1:7">
@@ -14511,7 +13896,7 @@
         <v>657</v>
       </c>
       <c r="G461" t="s">
-        <v>1138</v>
+        <v>840</v>
       </c>
     </row>
     <row r="462" spans="1:7">
@@ -14534,7 +13919,7 @@
         <v>797</v>
       </c>
       <c r="G462" t="s">
-        <v>847</v>
+        <v>824</v>
       </c>
     </row>
     <row r="463" spans="1:7">
@@ -14557,7 +13942,7 @@
         <v>667</v>
       </c>
       <c r="G463" t="s">
-        <v>1137</v>
+        <v>955</v>
       </c>
     </row>
     <row r="464" spans="1:7">
@@ -14580,7 +13965,7 @@
         <v>798</v>
       </c>
       <c r="G464" t="s">
-        <v>1139</v>
+        <v>858</v>
       </c>
     </row>
     <row r="465" spans="1:7">
@@ -14603,7 +13988,7 @@
         <v>653</v>
       </c>
       <c r="G465" t="s">
-        <v>1140</v>
+        <v>844</v>
       </c>
     </row>
     <row r="466" spans="1:7">
@@ -14626,7 +14011,7 @@
         <v>646</v>
       </c>
       <c r="G466" t="s">
-        <v>1141</v>
+        <v>965</v>
       </c>
     </row>
     <row r="467" spans="1:7">
@@ -14649,7 +14034,7 @@
         <v>657</v>
       </c>
       <c r="G467" t="s">
-        <v>1142</v>
+        <v>840</v>
       </c>
     </row>
     <row r="468" spans="1:7">
@@ -14672,7 +14057,7 @@
         <v>649</v>
       </c>
       <c r="G468" t="s">
-        <v>874</v>
+        <v>846</v>
       </c>
     </row>
     <row r="469" spans="1:7">
@@ -14695,7 +14080,7 @@
         <v>710</v>
       </c>
       <c r="G469" t="s">
-        <v>1143</v>
+        <v>966</v>
       </c>
     </row>
     <row r="470" spans="1:7">
@@ -14718,7 +14103,7 @@
         <v>657</v>
       </c>
       <c r="G470" t="s">
-        <v>1144</v>
+        <v>829</v>
       </c>
     </row>
     <row r="471" spans="1:7">
@@ -14741,7 +14126,7 @@
         <v>660</v>
       </c>
       <c r="G471" t="s">
-        <v>1023</v>
+        <v>860</v>
       </c>
     </row>
     <row r="472" spans="1:7">
@@ -14764,7 +14149,7 @@
         <v>799</v>
       </c>
       <c r="G472" t="s">
-        <v>916</v>
+        <v>824</v>
       </c>
     </row>
     <row r="473" spans="1:7">
@@ -14787,7 +14172,7 @@
         <v>705</v>
       </c>
       <c r="G473" t="s">
-        <v>899</v>
+        <v>824</v>
       </c>
     </row>
     <row r="474" spans="1:7">
@@ -14810,7 +14195,7 @@
         <v>702</v>
       </c>
       <c r="G474" t="s">
-        <v>844</v>
+        <v>827</v>
       </c>
     </row>
     <row r="475" spans="1:7">
@@ -14833,7 +14218,7 @@
         <v>774</v>
       </c>
       <c r="G475" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
     </row>
     <row r="476" spans="1:7">
@@ -14856,7 +14241,7 @@
         <v>697</v>
       </c>
       <c r="G476" t="s">
-        <v>1145</v>
+        <v>824</v>
       </c>
     </row>
     <row r="477" spans="1:7">
@@ -14879,7 +14264,7 @@
         <v>653</v>
       </c>
       <c r="G477" t="s">
-        <v>1146</v>
+        <v>826</v>
       </c>
     </row>
     <row r="478" spans="1:7">
@@ -14902,7 +14287,7 @@
         <v>665</v>
       </c>
       <c r="G478" t="s">
-        <v>1147</v>
+        <v>967</v>
       </c>
     </row>
     <row r="479" spans="1:7">
@@ -14925,7 +14310,7 @@
         <v>800</v>
       </c>
       <c r="G479" t="s">
-        <v>1148</v>
+        <v>816</v>
       </c>
     </row>
     <row r="480" spans="1:7">
@@ -14948,7 +14333,7 @@
         <v>659</v>
       </c>
       <c r="G480" t="s">
-        <v>1149</v>
+        <v>865</v>
       </c>
     </row>
     <row r="481" spans="1:7">
@@ -14971,7 +14356,7 @@
         <v>801</v>
       </c>
       <c r="G481" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
     </row>
     <row r="482" spans="1:7">
@@ -14994,7 +14379,7 @@
         <v>652</v>
       </c>
       <c r="G482" t="s">
-        <v>1050</v>
+        <v>820</v>
       </c>
     </row>
     <row r="483" spans="1:7">
@@ -15017,7 +14402,7 @@
         <v>659</v>
       </c>
       <c r="G483" t="s">
-        <v>1150</v>
+        <v>840</v>
       </c>
     </row>
     <row r="484" spans="1:7">
@@ -15040,7 +14425,7 @@
         <v>802</v>
       </c>
       <c r="G484" t="s">
-        <v>1151</v>
+        <v>968</v>
       </c>
     </row>
     <row r="485" spans="1:7">
@@ -15063,7 +14448,7 @@
         <v>685</v>
       </c>
       <c r="G485" t="s">
-        <v>948</v>
+        <v>824</v>
       </c>
     </row>
     <row r="486" spans="1:7">
@@ -15086,7 +14471,7 @@
         <v>803</v>
       </c>
       <c r="G486" t="s">
-        <v>847</v>
+        <v>969</v>
       </c>
     </row>
     <row r="487" spans="1:7">
@@ -15109,7 +14494,7 @@
         <v>766</v>
       </c>
       <c r="G487" t="s">
-        <v>867</v>
+        <v>820</v>
       </c>
     </row>
     <row r="488" spans="1:7">
@@ -15132,7 +14517,7 @@
         <v>804</v>
       </c>
       <c r="G488" t="s">
-        <v>1111</v>
+        <v>834</v>
       </c>
     </row>
     <row r="489" spans="1:7">
@@ -15155,7 +14540,7 @@
         <v>744</v>
       </c>
       <c r="G489" t="s">
-        <v>1152</v>
+        <v>833</v>
       </c>
     </row>
     <row r="490" spans="1:7">
@@ -15178,7 +14563,7 @@
         <v>805</v>
       </c>
       <c r="G490" t="s">
-        <v>936</v>
+        <v>824</v>
       </c>
     </row>
     <row r="491" spans="1:7">
@@ -15201,7 +14586,7 @@
         <v>684</v>
       </c>
       <c r="G491" t="s">
-        <v>1049</v>
+        <v>906</v>
       </c>
     </row>
     <row r="492" spans="1:7">
@@ -15224,7 +14609,7 @@
         <v>649</v>
       </c>
       <c r="G492" t="s">
-        <v>1153</v>
+        <v>819</v>
       </c>
     </row>
     <row r="493" spans="1:7">
@@ -15247,7 +14632,7 @@
         <v>691</v>
       </c>
       <c r="G493" t="s">
-        <v>1154</v>
+        <v>832</v>
       </c>
     </row>
     <row r="494" spans="1:7">
@@ -15270,7 +14655,7 @@
         <v>680</v>
       </c>
       <c r="G494" t="s">
-        <v>1155</v>
+        <v>824</v>
       </c>
     </row>
     <row r="495" spans="1:7">
@@ -15293,7 +14678,7 @@
         <v>653</v>
       </c>
       <c r="G495" t="s">
-        <v>899</v>
+        <v>832</v>
       </c>
     </row>
     <row r="496" spans="1:7">
@@ -15316,7 +14701,7 @@
         <v>658</v>
       </c>
       <c r="G496" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
     </row>
     <row r="497" spans="1:7">
@@ -15339,7 +14724,7 @@
         <v>655</v>
       </c>
       <c r="G497" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
     </row>
     <row r="498" spans="1:7">
@@ -15362,7 +14747,7 @@
         <v>657</v>
       </c>
       <c r="G498" t="s">
-        <v>1156</v>
+        <v>821</v>
       </c>
     </row>
     <row r="499" spans="1:7">
@@ -15385,7 +14770,7 @@
         <v>705</v>
       </c>
       <c r="G499" t="s">
-        <v>1157</v>
+        <v>824</v>
       </c>
     </row>
     <row r="500" spans="1:7">
@@ -15408,7 +14793,7 @@
         <v>641</v>
       </c>
       <c r="G500" t="s">
-        <v>1137</v>
+        <v>824</v>
       </c>
     </row>
     <row r="501" spans="1:7">
@@ -15428,10 +14813,10 @@
         <v>633</v>
       </c>
       <c r="F501" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="G501" t="s">
-        <v>1158</v>
+        <v>862</v>
       </c>
     </row>
     <row r="502" spans="1:7">
@@ -15451,10 +14836,10 @@
         <v>628</v>
       </c>
       <c r="F502" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="G502" t="s">
-        <v>1159</v>
+        <v>815</v>
       </c>
     </row>
     <row r="503" spans="1:7">
@@ -15477,7 +14862,7 @@
         <v>806</v>
       </c>
       <c r="G503" t="s">
-        <v>1160</v>
+        <v>827</v>
       </c>
     </row>
     <row r="504" spans="1:7">
@@ -15500,7 +14885,7 @@
         <v>653</v>
       </c>
       <c r="G504" t="s">
-        <v>1161</v>
+        <v>970</v>
       </c>
     </row>
     <row r="505" spans="1:7">
@@ -15523,7 +14908,7 @@
         <v>689</v>
       </c>
       <c r="G505" t="s">
-        <v>899</v>
+        <v>833</v>
       </c>
     </row>
     <row r="506" spans="1:7">
@@ -15546,7 +14931,7 @@
         <v>648</v>
       </c>
       <c r="G506" t="s">
-        <v>1162</v>
+        <v>971</v>
       </c>
     </row>
     <row r="507" spans="1:7">
@@ -15569,7 +14954,7 @@
         <v>807</v>
       </c>
       <c r="G507" t="s">
-        <v>1163</v>
+        <v>849</v>
       </c>
     </row>
     <row r="508" spans="1:7">
@@ -15592,7 +14977,7 @@
         <v>646</v>
       </c>
       <c r="G508" t="s">
-        <v>1164</v>
+        <v>870</v>
       </c>
     </row>
     <row r="509" spans="1:7">
@@ -15612,7 +14997,7 @@
         <v>723</v>
       </c>
       <c r="G509" t="s">
-        <v>1165</v>
+        <v>819</v>
       </c>
     </row>
     <row r="510" spans="1:7">
@@ -15635,7 +15020,7 @@
         <v>653</v>
       </c>
       <c r="G510" t="s">
-        <v>1166</v>
+        <v>827</v>
       </c>
     </row>
     <row r="511" spans="1:7">
@@ -15658,7 +15043,7 @@
         <v>773</v>
       </c>
       <c r="G511" t="s">
-        <v>877</v>
+        <v>824</v>
       </c>
     </row>
     <row r="512" spans="1:7">
@@ -15681,7 +15066,7 @@
         <v>655</v>
       </c>
       <c r="G512" t="s">
-        <v>878</v>
+        <v>822</v>
       </c>
     </row>
     <row r="513" spans="1:7">
@@ -15704,7 +15089,7 @@
         <v>702</v>
       </c>
       <c r="G513" t="s">
-        <v>847</v>
+        <v>824</v>
       </c>
     </row>
     <row r="514" spans="1:7">
@@ -15727,7 +15112,7 @@
         <v>641</v>
       </c>
       <c r="G514" t="s">
-        <v>873</v>
+        <v>886</v>
       </c>
     </row>
     <row r="515" spans="1:7">
@@ -15750,7 +15135,7 @@
         <v>702</v>
       </c>
       <c r="G515" t="s">
-        <v>1167</v>
+        <v>972</v>
       </c>
     </row>
     <row r="516" spans="1:7">
@@ -15773,7 +15158,7 @@
         <v>702</v>
       </c>
       <c r="G516" t="s">
-        <v>1168</v>
+        <v>885</v>
       </c>
     </row>
     <row r="517" spans="1:7">
@@ -15796,7 +15181,7 @@
         <v>655</v>
       </c>
       <c r="G517" t="s">
-        <v>1169</v>
+        <v>973</v>
       </c>
     </row>
     <row r="518" spans="1:7">
@@ -15819,7 +15204,7 @@
         <v>652</v>
       </c>
       <c r="G518" t="s">
-        <v>1170</v>
+        <v>974</v>
       </c>
     </row>
     <row r="519" spans="1:7">
@@ -15842,7 +15227,7 @@
         <v>808</v>
       </c>
       <c r="G519" t="s">
-        <v>1171</v>
+        <v>975</v>
       </c>
     </row>
     <row r="520" spans="1:7">
@@ -15865,7 +15250,7 @@
         <v>700</v>
       </c>
       <c r="G520" t="s">
-        <v>878</v>
+        <v>824</v>
       </c>
     </row>
     <row r="521" spans="1:7">
@@ -15888,7 +15273,7 @@
         <v>700</v>
       </c>
       <c r="G521" t="s">
-        <v>1172</v>
+        <v>822</v>
       </c>
     </row>
     <row r="522" spans="1:7">
@@ -15911,7 +15296,7 @@
         <v>652</v>
       </c>
       <c r="G522" t="s">
-        <v>1173</v>
+        <v>976</v>
       </c>
     </row>
     <row r="523" spans="1:7">
@@ -15934,7 +15319,7 @@
         <v>702</v>
       </c>
       <c r="G523" t="s">
-        <v>1174</v>
+        <v>870</v>
       </c>
     </row>
     <row r="524" spans="1:7">
@@ -15957,7 +15342,7 @@
         <v>635</v>
       </c>
       <c r="G524" t="s">
-        <v>1175</v>
+        <v>826</v>
       </c>
     </row>
     <row r="525" spans="1:7">
@@ -15977,7 +15362,7 @@
         <v>625</v>
       </c>
       <c r="G525" t="s">
-        <v>965</v>
+        <v>815</v>
       </c>
     </row>
     <row r="526" spans="1:7">
@@ -16000,7 +15385,7 @@
         <v>639</v>
       </c>
       <c r="G526" t="s">
-        <v>1176</v>
+        <v>977</v>
       </c>
     </row>
     <row r="527" spans="1:7">
@@ -16023,7 +15408,7 @@
         <v>710</v>
       </c>
       <c r="G527" t="s">
-        <v>968</v>
+        <v>978</v>
       </c>
     </row>
     <row r="528" spans="1:7">
@@ -16046,7 +15431,7 @@
         <v>642</v>
       </c>
       <c r="G528" t="s">
-        <v>1177</v>
+        <v>979</v>
       </c>
     </row>
     <row r="529" spans="1:7">
@@ -16069,7 +15454,7 @@
         <v>638</v>
       </c>
       <c r="G529" t="s">
-        <v>1178</v>
+        <v>931</v>
       </c>
     </row>
     <row r="530" spans="1:7">
@@ -16115,7 +15500,7 @@
         <v>640</v>
       </c>
       <c r="G531" t="s">
-        <v>873</v>
+        <v>948</v>
       </c>
     </row>
     <row r="532" spans="1:7">
@@ -16138,7 +15523,7 @@
         <v>668</v>
       </c>
       <c r="G532" t="s">
-        <v>849</v>
+        <v>822</v>
       </c>
     </row>
     <row r="533" spans="1:7">
@@ -16161,7 +15546,7 @@
         <v>677</v>
       </c>
       <c r="G533" t="s">
-        <v>873</v>
+        <v>822</v>
       </c>
     </row>
     <row r="534" spans="1:7">
@@ -16207,7 +15592,7 @@
         <v>809</v>
       </c>
       <c r="G535" t="s">
-        <v>1155</v>
+        <v>922</v>
       </c>
     </row>
     <row r="536" spans="1:7">
@@ -16230,7 +15615,7 @@
         <v>699</v>
       </c>
       <c r="G536" t="s">
-        <v>1179</v>
+        <v>980</v>
       </c>
     </row>
     <row r="537" spans="1:7">
@@ -16253,7 +15638,7 @@
         <v>674</v>
       </c>
       <c r="G537" t="s">
-        <v>1180</v>
+        <v>981</v>
       </c>
     </row>
     <row r="538" spans="1:7">
@@ -16276,7 +15661,7 @@
         <v>659</v>
       </c>
       <c r="G538" t="s">
-        <v>1181</v>
+        <v>820</v>
       </c>
     </row>
     <row r="539" spans="1:7">
@@ -16299,7 +15684,7 @@
         <v>640</v>
       </c>
       <c r="G539" t="s">
-        <v>849</v>
+        <v>824</v>
       </c>
     </row>
     <row r="540" spans="1:7">
@@ -16322,7 +15707,7 @@
         <v>649</v>
       </c>
       <c r="G540" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
     </row>
     <row r="541" spans="1:7">
@@ -16345,7 +15730,7 @@
         <v>810</v>
       </c>
       <c r="G541" t="s">
-        <v>1182</v>
+        <v>882</v>
       </c>
     </row>
     <row r="542" spans="1:7">
@@ -16368,7 +15753,7 @@
         <v>811</v>
       </c>
       <c r="G542" t="s">
-        <v>1183</v>
+        <v>982</v>
       </c>
     </row>
     <row r="543" spans="1:7">
@@ -16391,7 +15776,7 @@
         <v>702</v>
       </c>
       <c r="G543" t="s">
-        <v>965</v>
+        <v>815</v>
       </c>
     </row>
     <row r="544" spans="1:7">
@@ -16414,7 +15799,7 @@
         <v>711</v>
       </c>
       <c r="G544" t="s">
-        <v>1184</v>
+        <v>978</v>
       </c>
     </row>
     <row r="545" spans="1:7">
